--- a/activaspasivas ponderadas_2021_2025.xlsx
+++ b/activaspasivas ponderadas_2021_2025.xlsx
@@ -1027,56 +1027,56 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="148">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1084,11 +1084,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1096,15 +1096,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1112,19 +1112,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1136,35 +1136,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1176,7 +1176,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1188,11 +1188,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1212,11 +1212,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1228,7 +1228,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1240,59 +1240,59 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1300,7 +1300,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1308,15 +1308,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1332,11 +1332,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="26" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1344,7 +1344,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1372,23 +1372,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1400,207 +1400,211 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="21" fillId="4" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="21" fillId="4" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="8" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1608,11 +1612,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1725,8 +1729,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.272368798394035"/>
-          <c:y val="0.0466286025013594"/>
+          <c:x val="0.272420720332903"/>
+          <c:y val="0.0466349422161795"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1744,10 +1748,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.107757384571265"/>
-          <c:y val="0.050978792822186"/>
-          <c:w val="0.8698738170347"/>
-          <c:h val="0.774061990212072"/>
+          <c:x val="0.107762950208064"/>
+          <c:y val="0.0509857239972808"/>
+          <c:w val="0.8697804563065"/>
+          <c:h val="0.773895309313392"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -2427,11 +2431,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="26834843"/>
-        <c:axId val="10253491"/>
+        <c:axId val="84721394"/>
+        <c:axId val="42757286"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="26834843"/>
+        <c:axId val="84721394"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2463,7 +2467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10253491"/>
+        <c:crossAx val="42757286"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2471,7 +2475,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10253491"/>
+        <c:axId val="42757286"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.2"/>
@@ -2501,7 +2505,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26834843"/>
+        <c:crossAx val="84721394"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.04"/>
@@ -2601,8 +2605,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.267179925862561"/>
-          <c:y val="0.0591560404890233"/>
+          <c:x val="0.267227849907262"/>
+          <c:y val="0.0591638180383907"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -2620,10 +2624,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.131593954947248"/>
-          <c:y val="0.066912054686473"/>
-          <c:w val="0.860065583119475"/>
-          <c:h val="0.774023925331931"/>
+          <c:x val="0.131616493080325"/>
+          <c:y val="0.0669208519589798"/>
+          <c:w val="0.860037095163361"/>
+          <c:h val="0.773862739942151"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -3231,11 +3235,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="71397266"/>
-        <c:axId val="53824147"/>
+        <c:axId val="55885118"/>
+        <c:axId val="41760718"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="71397266"/>
+        <c:axId val="55885118"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3267,7 +3271,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53824147"/>
+        <c:crossAx val="41760718"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3275,7 +3279,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53824147"/>
+        <c:axId val="41760718"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.2"/>
@@ -3305,7 +3309,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71397266"/>
+        <c:crossAx val="55885118"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.04"/>
@@ -3381,9 +3385,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>576000</xdr:colOff>
+      <xdr:colOff>575640</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>123480</xdr:rowOff>
+      <xdr:rowOff>123120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3391,8 +3395,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6242760" y="7515000"/>
-        <a:ext cx="5020920" cy="2647800"/>
+        <a:off x="6243480" y="7515000"/>
+        <a:ext cx="5017320" cy="2647440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3411,9 +3415,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>614160</xdr:colOff>
+      <xdr:colOff>613800</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>42480</xdr:rowOff>
+      <xdr:rowOff>42120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3421,8 +3425,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6252120" y="10505880"/>
-        <a:ext cx="5049720" cy="2738160"/>
+        <a:off x="6252840" y="10505880"/>
+        <a:ext cx="5046120" cy="2737800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3616,7 +3620,7 @@
   <dimension ref="B1:Y415"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="7.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="11.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3"/>
@@ -3772,10 +3776,6 @@
       </c>
       <c r="I6" s="13" t="n">
         <v>0.0473242274039947</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <f aca="false">COUNT(I6:I81)</f>
-        <v>76</v>
       </c>
       <c r="N6" s="15" t="n">
         <v>43831</v>
@@ -8956,10 +8956,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BY105"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="30.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="2" style="4" width="11.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="30.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="2" style="4" width="11.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="4" width="9.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="75" min="75" style="4" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="76" min="76" style="4" width="10.26"/>
@@ -19828,112 +19828,112 @@
   <dimension ref="A1:BY24"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="45" min="2" style="0" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="76" min="46" style="0" width="10.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="93" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="45" min="2" style="93" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="76" min="46" style="93" width="10.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="94" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" s="102" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95" t="n">
+    <row r="2" s="103" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="95"/>
+      <c r="B2" s="96" t="n">
         <v>2020</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="96" t="n">
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="97" t="n">
         <v>2021</v>
       </c>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="96"/>
-      <c r="S2" s="96"/>
-      <c r="T2" s="96"/>
-      <c r="U2" s="96"/>
-      <c r="V2" s="96"/>
-      <c r="W2" s="96"/>
-      <c r="X2" s="96"/>
-      <c r="Y2" s="96"/>
-      <c r="Z2" s="97" t="n">
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
+      <c r="W2" s="97"/>
+      <c r="X2" s="97"/>
+      <c r="Y2" s="97"/>
+      <c r="Z2" s="98" t="n">
         <v>2022</v>
       </c>
-      <c r="AA2" s="97"/>
-      <c r="AB2" s="97"/>
-      <c r="AC2" s="97"/>
-      <c r="AD2" s="97"/>
-      <c r="AE2" s="97"/>
-      <c r="AF2" s="97"/>
-      <c r="AG2" s="97"/>
-      <c r="AH2" s="97"/>
-      <c r="AI2" s="97"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="97"/>
-      <c r="AL2" s="98" t="n">
+      <c r="AA2" s="98"/>
+      <c r="AB2" s="98"/>
+      <c r="AC2" s="98"/>
+      <c r="AD2" s="98"/>
+      <c r="AE2" s="98"/>
+      <c r="AF2" s="98"/>
+      <c r="AG2" s="98"/>
+      <c r="AH2" s="98"/>
+      <c r="AI2" s="98"/>
+      <c r="AJ2" s="98"/>
+      <c r="AK2" s="98"/>
+      <c r="AL2" s="99" t="n">
         <v>2023</v>
       </c>
-      <c r="AM2" s="98"/>
-      <c r="AN2" s="98"/>
-      <c r="AO2" s="98"/>
-      <c r="AP2" s="98"/>
-      <c r="AQ2" s="98"/>
-      <c r="AR2" s="98"/>
-      <c r="AS2" s="98"/>
-      <c r="AT2" s="98"/>
-      <c r="AU2" s="98"/>
-      <c r="AV2" s="98"/>
-      <c r="AW2" s="98"/>
-      <c r="AX2" s="99" t="n">
+      <c r="AM2" s="99"/>
+      <c r="AN2" s="99"/>
+      <c r="AO2" s="99"/>
+      <c r="AP2" s="99"/>
+      <c r="AQ2" s="99"/>
+      <c r="AR2" s="99"/>
+      <c r="AS2" s="99"/>
+      <c r="AT2" s="99"/>
+      <c r="AU2" s="99"/>
+      <c r="AV2" s="99"/>
+      <c r="AW2" s="99"/>
+      <c r="AX2" s="100" t="n">
         <v>2024</v>
       </c>
-      <c r="AY2" s="99"/>
-      <c r="AZ2" s="99"/>
-      <c r="BA2" s="99"/>
-      <c r="BB2" s="99"/>
-      <c r="BC2" s="99"/>
-      <c r="BD2" s="99"/>
-      <c r="BE2" s="99"/>
-      <c r="BF2" s="99"/>
-      <c r="BG2" s="99"/>
-      <c r="BH2" s="99"/>
-      <c r="BI2" s="99"/>
-      <c r="BJ2" s="100" t="n">
+      <c r="AY2" s="100"/>
+      <c r="AZ2" s="100"/>
+      <c r="BA2" s="100"/>
+      <c r="BB2" s="100"/>
+      <c r="BC2" s="100"/>
+      <c r="BD2" s="100"/>
+      <c r="BE2" s="100"/>
+      <c r="BF2" s="100"/>
+      <c r="BG2" s="100"/>
+      <c r="BH2" s="100"/>
+      <c r="BI2" s="100"/>
+      <c r="BJ2" s="101" t="n">
         <v>2025</v>
       </c>
-      <c r="BK2" s="100"/>
-      <c r="BL2" s="100"/>
-      <c r="BM2" s="100"/>
-      <c r="BN2" s="100"/>
-      <c r="BO2" s="100"/>
-      <c r="BP2" s="100"/>
-      <c r="BQ2" s="100"/>
-      <c r="BR2" s="100"/>
-      <c r="BS2" s="100"/>
-      <c r="BT2" s="100"/>
-      <c r="BU2" s="100"/>
-      <c r="BV2" s="101" t="n">
+      <c r="BK2" s="101"/>
+      <c r="BL2" s="101"/>
+      <c r="BM2" s="101"/>
+      <c r="BN2" s="101"/>
+      <c r="BO2" s="101"/>
+      <c r="BP2" s="101"/>
+      <c r="BQ2" s="101"/>
+      <c r="BR2" s="101"/>
+      <c r="BS2" s="101"/>
+      <c r="BT2" s="101"/>
+      <c r="BU2" s="101"/>
+      <c r="BV2" s="102" t="n">
         <v>2026</v>
       </c>
-      <c r="BW2" s="101"/>
-      <c r="BX2" s="101"/>
-      <c r="BY2" s="101"/>
-    </row>
-    <row r="3" s="107" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="103"/>
-      <c r="B3" s="104" t="n">
+      <c r="BW2" s="102"/>
+      <c r="BX2" s="102"/>
+      <c r="BY2" s="102"/>
+    </row>
+    <row r="3" s="108" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="104"/>
+      <c r="B3" s="105" t="n">
         <v>43831</v>
       </c>
       <c r="C3" s="64" t="s">
@@ -20005,4181 +20005,4181 @@
       <c r="Y3" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="Z3" s="105" t="n">
+      <c r="Z3" s="106" t="n">
         <v>44562</v>
       </c>
-      <c r="AA3" s="105" t="s">
+      <c r="AA3" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="AB3" s="105" t="s">
+      <c r="AB3" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="AC3" s="105" t="s">
+      <c r="AC3" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="AD3" s="105" t="s">
+      <c r="AD3" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="AE3" s="105" t="s">
+      <c r="AE3" s="106" t="s">
         <v>26</v>
       </c>
-      <c r="AF3" s="105" t="s">
+      <c r="AF3" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="AG3" s="105" t="s">
+      <c r="AG3" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="AH3" s="105" t="s">
+      <c r="AH3" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="AI3" s="105" t="s">
+      <c r="AI3" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="AJ3" s="105" t="s">
+      <c r="AJ3" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="AK3" s="105" t="s">
+      <c r="AK3" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="AL3" s="105" t="n">
+      <c r="AL3" s="106" t="n">
         <v>44927</v>
       </c>
-      <c r="AM3" s="105" t="s">
+      <c r="AM3" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="AN3" s="105" t="s">
+      <c r="AN3" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="AO3" s="105" t="s">
+      <c r="AO3" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="AP3" s="105" t="s">
+      <c r="AP3" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="AQ3" s="105" t="s">
+      <c r="AQ3" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="AR3" s="105" t="s">
+      <c r="AR3" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="AS3" s="105" t="s">
+      <c r="AS3" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="AT3" s="105" t="s">
+      <c r="AT3" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="AU3" s="105" t="s">
+      <c r="AU3" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="AV3" s="105" t="s">
+      <c r="AV3" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="AW3" s="105" t="s">
+      <c r="AW3" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="AX3" s="106" t="n">
+      <c r="AX3" s="107" t="n">
         <v>45292</v>
       </c>
-      <c r="AY3" s="105" t="s">
+      <c r="AY3" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="AZ3" s="105" t="s">
+      <c r="AZ3" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="BA3" s="105" t="s">
+      <c r="BA3" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="BB3" s="105" t="s">
+      <c r="BB3" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="BC3" s="105" t="s">
+      <c r="BC3" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="BD3" s="105" t="s">
+      <c r="BD3" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="BE3" s="105" t="s">
+      <c r="BE3" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="BF3" s="105" t="s">
+      <c r="BF3" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="BG3" s="105" t="s">
+      <c r="BG3" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="BH3" s="105" t="s">
+      <c r="BH3" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="BI3" s="105" t="s">
+      <c r="BI3" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="BJ3" s="105" t="s">
+      <c r="BJ3" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="BK3" s="105" t="s">
+      <c r="BK3" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="BL3" s="105" t="s">
+      <c r="BL3" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="BM3" s="105" t="s">
+      <c r="BM3" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="BN3" s="105" t="s">
+      <c r="BN3" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="BO3" s="105" t="s">
+      <c r="BO3" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="105" t="s">
+      <c r="BP3" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="BQ3" s="105" t="s">
+      <c r="BQ3" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="BR3" s="105" t="s">
+      <c r="BR3" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="BS3" s="105" t="s">
+      <c r="BS3" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="BT3" s="105" t="s">
+      <c r="BT3" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="BU3" s="105" t="s">
+      <c r="BU3" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="BV3" s="105" t="s">
+      <c r="BV3" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="BW3" s="105" t="s">
+      <c r="BW3" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="BX3" s="105" t="s">
+      <c r="BX3" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="BY3" s="105" t="s">
+      <c r="BY3" s="106" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" s="102" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="108" t="s">
+    <row r="4" s="103" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111"/>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="AX4" s="113"/>
-      <c r="AZ4" s="114"/>
-      <c r="BB4" s="114"/>
-      <c r="BC4" s="114"/>
-      <c r="BD4" s="114"/>
-      <c r="BE4" s="114"/>
-      <c r="BF4" s="114"/>
-      <c r="BG4" s="114"/>
-      <c r="BH4" s="114"/>
-      <c r="BI4" s="114"/>
-      <c r="BJ4" s="114"/>
-      <c r="BK4" s="114"/>
-      <c r="BL4" s="114"/>
-      <c r="BM4" s="114"/>
-      <c r="BN4" s="114"/>
-      <c r="BO4" s="114"/>
-      <c r="BP4" s="114"/>
-      <c r="BQ4" s="114"/>
-      <c r="BR4" s="114"/>
-      <c r="BS4" s="114"/>
-      <c r="BT4" s="114"/>
-      <c r="BU4" s="114"/>
-      <c r="BV4" s="114"/>
-      <c r="BW4" s="114"/>
-      <c r="BX4" s="114"/>
-      <c r="BY4" s="114"/>
-    </row>
-    <row r="5" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="110"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113"/>
+      <c r="V4" s="113"/>
+      <c r="W4" s="113"/>
+      <c r="X4" s="113"/>
+      <c r="Y4" s="113"/>
+      <c r="AX4" s="114"/>
+      <c r="AZ4" s="115"/>
+      <c r="BB4" s="115"/>
+      <c r="BC4" s="115"/>
+      <c r="BD4" s="115"/>
+      <c r="BE4" s="115"/>
+      <c r="BF4" s="115"/>
+      <c r="BG4" s="115"/>
+      <c r="BH4" s="115"/>
+      <c r="BI4" s="115"/>
+      <c r="BJ4" s="115"/>
+      <c r="BK4" s="115"/>
+      <c r="BL4" s="115"/>
+      <c r="BM4" s="115"/>
+      <c r="BN4" s="115"/>
+      <c r="BO4" s="115"/>
+      <c r="BP4" s="115"/>
+      <c r="BQ4" s="115"/>
+      <c r="BR4" s="115"/>
+      <c r="BS4" s="115"/>
+      <c r="BT4" s="115"/>
+      <c r="BU4" s="115"/>
+      <c r="BV4" s="115"/>
+      <c r="BW4" s="115"/>
+      <c r="BX4" s="115"/>
+      <c r="BY4" s="115"/>
+    </row>
+    <row r="5" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="115" t="n">
+      <c r="B5" s="116" t="n">
         <v>0.0425975319497057</v>
       </c>
-      <c r="C5" s="115" t="n">
+      <c r="C5" s="116" t="n">
         <v>0.0430296117634239</v>
       </c>
-      <c r="D5" s="115" t="n">
+      <c r="D5" s="116" t="n">
         <v>0.0428054714365006</v>
       </c>
-      <c r="E5" s="115" t="n">
+      <c r="E5" s="116" t="n">
         <v>0.0390249288340507</v>
       </c>
-      <c r="F5" s="115" t="n">
+      <c r="F5" s="116" t="n">
         <v>0.0398298374120185</v>
       </c>
-      <c r="G5" s="115" t="n">
+      <c r="G5" s="116" t="n">
         <v>0.0385535560433425</v>
       </c>
-      <c r="H5" s="115" t="n">
+      <c r="H5" s="116" t="n">
         <v>0.0363309400540588</v>
       </c>
-      <c r="I5" s="115" t="n">
+      <c r="I5" s="116" t="n">
         <v>0.0384256493956196</v>
       </c>
-      <c r="J5" s="115" t="n">
+      <c r="J5" s="116" t="n">
         <v>0.0306091387472511</v>
       </c>
-      <c r="K5" s="115" t="n">
+      <c r="K5" s="116" t="n">
         <v>0.0336664387548364</v>
       </c>
-      <c r="L5" s="115" t="n">
+      <c r="L5" s="116" t="n">
         <v>0.0294372181291466</v>
       </c>
-      <c r="M5" s="115" t="n">
+      <c r="M5" s="116" t="n">
         <v>0.03119040918931</v>
       </c>
-      <c r="N5" s="115" t="n">
+      <c r="N5" s="116" t="n">
         <v>0.0287354948622432</v>
       </c>
-      <c r="O5" s="115" t="n">
+      <c r="O5" s="116" t="n">
         <v>0.0290603555525303</v>
       </c>
-      <c r="P5" s="115" t="n">
+      <c r="P5" s="116" t="n">
         <v>0.0305416599639899</v>
       </c>
-      <c r="Q5" s="115" t="n">
+      <c r="Q5" s="116" t="n">
         <v>0.0263228765870711</v>
       </c>
-      <c r="R5" s="115" t="n">
+      <c r="R5" s="116" t="n">
         <v>0.0255510140969182</v>
       </c>
-      <c r="S5" s="116" t="n">
+      <c r="S5" s="117" t="n">
         <v>0.0224800265455571</v>
       </c>
-      <c r="T5" s="116" t="n">
+      <c r="T5" s="117" t="n">
         <v>0.025912312053923</v>
       </c>
-      <c r="U5" s="116" t="n">
+      <c r="U5" s="117" t="n">
         <v>0.02671795191373</v>
       </c>
-      <c r="V5" s="116" t="n">
+      <c r="V5" s="117" t="n">
         <v>0.0262710914275744</v>
       </c>
-      <c r="W5" s="116" t="n">
+      <c r="W5" s="117" t="n">
         <v>0.0266298636822424</v>
       </c>
-      <c r="X5" s="116" t="n">
+      <c r="X5" s="117" t="n">
         <v>0.0276880295544569</v>
       </c>
-      <c r="Y5" s="116" t="n">
+      <c r="Y5" s="117" t="n">
         <v>0.0269735075315241</v>
       </c>
-      <c r="Z5" s="116" t="n">
+      <c r="Z5" s="117" t="n">
         <v>0.0271627882955207</v>
       </c>
-      <c r="AA5" s="116" t="n">
+      <c r="AA5" s="117" t="n">
         <v>0.0261031477003621</v>
       </c>
-      <c r="AB5" s="116" t="n">
+      <c r="AB5" s="117" t="n">
         <v>0.0283801058567175</v>
       </c>
-      <c r="AC5" s="116" t="n">
+      <c r="AC5" s="117" t="n">
         <v>0.0246963202814825</v>
       </c>
-      <c r="AD5" s="116" t="n">
+      <c r="AD5" s="117" t="n">
         <v>0.0243352208239242</v>
       </c>
-      <c r="AE5" s="116" t="n">
+      <c r="AE5" s="117" t="n">
         <v>0.0222122199689108</v>
       </c>
-      <c r="AF5" s="116" t="n">
+      <c r="AF5" s="117" t="n">
         <v>0.0263611952634314</v>
       </c>
-      <c r="AG5" s="116" t="n">
+      <c r="AG5" s="117" t="n">
         <v>0.0260597550720116</v>
       </c>
-      <c r="AH5" s="116" t="n">
+      <c r="AH5" s="117" t="n">
         <v>0.0261833679730578</v>
       </c>
-      <c r="AI5" s="116" t="n">
+      <c r="AI5" s="117" t="n">
         <v>0.0272182114548304</v>
       </c>
-      <c r="AJ5" s="116" t="n">
+      <c r="AJ5" s="117" t="n">
         <v>0.0234144818768833</v>
       </c>
-      <c r="AK5" s="116" t="n">
+      <c r="AK5" s="117" t="n">
         <v>0.0299424015884176</v>
       </c>
-      <c r="AL5" s="116" t="n">
+      <c r="AL5" s="117" t="n">
         <v>0.0282928063932137</v>
       </c>
-      <c r="AM5" s="116" t="n">
+      <c r="AM5" s="117" t="n">
         <v>0.0273472536961994</v>
       </c>
-      <c r="AN5" s="116" t="n">
+      <c r="AN5" s="117" t="n">
         <v>0.0297293845192915</v>
       </c>
-      <c r="AO5" s="116" t="n">
+      <c r="AO5" s="117" t="n">
         <v>0.0289697559913177</v>
       </c>
-      <c r="AP5" s="116" t="n">
+      <c r="AP5" s="117" t="n">
         <v>0.0272435904908619</v>
       </c>
-      <c r="AQ5" s="116" t="n">
+      <c r="AQ5" s="117" t="n">
         <v>0.0284522602097437</v>
       </c>
-      <c r="AR5" s="116" t="n">
+      <c r="AR5" s="117" t="n">
         <v>0.0314238641257269</v>
       </c>
-      <c r="AS5" s="116" t="n">
+      <c r="AS5" s="117" t="n">
         <v>0.0304759983291592</v>
       </c>
-      <c r="AT5" s="116" t="n">
+      <c r="AT5" s="117" t="n">
         <v>0.0318348942638575</v>
       </c>
-      <c r="AU5" s="116" t="n">
+      <c r="AU5" s="117" t="n">
         <v>0.031196101714123</v>
       </c>
-      <c r="AV5" s="116" t="n">
+      <c r="AV5" s="117" t="n">
         <v>0.0331759148770066</v>
       </c>
-      <c r="AW5" s="116" t="n">
+      <c r="AW5" s="117" t="n">
         <v>0.0371728391920679</v>
       </c>
-      <c r="AX5" s="116" t="n">
+      <c r="AX5" s="117" t="n">
         <v>0.0334823221044087</v>
       </c>
-      <c r="AY5" s="116" t="n">
+      <c r="AY5" s="117" t="n">
         <v>0.0327445507082802</v>
       </c>
-      <c r="AZ5" s="116" t="n">
+      <c r="AZ5" s="117" t="n">
         <v>0.031717847036904</v>
       </c>
-      <c r="BA5" s="116" t="n">
+      <c r="BA5" s="117" t="n">
         <v>0.0271286383133506</v>
       </c>
-      <c r="BB5" s="116" t="n">
+      <c r="BB5" s="117" t="n">
         <v>0.0316124210693841</v>
       </c>
-      <c r="BC5" s="116" t="n">
+      <c r="BC5" s="117" t="n">
         <v>0.029885389538783</v>
       </c>
-      <c r="BD5" s="116" t="n">
+      <c r="BD5" s="117" t="n">
         <v>0.0339233690797094</v>
       </c>
-      <c r="BE5" s="116" t="n">
+      <c r="BE5" s="117" t="n">
         <v>0.0326259746022958</v>
       </c>
-      <c r="BF5" s="116" t="n">
+      <c r="BF5" s="117" t="n">
         <v>0.0310759977252037</v>
       </c>
-      <c r="BG5" s="117" t="n">
+      <c r="BG5" s="118" t="n">
         <v>0.0323358437587647</v>
       </c>
-      <c r="BH5" s="116" t="n">
+      <c r="BH5" s="117" t="n">
         <v>0.0379967282681319</v>
       </c>
-      <c r="BI5" s="116" t="n">
+      <c r="BI5" s="117" t="n">
         <v>0.0387579408910653</v>
       </c>
-      <c r="BJ5" s="116" t="n">
+      <c r="BJ5" s="117" t="n">
         <v>0.0328855371489022</v>
       </c>
-      <c r="BK5" s="116" t="n">
+      <c r="BK5" s="117" t="n">
         <v>0.0350349694278179</v>
       </c>
-      <c r="BL5" s="116" t="n">
+      <c r="BL5" s="117" t="n">
         <v>0.0331299335321065</v>
       </c>
-      <c r="BM5" s="116" t="n">
+      <c r="BM5" s="117" t="n">
         <v>0.036190720502507</v>
       </c>
-      <c r="BN5" s="116" t="n">
+      <c r="BN5" s="117" t="n">
         <v>0.033102591723603</v>
       </c>
-      <c r="BO5" s="116" t="n">
+      <c r="BO5" s="117" t="n">
         <v>0.0358603757341374</v>
       </c>
-      <c r="BP5" s="116" t="n">
+      <c r="BP5" s="117" t="n">
         <v>0.0371558955895397</v>
       </c>
-      <c r="BQ5" s="116" t="n">
+      <c r="BQ5" s="117" t="n">
         <v>0.0377938781104779</v>
       </c>
-      <c r="BR5" s="116" t="n">
+      <c r="BR5" s="117" t="n">
         <v>0.0366084464133556</v>
       </c>
-      <c r="BS5" s="116" t="n">
+      <c r="BS5" s="117" t="n">
         <v>0.0337001932973153</v>
       </c>
-      <c r="BT5" s="116" t="n">
+      <c r="BT5" s="117" t="n">
         <v>0.0320692096921545</v>
       </c>
-      <c r="BU5" s="116" t="n">
+      <c r="BU5" s="117" t="n">
         <v>0.0376644441292932</v>
       </c>
-      <c r="BV5" s="116" t="n">
+      <c r="BV5" s="117" t="n">
         <v>0.0339340662100494</v>
       </c>
-      <c r="BW5" s="116" t="n">
+      <c r="BW5" s="117" t="n">
         <v>0.0396650878473845</v>
       </c>
-      <c r="BX5" s="117" t="n">
+      <c r="BX5" s="118" t="n">
         <v>0.0334989323103511</v>
       </c>
-      <c r="BY5" s="118" t="n">
+      <c r="BY5" s="119" t="n">
         <v>0.0359070276473451</v>
       </c>
     </row>
-    <row r="6" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="119" t="s">
+    <row r="6" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="120" t="n">
+      <c r="B6" s="121" t="n">
         <v>0.0110465095171142</v>
       </c>
-      <c r="C6" s="120" t="n">
+      <c r="C6" s="121" t="n">
         <v>0.0109708083882109</v>
       </c>
-      <c r="D6" s="120" t="n">
+      <c r="D6" s="121" t="n">
         <v>0.0103035538679219</v>
       </c>
-      <c r="E6" s="120" t="n">
+      <c r="E6" s="121" t="n">
         <v>0.0112412498661007</v>
       </c>
-      <c r="F6" s="120" t="n">
+      <c r="F6" s="121" t="n">
         <v>0.00996749099261132</v>
       </c>
-      <c r="G6" s="121" t="n">
+      <c r="G6" s="122" t="n">
         <v>0.0104772318985669</v>
       </c>
-      <c r="H6" s="121" t="n">
+      <c r="H6" s="122" t="n">
         <v>0.0103453100543538</v>
       </c>
-      <c r="I6" s="121" t="n">
+      <c r="I6" s="122" t="n">
         <v>0.0103783672443574</v>
       </c>
-      <c r="J6" s="121" t="n">
+      <c r="J6" s="122" t="n">
         <v>0.0106989371910817</v>
       </c>
-      <c r="K6" s="121" t="n">
+      <c r="K6" s="122" t="n">
         <v>0.0102836486871471</v>
       </c>
-      <c r="L6" s="121" t="n">
+      <c r="L6" s="122" t="n">
         <v>0.0102236362149254</v>
       </c>
-      <c r="M6" s="121" t="n">
+      <c r="M6" s="122" t="n">
         <v>0.010220710763857</v>
       </c>
-      <c r="N6" s="121" t="n">
+      <c r="N6" s="122" t="n">
         <v>0.0108266107158874</v>
       </c>
-      <c r="O6" s="121" t="n">
+      <c r="O6" s="122" t="n">
         <v>0.0101845292710684</v>
       </c>
-      <c r="P6" s="121" t="n">
+      <c r="P6" s="122" t="n">
         <v>0.0103001438270229</v>
       </c>
-      <c r="Q6" s="121" t="n">
+      <c r="Q6" s="122" t="n">
         <v>0.0103404879826739</v>
       </c>
-      <c r="R6" s="121" t="n">
+      <c r="R6" s="122" t="n">
         <v>0.0102246570029521</v>
       </c>
-      <c r="S6" s="121" t="n">
+      <c r="S6" s="122" t="n">
         <v>0.0104198257821497</v>
       </c>
-      <c r="T6" s="121" t="n">
+      <c r="T6" s="122" t="n">
         <v>0.0102524162488645</v>
       </c>
-      <c r="U6" s="121" t="n">
+      <c r="U6" s="122" t="n">
         <v>0.01033342609272</v>
       </c>
-      <c r="V6" s="121" t="n">
+      <c r="V6" s="122" t="n">
         <v>0.0104047147154597</v>
       </c>
-      <c r="W6" s="121" t="n">
+      <c r="W6" s="122" t="n">
         <v>0.0102283204482348</v>
       </c>
-      <c r="X6" s="121" t="n">
+      <c r="X6" s="122" t="n">
         <v>0.00999076935334248</v>
       </c>
-      <c r="Y6" s="121" t="n">
+      <c r="Y6" s="122" t="n">
         <v>0.0101127871673367</v>
       </c>
-      <c r="Z6" s="121" t="n">
+      <c r="Z6" s="122" t="n">
         <v>0.0103313396725246</v>
       </c>
-      <c r="AA6" s="121" t="n">
+      <c r="AA6" s="122" t="n">
         <v>0.0102264307468826</v>
       </c>
-      <c r="AB6" s="121" t="n">
+      <c r="AB6" s="122" t="n">
         <v>0.0101067832591123</v>
       </c>
-      <c r="AC6" s="121" t="n">
+      <c r="AC6" s="122" t="n">
         <v>0.0102346630628568</v>
       </c>
-      <c r="AD6" s="121" t="n">
+      <c r="AD6" s="122" t="n">
         <v>0.0101641763198729</v>
       </c>
-      <c r="AE6" s="121" t="n">
+      <c r="AE6" s="122" t="n">
         <v>0.0104642261025874</v>
       </c>
-      <c r="AF6" s="121" t="n">
+      <c r="AF6" s="122" t="n">
         <v>0.010311037918437</v>
       </c>
-      <c r="AG6" s="121" t="n">
+      <c r="AG6" s="122" t="n">
         <v>0.0103334106306752</v>
       </c>
-      <c r="AH6" s="121" t="n">
+      <c r="AH6" s="122" t="n">
         <v>0.0104080293541023</v>
       </c>
-      <c r="AI6" s="121" t="n">
+      <c r="AI6" s="122" t="n">
         <v>0.0101569645388207</v>
       </c>
-      <c r="AJ6" s="121" t="n">
+      <c r="AJ6" s="122" t="n">
         <v>0.0101270623757508</v>
       </c>
-      <c r="AK6" s="121" t="n">
+      <c r="AK6" s="122" t="n">
         <v>0.0106170377949023</v>
       </c>
-      <c r="AL6" s="121" t="n">
+      <c r="AL6" s="122" t="n">
         <v>0.01020711863977</v>
       </c>
-      <c r="AM6" s="121" t="n">
+      <c r="AM6" s="122" t="n">
         <v>0.010318056942975</v>
       </c>
-      <c r="AN6" s="121" t="n">
+      <c r="AN6" s="122" t="n">
         <v>0.0102033521004945</v>
       </c>
-      <c r="AO6" s="121" t="n">
+      <c r="AO6" s="122" t="n">
         <v>0.009951468428651</v>
       </c>
-      <c r="AP6" s="121" t="n">
+      <c r="AP6" s="122" t="n">
         <v>0.0106665532687846</v>
       </c>
-      <c r="AQ6" s="121" t="n">
+      <c r="AQ6" s="122" t="n">
         <v>0.0107752750561403</v>
       </c>
-      <c r="AR6" s="121" t="n">
+      <c r="AR6" s="122" t="n">
         <v>0.010243808165793</v>
       </c>
-      <c r="AS6" s="121" t="n">
+      <c r="AS6" s="122" t="n">
         <v>0.0100462809834606</v>
       </c>
-      <c r="AT6" s="121" t="n">
+      <c r="AT6" s="122" t="n">
         <v>0.0103087781219652</v>
       </c>
-      <c r="AU6" s="121" t="n">
+      <c r="AU6" s="122" t="n">
         <v>0.0101011033521678</v>
       </c>
-      <c r="AV6" s="121" t="n">
+      <c r="AV6" s="122" t="n">
         <v>0.0101333997793468</v>
       </c>
-      <c r="AW6" s="121" t="n">
+      <c r="AW6" s="122" t="n">
         <v>0.0107871482802423</v>
       </c>
-      <c r="AX6" s="121" t="n">
+      <c r="AX6" s="122" t="n">
         <v>0.0102687018740771</v>
       </c>
-      <c r="AY6" s="121" t="n">
+      <c r="AY6" s="122" t="n">
         <v>0.0101873593703658</v>
       </c>
-      <c r="AZ6" s="121" t="n">
+      <c r="AZ6" s="122" t="n">
         <v>0.0129417478436936</v>
       </c>
-      <c r="BA6" s="121" t="n">
+      <c r="BA6" s="122" t="n">
         <v>0.0103975299113572</v>
       </c>
-      <c r="BB6" s="121" t="n">
+      <c r="BB6" s="122" t="n">
         <v>0.0104983163531364</v>
       </c>
-      <c r="BC6" s="121" t="n">
+      <c r="BC6" s="122" t="n">
         <v>0.0102879772321977</v>
       </c>
-      <c r="BD6" s="121" t="n">
+      <c r="BD6" s="122" t="n">
         <v>0.0102790448503927</v>
       </c>
-      <c r="BE6" s="121" t="n">
+      <c r="BE6" s="122" t="n">
         <v>0.0104797683649691</v>
       </c>
-      <c r="BF6" s="121" t="n">
+      <c r="BF6" s="122" t="n">
         <v>0.010123853312396</v>
       </c>
-      <c r="BG6" s="120" t="n">
+      <c r="BG6" s="121" t="n">
         <v>0.00995814639092763</v>
       </c>
-      <c r="BH6" s="122" t="n">
+      <c r="BH6" s="123" t="n">
         <v>0.0101275146219646</v>
       </c>
-      <c r="BI6" s="122" t="n">
+      <c r="BI6" s="123" t="n">
         <v>0.0102263560193177</v>
       </c>
-      <c r="BJ6" s="122" t="n">
+      <c r="BJ6" s="123" t="n">
         <v>0.0100014389806602</v>
       </c>
-      <c r="BK6" s="122" t="n">
+      <c r="BK6" s="123" t="n">
         <v>0.0100533002458096</v>
       </c>
-      <c r="BL6" s="122" t="n">
+      <c r="BL6" s="123" t="n">
         <v>0.010073275868001</v>
       </c>
-      <c r="BM6" s="122" t="n">
+      <c r="BM6" s="123" t="n">
         <v>0.0108680764706629</v>
       </c>
-      <c r="BN6" s="122" t="n">
+      <c r="BN6" s="123" t="n">
         <v>0.0101366886076159</v>
       </c>
-      <c r="BO6" s="122" t="n">
+      <c r="BO6" s="123" t="n">
         <v>0.0102264308166738</v>
       </c>
-      <c r="BP6" s="122" t="n">
+      <c r="BP6" s="123" t="n">
         <v>0.0103621350284557</v>
       </c>
-      <c r="BQ6" s="122" t="n">
+      <c r="BQ6" s="123" t="n">
         <v>0.010046935050863</v>
       </c>
-      <c r="BR6" s="122" t="n">
+      <c r="BR6" s="123" t="n">
         <v>0.0100456304471952</v>
       </c>
-      <c r="BS6" s="122" t="n">
+      <c r="BS6" s="123" t="n">
         <v>0.0101096967408491</v>
       </c>
-      <c r="BT6" s="122" t="n">
+      <c r="BT6" s="123" t="n">
         <v>0.0104565615663604</v>
       </c>
-      <c r="BU6" s="122" t="n">
+      <c r="BU6" s="123" t="n">
         <v>0.0100718799596501</v>
       </c>
-      <c r="BV6" s="122" t="n">
+      <c r="BV6" s="123" t="n">
         <v>0.00985470133425418</v>
       </c>
-      <c r="BW6" s="122" t="n">
+      <c r="BW6" s="123" t="n">
         <v>0.00988340920937986</v>
       </c>
-      <c r="BX6" s="123" t="n">
+      <c r="BX6" s="124" t="n">
         <v>0.0101109336907753</v>
       </c>
-      <c r="BY6" s="124" t="n">
+      <c r="BY6" s="125" t="n">
         <v>0.0100086438963109</v>
       </c>
     </row>
-    <row r="7" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="119" t="s">
+    <row r="7" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="120" t="n">
+      <c r="B7" s="121" t="n">
         <v>0.0127234846099057</v>
       </c>
-      <c r="C7" s="120" t="n">
+      <c r="C7" s="121" t="n">
         <v>0.0130807296976071</v>
       </c>
-      <c r="D7" s="120" t="n">
+      <c r="D7" s="121" t="n">
         <v>0.0138909155300187</v>
       </c>
-      <c r="E7" s="120" t="n">
+      <c r="E7" s="121" t="n">
         <v>0.0163684667952602</v>
       </c>
-      <c r="F7" s="120" t="n">
+      <c r="F7" s="121" t="n">
         <v>0.0179708957300668</v>
       </c>
-      <c r="G7" s="121" t="n">
+      <c r="G7" s="122" t="n">
         <v>0.0150456462468023</v>
       </c>
-      <c r="H7" s="121" t="n">
+      <c r="H7" s="122" t="n">
         <v>0.0132643743541724</v>
       </c>
-      <c r="I7" s="121" t="n">
+      <c r="I7" s="122" t="n">
         <v>0.0194202518191092</v>
       </c>
-      <c r="J7" s="121" t="n">
+      <c r="J7" s="122" t="n">
         <v>0.0182559325541738</v>
       </c>
-      <c r="K7" s="121" t="n">
+      <c r="K7" s="122" t="n">
         <v>0.0167422589304031</v>
       </c>
-      <c r="L7" s="121" t="n">
+      <c r="L7" s="122" t="n">
         <v>0.0157371303480572</v>
       </c>
-      <c r="M7" s="121" t="n">
+      <c r="M7" s="122" t="n">
         <v>0.0138944793366063</v>
       </c>
-      <c r="N7" s="121" t="n">
+      <c r="N7" s="122" t="n">
         <v>0.0191265526254895</v>
       </c>
-      <c r="O7" s="121" t="n">
+      <c r="O7" s="122" t="n">
         <v>0.0125950775658435</v>
       </c>
-      <c r="P7" s="121" t="n">
+      <c r="P7" s="122" t="n">
         <v>0.017336979781727</v>
       </c>
-      <c r="Q7" s="121" t="n">
+      <c r="Q7" s="122" t="n">
         <v>0.0136344879274333</v>
       </c>
-      <c r="R7" s="121" t="n">
+      <c r="R7" s="122" t="n">
         <v>0.00995579010149238</v>
       </c>
-      <c r="S7" s="121" t="n">
+      <c r="S7" s="122" t="n">
         <v>0.0100343515991667</v>
       </c>
-      <c r="T7" s="121" t="n">
+      <c r="T7" s="122" t="n">
         <v>0.00447172184553357</v>
       </c>
-      <c r="U7" s="121" t="n">
+      <c r="U7" s="122" t="n">
         <v>0.0100379915467715</v>
       </c>
-      <c r="V7" s="121" t="n">
+      <c r="V7" s="122" t="n">
         <v>0.00580551371926316</v>
       </c>
-      <c r="W7" s="121" t="n">
+      <c r="W7" s="122" t="n">
         <v>0.0120693691262435</v>
       </c>
-      <c r="X7" s="121" t="n">
+      <c r="X7" s="122" t="n">
         <v>0.0104800252412265</v>
       </c>
-      <c r="Y7" s="121" t="n">
+      <c r="Y7" s="122" t="n">
         <v>0.00732651466146734</v>
       </c>
-      <c r="Z7" s="121" t="n">
+      <c r="Z7" s="122" t="n">
         <v>0.00481570584076268</v>
       </c>
-      <c r="AA7" s="121" t="n">
+      <c r="AA7" s="122" t="n">
         <v>0.00485966875727104</v>
       </c>
-      <c r="AB7" s="121" t="n">
+      <c r="AB7" s="122" t="n">
         <v>0.00783866626495107</v>
       </c>
-      <c r="AC7" s="121" t="n">
+      <c r="AC7" s="122" t="n">
         <v>0.00426033797401145</v>
       </c>
-      <c r="AD7" s="121" t="n">
+      <c r="AD7" s="122" t="n">
         <v>0.00454473495174492</v>
       </c>
-      <c r="AE7" s="121" t="n">
+      <c r="AE7" s="122" t="n">
         <v>0.00502978574358138</v>
       </c>
-      <c r="AF7" s="121" t="n">
+      <c r="AF7" s="122" t="n">
         <v>0.00529810204229605</v>
       </c>
-      <c r="AG7" s="121" t="n">
+      <c r="AG7" s="122" t="n">
         <v>0.00950390148321116</v>
       </c>
-      <c r="AH7" s="121" t="n">
+      <c r="AH7" s="122" t="n">
         <v>0.0104376276125491</v>
       </c>
-      <c r="AI7" s="121" t="n">
+      <c r="AI7" s="122" t="n">
         <v>0.0114781985374176</v>
       </c>
-      <c r="AJ7" s="121" t="n">
+      <c r="AJ7" s="122" t="n">
         <v>0.00464245397504914</v>
       </c>
-      <c r="AK7" s="121" t="n">
+      <c r="AK7" s="122" t="n">
         <v>0.0102124261838036</v>
       </c>
-      <c r="AL7" s="121" t="n">
+      <c r="AL7" s="122" t="n">
         <v>0.00836614263519464</v>
       </c>
-      <c r="AM7" s="121" t="n">
+      <c r="AM7" s="122" t="n">
         <v>0.00641639146250544</v>
       </c>
-      <c r="AN7" s="121" t="n">
+      <c r="AN7" s="122" t="n">
         <v>0.0129590251824744</v>
       </c>
-      <c r="AO7" s="121" t="n">
+      <c r="AO7" s="122" t="n">
         <v>0.0105098457403686</v>
       </c>
-      <c r="AP7" s="121" t="n">
+      <c r="AP7" s="122" t="n">
         <v>0.0151765477647308</v>
       </c>
-      <c r="AQ7" s="121" t="n">
+      <c r="AQ7" s="122" t="n">
         <v>0.00996732837695936</v>
       </c>
-      <c r="AR7" s="121" t="n">
+      <c r="AR7" s="122" t="n">
         <v>0.0140103931275106</v>
       </c>
-      <c r="AS7" s="121" t="n">
+      <c r="AS7" s="122" t="n">
         <v>0.00508738848791</v>
       </c>
-      <c r="AT7" s="121" t="n">
+      <c r="AT7" s="122" t="n">
         <v>0.0120113142929916</v>
       </c>
-      <c r="AU7" s="121" t="n">
+      <c r="AU7" s="122" t="n">
         <v>0.0093444316219456</v>
       </c>
-      <c r="AV7" s="121" t="n">
+      <c r="AV7" s="122" t="n">
         <v>0.00747580897786016</v>
       </c>
-      <c r="AW7" s="121" t="n">
+      <c r="AW7" s="122" t="n">
         <v>0.0104449801810562</v>
       </c>
-      <c r="AX7" s="121" t="n">
+      <c r="AX7" s="122" t="n">
         <v>0.0124869270326455</v>
       </c>
-      <c r="AY7" s="121" t="n">
+      <c r="AY7" s="122" t="n">
         <v>0.00772416944682176</v>
       </c>
-      <c r="AZ7" s="121" t="n">
+      <c r="AZ7" s="122" t="n">
         <v>0.0181259444612758</v>
       </c>
-      <c r="BA7" s="121" t="n">
+      <c r="BA7" s="122" t="n">
         <v>0.00784813126476173</v>
       </c>
-      <c r="BB7" s="121" t="n">
+      <c r="BB7" s="122" t="n">
         <v>0.0192232934320082</v>
       </c>
-      <c r="BC7" s="121" t="n">
+      <c r="BC7" s="122" t="n">
         <v>0.0144048414255527</v>
       </c>
-      <c r="BD7" s="121" t="n">
+      <c r="BD7" s="122" t="n">
         <v>0.00872601107122916</v>
       </c>
-      <c r="BE7" s="121" t="n">
+      <c r="BE7" s="122" t="n">
         <v>0.00776704798697851</v>
       </c>
-      <c r="BF7" s="121" t="n">
+      <c r="BF7" s="122" t="n">
         <v>0.00640285932905952</v>
       </c>
-      <c r="BG7" s="120" t="n">
+      <c r="BG7" s="121" t="n">
         <v>0.00632540761131044</v>
       </c>
-      <c r="BH7" s="122" t="n">
+      <c r="BH7" s="123" t="n">
         <v>0.0207299950518688</v>
       </c>
-      <c r="BI7" s="122" t="n">
+      <c r="BI7" s="123" t="n">
         <v>0.0196014601148541</v>
       </c>
-      <c r="BJ7" s="122" t="n">
+      <c r="BJ7" s="123" t="n">
         <v>0.00811089896579215</v>
       </c>
-      <c r="BK7" s="122" t="n">
+      <c r="BK7" s="123" t="n">
         <v>0.00727949615105557</v>
       </c>
-      <c r="BL7" s="122" t="n">
+      <c r="BL7" s="123" t="n">
         <v>0.00762071555022352</v>
       </c>
-      <c r="BM7" s="122" t="n">
+      <c r="BM7" s="123" t="n">
         <v>0.0133366936498218</v>
       </c>
-      <c r="BN7" s="122" t="n">
+      <c r="BN7" s="123" t="n">
         <v>0.00778957695768113</v>
       </c>
-      <c r="BO7" s="122" t="n">
+      <c r="BO7" s="123" t="n">
         <v>0.0131836783261533</v>
       </c>
-      <c r="BP7" s="122" t="n">
+      <c r="BP7" s="123" t="n">
         <v>0.0131416538358973</v>
       </c>
-      <c r="BQ7" s="122" t="n">
+      <c r="BQ7" s="123" t="n">
         <v>0.00815481580201456</v>
       </c>
-      <c r="BR7" s="122" t="n">
+      <c r="BR7" s="123" t="n">
         <v>0.0273322060231484</v>
       </c>
-      <c r="BS7" s="122" t="n">
+      <c r="BS7" s="123" t="n">
         <v>0.0217681500762758</v>
       </c>
-      <c r="BT7" s="122" t="n">
+      <c r="BT7" s="123" t="n">
         <v>0.0136092207650628</v>
       </c>
-      <c r="BU7" s="122" t="n">
+      <c r="BU7" s="123" t="n">
         <v>0.00780635589831799</v>
       </c>
-      <c r="BV7" s="122" t="n">
+      <c r="BV7" s="123" t="n">
         <v>0.0117189023471066</v>
       </c>
-      <c r="BW7" s="122" t="n">
+      <c r="BW7" s="123" t="n">
         <v>0.0113687915190517</v>
       </c>
-      <c r="BX7" s="123" t="n">
+      <c r="BX7" s="124" t="n">
         <v>0.0226376729992035</v>
       </c>
-      <c r="BY7" s="124" t="n">
+      <c r="BY7" s="125" t="n">
         <v>0.0113290784448174</v>
       </c>
     </row>
-    <row r="8" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="119" t="s">
+    <row r="8" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="120" t="n">
+      <c r="B8" s="121" t="n">
         <v>0.0445729249938631</v>
       </c>
-      <c r="C8" s="120" t="n">
+      <c r="C8" s="121" t="n">
         <v>0.0478761449250691</v>
       </c>
-      <c r="D8" s="120" t="n">
+      <c r="D8" s="121" t="n">
         <v>0.0359931148386406</v>
       </c>
-      <c r="E8" s="120" t="n">
+      <c r="E8" s="121" t="n">
         <v>0.029446897521119</v>
       </c>
-      <c r="F8" s="120" t="n">
+      <c r="F8" s="121" t="n">
         <v>0.0436527740564915</v>
       </c>
-      <c r="G8" s="121" t="n">
+      <c r="G8" s="122" t="n">
         <v>0.0397285838089362</v>
       </c>
-      <c r="H8" s="121" t="n">
+      <c r="H8" s="122" t="n">
         <v>0.0328222998486693</v>
       </c>
-      <c r="I8" s="121" t="n">
+      <c r="I8" s="122" t="n">
         <v>0.0429452072555207</v>
       </c>
-      <c r="J8" s="121" t="n">
+      <c r="J8" s="122" t="n">
         <v>0.0333700188474048</v>
       </c>
-      <c r="K8" s="121" t="n">
+      <c r="K8" s="122" t="n">
         <v>0.034472397461667</v>
       </c>
-      <c r="L8" s="121" t="n">
+      <c r="L8" s="122" t="n">
         <v>0.0265990192954439</v>
       </c>
-      <c r="M8" s="121" t="n">
+      <c r="M8" s="122" t="n">
         <v>0.0274485916017495</v>
       </c>
-      <c r="N8" s="121" t="n">
+      <c r="N8" s="122" t="n">
         <v>0.0191201469121276</v>
       </c>
-      <c r="O8" s="121" t="n">
+      <c r="O8" s="122" t="n">
         <v>0.0179658702707586</v>
       </c>
-      <c r="P8" s="121" t="n">
+      <c r="P8" s="122" t="n">
         <v>0.0257844273848399</v>
       </c>
-      <c r="Q8" s="121" t="n">
+      <c r="Q8" s="122" t="n">
         <v>0.0238499425609296</v>
       </c>
-      <c r="R8" s="121" t="n">
+      <c r="R8" s="122" t="n">
         <v>0.0210925538813433</v>
       </c>
-      <c r="S8" s="121" t="n">
+      <c r="S8" s="122" t="n">
         <v>0.0180838440185572</v>
       </c>
-      <c r="T8" s="121" t="n">
+      <c r="T8" s="122" t="n">
         <v>0.0206797595860818</v>
       </c>
-      <c r="U8" s="121" t="n">
+      <c r="U8" s="122" t="n">
         <v>0.0249736627872142</v>
       </c>
-      <c r="V8" s="121" t="n">
+      <c r="V8" s="122" t="n">
         <v>0.0227074224293362</v>
       </c>
-      <c r="W8" s="121" t="n">
+      <c r="W8" s="122" t="n">
         <v>0.015396818088056</v>
       </c>
-      <c r="X8" s="121" t="n">
+      <c r="X8" s="122" t="n">
         <v>0.0191758492714609</v>
       </c>
-      <c r="Y8" s="121" t="n">
+      <c r="Y8" s="122" t="n">
         <v>0.0307356642952217</v>
       </c>
-      <c r="Z8" s="121" t="n">
+      <c r="Z8" s="122" t="n">
         <v>0.0211370250874685</v>
       </c>
-      <c r="AA8" s="121" t="n">
+      <c r="AA8" s="122" t="n">
         <v>0.017597233725694</v>
       </c>
-      <c r="AB8" s="121" t="n">
+      <c r="AB8" s="122" t="n">
         <v>0.0184626574630831</v>
       </c>
-      <c r="AC8" s="121" t="n">
+      <c r="AC8" s="122" t="n">
         <v>0.0224741424691255</v>
       </c>
-      <c r="AD8" s="121" t="n">
+      <c r="AD8" s="122" t="n">
         <v>0.0190802734575853</v>
       </c>
-      <c r="AE8" s="121" t="n">
+      <c r="AE8" s="122" t="n">
         <v>0.0174057122741892</v>
       </c>
-      <c r="AF8" s="121" t="n">
+      <c r="AF8" s="122" t="n">
         <v>0.0179162114589407</v>
       </c>
-      <c r="AG8" s="121" t="n">
+      <c r="AG8" s="122" t="n">
         <v>0.019274554874022</v>
       </c>
-      <c r="AH8" s="121" t="n">
+      <c r="AH8" s="122" t="n">
         <v>0.0169190128742118</v>
       </c>
-      <c r="AI8" s="121" t="n">
+      <c r="AI8" s="122" t="n">
         <v>0.0203477515591388</v>
       </c>
-      <c r="AJ8" s="121" t="n">
+      <c r="AJ8" s="122" t="n">
         <v>0.0127506694206738</v>
       </c>
-      <c r="AK8" s="121" t="n">
+      <c r="AK8" s="122" t="n">
         <v>0.0165011907043208</v>
       </c>
-      <c r="AL8" s="121" t="n">
+      <c r="AL8" s="122" t="n">
         <v>0.0302171503575906</v>
       </c>
-      <c r="AM8" s="121" t="n">
+      <c r="AM8" s="122" t="n">
         <v>0.00550601134880493</v>
       </c>
-      <c r="AN8" s="121" t="n">
+      <c r="AN8" s="122" t="n">
         <v>0.0204146525258332</v>
       </c>
-      <c r="AO8" s="121" t="n">
+      <c r="AO8" s="122" t="n">
         <v>0.0192828988318265</v>
       </c>
-      <c r="AP8" s="121" t="n">
+      <c r="AP8" s="122" t="n">
         <v>0.0065632979040199</v>
       </c>
-      <c r="AQ8" s="121" t="n">
+      <c r="AQ8" s="122" t="n">
         <v>0.0127484148343118</v>
       </c>
-      <c r="AR8" s="121" t="n">
+      <c r="AR8" s="122" t="n">
         <v>0.0282846437250798</v>
       </c>
-      <c r="AS8" s="121" t="n">
+      <c r="AS8" s="122" t="n">
         <v>0.0298286818827103</v>
       </c>
-      <c r="AT8" s="121" t="n">
+      <c r="AT8" s="122" t="n">
         <v>0.0217384088307714</v>
       </c>
-      <c r="AU8" s="121" t="n">
+      <c r="AU8" s="122" t="n">
         <v>0.0232186413481381</v>
       </c>
-      <c r="AV8" s="121" t="n">
+      <c r="AV8" s="122" t="n">
         <v>0.0250724857122145</v>
       </c>
-      <c r="AW8" s="121" t="n">
+      <c r="AW8" s="122" t="n">
         <v>0.0265436103098116</v>
       </c>
-      <c r="AX8" s="121" t="n">
+      <c r="AX8" s="122" t="n">
         <v>0.030383726539696</v>
       </c>
-      <c r="AY8" s="121" t="n">
+      <c r="AY8" s="122" t="n">
         <v>0.0295434962542568</v>
       </c>
-      <c r="AZ8" s="121" t="n">
+      <c r="AZ8" s="122" t="n">
         <v>0.0240437283851461</v>
       </c>
-      <c r="BA8" s="121" t="n">
+      <c r="BA8" s="122" t="n">
         <v>0.00689965864997404</v>
       </c>
-      <c r="BB8" s="121" t="n">
+      <c r="BB8" s="122" t="n">
         <v>0.0143386285597667</v>
       </c>
-      <c r="BC8" s="121" t="n">
+      <c r="BC8" s="122" t="n">
         <v>0.0177582362968416</v>
       </c>
-      <c r="BD8" s="121" t="n">
+      <c r="BD8" s="122" t="n">
         <v>0.0289695118515809</v>
       </c>
-      <c r="BE8" s="121" t="n">
+      <c r="BE8" s="122" t="n">
         <v>0.0194757890079964</v>
       </c>
-      <c r="BF8" s="121" t="n">
+      <c r="BF8" s="122" t="n">
         <v>0.027249927357765</v>
       </c>
-      <c r="BG8" s="120" t="n">
+      <c r="BG8" s="121" t="n">
         <v>0.0217480986653104</v>
       </c>
-      <c r="BH8" s="122" t="n">
+      <c r="BH8" s="123" t="n">
         <v>0.0197201938625887</v>
       </c>
-      <c r="BI8" s="122" t="n">
+      <c r="BI8" s="123" t="n">
         <v>0.0308565584674777</v>
       </c>
-      <c r="BJ8" s="122" t="n">
+      <c r="BJ8" s="123" t="n">
         <v>0.0179993553510136</v>
       </c>
-      <c r="BK8" s="122" t="n">
+      <c r="BK8" s="123" t="n">
         <v>0.0216226250969507</v>
       </c>
-      <c r="BL8" s="122" t="n">
+      <c r="BL8" s="123" t="n">
         <v>0.0279109234580925</v>
       </c>
-      <c r="BM8" s="122" t="n">
+      <c r="BM8" s="123" t="n">
         <v>0.0359259550375714</v>
       </c>
-      <c r="BN8" s="122" t="n">
+      <c r="BN8" s="123" t="n">
         <v>0.0265517707574238</v>
       </c>
-      <c r="BO8" s="122" t="n">
+      <c r="BO8" s="123" t="n">
         <v>0.0313222864523474</v>
       </c>
-      <c r="BP8" s="122" t="n">
+      <c r="BP8" s="123" t="n">
         <v>0.0269431217550042</v>
       </c>
-      <c r="BQ8" s="122" t="n">
+      <c r="BQ8" s="123" t="n">
         <v>0.0350471966634788</v>
       </c>
-      <c r="BR8" s="122" t="n">
+      <c r="BR8" s="123" t="n">
         <v>0.0302418843447855</v>
       </c>
-      <c r="BS8" s="122" t="n">
+      <c r="BS8" s="123" t="n">
         <v>0.0160083293185968</v>
       </c>
-      <c r="BT8" s="122" t="n">
+      <c r="BT8" s="123" t="n">
         <v>0.0259792395870475</v>
       </c>
-      <c r="BU8" s="122" t="n">
+      <c r="BU8" s="123" t="n">
         <v>0.0332440079089635</v>
       </c>
-      <c r="BV8" s="122" t="n">
+      <c r="BV8" s="123" t="n">
         <v>0.0193299559603526</v>
       </c>
-      <c r="BW8" s="122" t="n">
+      <c r="BW8" s="123" t="n">
         <v>0.0255938410215721</v>
       </c>
-      <c r="BX8" s="123" t="n">
+      <c r="BX8" s="124" t="n">
         <v>0.029215550082344</v>
       </c>
-      <c r="BY8" s="124" t="n">
+      <c r="BY8" s="125" t="n">
         <v>0.0267526452666448</v>
       </c>
     </row>
-    <row r="9" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="119" t="s">
+    <row r="9" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="120" t="n">
+      <c r="B9" s="121" t="n">
         <v>0.0591883677711369</v>
       </c>
-      <c r="C9" s="120" t="n">
+      <c r="C9" s="121" t="n">
         <v>0.0556794707560318</v>
       </c>
-      <c r="D9" s="120" t="n">
+      <c r="D9" s="121" t="n">
         <v>0.0540154748949561</v>
       </c>
-      <c r="E9" s="120" t="n">
+      <c r="E9" s="121" t="n">
         <v>0.049626651548081</v>
       </c>
-      <c r="F9" s="120" t="n">
+      <c r="F9" s="121" t="n">
         <v>0.0541769422355108</v>
       </c>
-      <c r="G9" s="121" t="n">
+      <c r="G9" s="122" t="n">
         <v>0.052305593457609</v>
       </c>
-      <c r="H9" s="121" t="n">
+      <c r="H9" s="122" t="n">
         <v>0.0491273021070286</v>
       </c>
-      <c r="I9" s="121" t="n">
+      <c r="I9" s="122" t="n">
         <v>0.0460466529113654</v>
       </c>
-      <c r="J9" s="121" t="n">
+      <c r="J9" s="122" t="n">
         <v>0.0439285868144132</v>
       </c>
-      <c r="K9" s="121" t="n">
+      <c r="K9" s="122" t="n">
         <v>0.0482520097001874</v>
       </c>
-      <c r="L9" s="121" t="n">
+      <c r="L9" s="122" t="n">
         <v>0.0339365238916964</v>
       </c>
-      <c r="M9" s="121" t="n">
+      <c r="M9" s="122" t="n">
         <v>0.0341796461395188</v>
       </c>
-      <c r="N9" s="121" t="n">
+      <c r="N9" s="122" t="n">
         <v>0.0333369932279941</v>
       </c>
-      <c r="O9" s="121" t="n">
+      <c r="O9" s="122" t="n">
         <v>0.033104253862992</v>
       </c>
-      <c r="P9" s="121" t="n">
+      <c r="P9" s="122" t="n">
         <v>0.0363145965003417</v>
       </c>
-      <c r="Q9" s="121" t="n">
+      <c r="Q9" s="122" t="n">
         <v>0.0339689006619918</v>
       </c>
-      <c r="R9" s="121" t="n">
+      <c r="R9" s="122" t="n">
         <v>0.0301258470670308</v>
       </c>
-      <c r="S9" s="121" t="n">
+      <c r="S9" s="122" t="n">
         <v>0.0297323336671486</v>
       </c>
-      <c r="T9" s="121" t="n">
+      <c r="T9" s="122" t="n">
         <v>0.0275261817943028</v>
       </c>
-      <c r="U9" s="121" t="n">
+      <c r="U9" s="122" t="n">
         <v>0.0362459677504646</v>
       </c>
-      <c r="V9" s="121" t="n">
+      <c r="V9" s="122" t="n">
         <v>0.0360035947179536</v>
       </c>
-      <c r="W9" s="121" t="n">
+      <c r="W9" s="122" t="n">
         <v>0.0320207467413321</v>
       </c>
-      <c r="X9" s="121" t="n">
+      <c r="X9" s="122" t="n">
         <v>0.0321891641723492</v>
       </c>
-      <c r="Y9" s="121" t="n">
+      <c r="Y9" s="122" t="n">
         <v>0.0293059674003303</v>
       </c>
-      <c r="Z9" s="121" t="n">
+      <c r="Z9" s="122" t="n">
         <v>0.0355838992680867</v>
       </c>
-      <c r="AA9" s="121" t="n">
+      <c r="AA9" s="122" t="n">
         <v>0.028502049524473</v>
       </c>
-      <c r="AB9" s="121" t="n">
+      <c r="AB9" s="122" t="n">
         <v>0.0368628518536787</v>
       </c>
-      <c r="AC9" s="121" t="n">
+      <c r="AC9" s="122" t="n">
         <v>0.0299499398249841</v>
       </c>
-      <c r="AD9" s="121" t="n">
+      <c r="AD9" s="122" t="n">
         <v>0.0293683080499306</v>
       </c>
-      <c r="AE9" s="121" t="n">
+      <c r="AE9" s="122" t="n">
         <v>0.0346019872797281</v>
       </c>
-      <c r="AF9" s="121" t="n">
+      <c r="AF9" s="122" t="n">
         <v>0.028774126359826</v>
       </c>
-      <c r="AG9" s="121" t="n">
+      <c r="AG9" s="122" t="n">
         <v>0.0274562092743146</v>
       </c>
-      <c r="AH9" s="121" t="n">
+      <c r="AH9" s="122" t="n">
         <v>0.0350493091031689</v>
       </c>
-      <c r="AI9" s="121" t="n">
+      <c r="AI9" s="122" t="n">
         <v>0.0299478970491942</v>
       </c>
-      <c r="AJ9" s="121" t="n">
+      <c r="AJ9" s="122" t="n">
         <v>0.0307038066495238</v>
       </c>
-      <c r="AK9" s="121" t="n">
+      <c r="AK9" s="122" t="n">
         <v>0.0342305539826199</v>
       </c>
-      <c r="AL9" s="121" t="n">
+      <c r="AL9" s="122" t="n">
         <v>0.0356864819771844</v>
       </c>
-      <c r="AM9" s="121" t="n">
+      <c r="AM9" s="122" t="n">
         <v>0.0360141308851991</v>
       </c>
-      <c r="AN9" s="121" t="n">
+      <c r="AN9" s="122" t="n">
         <v>0.034373406004737</v>
       </c>
-      <c r="AO9" s="121" t="n">
+      <c r="AO9" s="122" t="n">
         <v>0.0379665895978882</v>
       </c>
-      <c r="AP9" s="121" t="n">
+      <c r="AP9" s="122" t="n">
         <v>0.0371005281744225</v>
       </c>
-      <c r="AQ9" s="121" t="n">
+      <c r="AQ9" s="122" t="n">
         <v>0.0366621704118585</v>
       </c>
-      <c r="AR9" s="121" t="n">
+      <c r="AR9" s="122" t="n">
         <v>0.0404247437928717</v>
       </c>
-      <c r="AS9" s="121" t="n">
+      <c r="AS9" s="122" t="n">
         <v>0.0367808116553229</v>
       </c>
-      <c r="AT9" s="121" t="n">
+      <c r="AT9" s="122" t="n">
         <v>0.0343615114222901</v>
       </c>
-      <c r="AU9" s="121" t="n">
+      <c r="AU9" s="122" t="n">
         <v>0.033575618667359</v>
       </c>
-      <c r="AV9" s="121" t="n">
+      <c r="AV9" s="122" t="n">
         <v>0.0392234835405737</v>
       </c>
-      <c r="AW9" s="121" t="n">
+      <c r="AW9" s="122" t="n">
         <v>0.039851452649931</v>
       </c>
-      <c r="AX9" s="121" t="n">
+      <c r="AX9" s="122" t="n">
         <v>0.0389356803064214</v>
       </c>
-      <c r="AY9" s="121" t="n">
+      <c r="AY9" s="122" t="n">
         <v>0.0393992388364316</v>
       </c>
-      <c r="AZ9" s="121" t="n">
+      <c r="AZ9" s="122" t="n">
         <v>0.0385190367197624</v>
       </c>
-      <c r="BA9" s="121" t="n">
+      <c r="BA9" s="122" t="n">
         <v>0.0384434626425634</v>
       </c>
-      <c r="BB9" s="121" t="n">
+      <c r="BB9" s="122" t="n">
         <v>0.0422606139326762</v>
       </c>
-      <c r="BC9" s="121" t="n">
+      <c r="BC9" s="122" t="n">
         <v>0.0389482310889574</v>
       </c>
-      <c r="BD9" s="121" t="n">
+      <c r="BD9" s="122" t="n">
         <v>0.038656177418982</v>
       </c>
-      <c r="BE9" s="121" t="n">
+      <c r="BE9" s="122" t="n">
         <v>0.0484156609715361</v>
       </c>
-      <c r="BF9" s="121" t="n">
+      <c r="BF9" s="122" t="n">
         <v>0.0352514340756067</v>
       </c>
-      <c r="BG9" s="120" t="n">
+      <c r="BG9" s="121" t="n">
         <v>0.0430216815902</v>
       </c>
-      <c r="BH9" s="122" t="n">
+      <c r="BH9" s="123" t="n">
         <v>0.0627141337372695</v>
       </c>
-      <c r="BI9" s="122" t="n">
+      <c r="BI9" s="123" t="n">
         <v>0.0472140657982367</v>
       </c>
-      <c r="BJ9" s="122" t="n">
+      <c r="BJ9" s="123" t="n">
         <v>0.0503063329478655</v>
       </c>
-      <c r="BK9" s="122" t="n">
+      <c r="BK9" s="123" t="n">
         <v>0.0538396759778791</v>
       </c>
-      <c r="BL9" s="122" t="n">
+      <c r="BL9" s="123" t="n">
         <v>0.0468126534246428</v>
       </c>
-      <c r="BM9" s="122" t="n">
+      <c r="BM9" s="123" t="n">
         <v>0.049017453037052</v>
       </c>
-      <c r="BN9" s="122" t="n">
+      <c r="BN9" s="123" t="n">
         <v>0.044282184937462</v>
       </c>
-      <c r="BO9" s="122" t="n">
+      <c r="BO9" s="123" t="n">
         <v>0.0479105634079454</v>
       </c>
-      <c r="BP9" s="122" t="n">
+      <c r="BP9" s="123" t="n">
         <v>0.0432583297972201</v>
       </c>
-      <c r="BQ9" s="122" t="n">
+      <c r="BQ9" s="123" t="n">
         <v>0.0541024927623053</v>
       </c>
-      <c r="BR9" s="122" t="n">
+      <c r="BR9" s="123" t="n">
         <v>0.0414340969348731</v>
       </c>
-      <c r="BS9" s="122" t="n">
+      <c r="BS9" s="123" t="n">
         <v>0.044343176213721</v>
       </c>
-      <c r="BT9" s="122" t="n">
+      <c r="BT9" s="123" t="n">
         <v>0.0411639616256657</v>
       </c>
-      <c r="BU9" s="122" t="n">
+      <c r="BU9" s="123" t="n">
         <v>0.0537259342763565</v>
       </c>
-      <c r="BV9" s="122" t="n">
+      <c r="BV9" s="123" t="n">
         <v>0.0410649350304046</v>
       </c>
-      <c r="BW9" s="122" t="n">
+      <c r="BW9" s="123" t="n">
         <v>0.0582310993424966</v>
       </c>
-      <c r="BX9" s="123" t="n">
+      <c r="BX9" s="124" t="n">
         <v>0.0425180538289166</v>
       </c>
-      <c r="BY9" s="124" t="n">
+      <c r="BY9" s="125" t="n">
         <v>0.0437492721939487</v>
       </c>
     </row>
-    <row r="10" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="119" t="s">
+    <row r="10" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="120" t="n">
+      <c r="B10" s="121" t="n">
         <v>0.0582788690255497</v>
       </c>
-      <c r="C10" s="120" t="n">
+      <c r="C10" s="121" t="n">
         <v>0.0476688735227193</v>
       </c>
-      <c r="D10" s="120" t="n">
+      <c r="D10" s="121" t="n">
         <v>0.0585809560568022</v>
       </c>
-      <c r="E10" s="120" t="n">
+      <c r="E10" s="121" t="n">
         <v>0.0542550604463286</v>
       </c>
-      <c r="F10" s="120" t="n">
+      <c r="F10" s="121" t="n">
         <v>0.0478021197233782</v>
       </c>
-      <c r="G10" s="121" t="n">
+      <c r="G10" s="122" t="n">
         <v>0.0376201273758972</v>
       </c>
-      <c r="H10" s="121" t="n">
+      <c r="H10" s="122" t="n">
         <v>0.0147765638245639</v>
       </c>
-      <c r="I10" s="121" t="n">
+      <c r="I10" s="122" t="n">
         <v>0.0360417669004346</v>
       </c>
-      <c r="J10" s="121" t="n">
+      <c r="J10" s="122" t="n">
         <v>0.0336352982604413</v>
       </c>
-      <c r="K10" s="121" t="n">
+      <c r="K10" s="122" t="n">
         <v>0.0116412622980357</v>
       </c>
-      <c r="L10" s="121" t="n">
+      <c r="L10" s="122" t="n">
         <v>0.0078432863947735</v>
       </c>
-      <c r="M10" s="121" t="n">
+      <c r="M10" s="122" t="n">
         <v>0.0429293685797437</v>
       </c>
-      <c r="N10" s="121" t="n">
+      <c r="N10" s="122" t="n">
         <v>0.0305968074852454</v>
       </c>
-      <c r="O10" s="121" t="n">
+      <c r="O10" s="122" t="n">
         <v>0.0470159487341764</v>
       </c>
-      <c r="P10" s="121" t="n">
+      <c r="P10" s="122" t="n">
         <v>0.0328498608120105</v>
       </c>
-      <c r="Q10" s="121" t="n">
+      <c r="Q10" s="122" t="n">
         <v>0.0403603234780499</v>
       </c>
-      <c r="R10" s="121" t="n">
+      <c r="R10" s="122" t="n">
         <v>0.0121158472583054</v>
       </c>
-      <c r="S10" s="121" t="n">
+      <c r="S10" s="122" t="n">
         <v>0.0111925364622175</v>
       </c>
-      <c r="T10" s="121" t="n">
+      <c r="T10" s="122" t="n">
         <v>0.0196607409314799</v>
       </c>
-      <c r="U10" s="121" t="n">
+      <c r="U10" s="122" t="n">
         <v>0.0122202344720197</v>
       </c>
-      <c r="V10" s="121" t="n">
+      <c r="V10" s="122" t="n">
         <v>0.0125927543816053</v>
       </c>
-      <c r="W10" s="121" t="n">
+      <c r="W10" s="122" t="n">
         <v>0.0216299007309465</v>
       </c>
-      <c r="X10" s="121" t="n">
+      <c r="X10" s="122" t="n">
         <v>0.0267795273806731</v>
       </c>
-      <c r="Y10" s="121" t="n">
+      <c r="Y10" s="122" t="n">
         <v>0.0170805772933676</v>
       </c>
-      <c r="Z10" s="121" t="n">
+      <c r="Z10" s="122" t="n">
         <v>0.0352891212541193</v>
       </c>
-      <c r="AA10" s="121" t="n">
+      <c r="AA10" s="122" t="n">
         <v>0.0351197473228121</v>
       </c>
-      <c r="AB10" s="121" t="n">
+      <c r="AB10" s="122" t="n">
         <v>0.0358129305333127</v>
       </c>
-      <c r="AC10" s="121" t="n">
+      <c r="AC10" s="122" t="n">
         <v>0.014134724934619</v>
       </c>
-      <c r="AD10" s="121" t="n">
+      <c r="AD10" s="122" t="n">
         <v>0.027231693800052</v>
       </c>
-      <c r="AE10" s="121" t="n">
+      <c r="AE10" s="122" t="n">
         <v>0.0101319945837448</v>
       </c>
-      <c r="AF10" s="121" t="n">
+      <c r="AF10" s="122" t="n">
         <v>0.0202139852128751</v>
       </c>
-      <c r="AG10" s="121" t="n">
+      <c r="AG10" s="122" t="n">
         <v>0.0210479766468327</v>
       </c>
-      <c r="AH10" s="121" t="n">
+      <c r="AH10" s="122" t="n">
         <v>0.00995939031436998</v>
       </c>
-      <c r="AI10" s="121" t="n">
+      <c r="AI10" s="122" t="n">
         <v>0.0107235024724817</v>
       </c>
-      <c r="AJ10" s="121" t="n">
+      <c r="AJ10" s="122" t="n">
         <v>0.00602747570405167</v>
       </c>
-      <c r="AK10" s="121" t="n">
+      <c r="AK10" s="122" t="n">
         <v>0.0337195098561021</v>
       </c>
-      <c r="AL10" s="121" t="n">
+      <c r="AL10" s="122" t="n">
         <v>0.0349405005363635</v>
       </c>
-      <c r="AM10" s="121" t="n">
+      <c r="AM10" s="122" t="n">
         <v>0.0333345059318486</v>
       </c>
-      <c r="AN10" s="121" t="n">
+      <c r="AN10" s="122" t="n">
         <v>0.0395404199171369</v>
       </c>
-      <c r="AO10" s="121" t="n">
+      <c r="AO10" s="122" t="n">
         <v>0.0220356281824907</v>
       </c>
-      <c r="AP10" s="121" t="n">
+      <c r="AP10" s="122" t="n">
         <v>0.0141443427019187</v>
       </c>
-      <c r="AQ10" s="121" t="n">
+      <c r="AQ10" s="122" t="n">
         <v>0.0359296487685514</v>
       </c>
-      <c r="AR10" s="121" t="n">
+      <c r="AR10" s="122" t="n">
         <v>0.00860087747134861</v>
       </c>
-      <c r="AS10" s="121" t="n">
+      <c r="AS10" s="122" t="n">
         <v>0.0128551069450542</v>
       </c>
-      <c r="AT10" s="121" t="n">
+      <c r="AT10" s="122" t="n">
         <v>0.0342150481886571</v>
       </c>
-      <c r="AU10" s="121" t="n">
+      <c r="AU10" s="122" t="n">
         <v>0.0188109540217701</v>
       </c>
-      <c r="AV10" s="121" t="n">
+      <c r="AV10" s="122" t="n">
         <v>0.0356065972436814</v>
       </c>
-      <c r="AW10" s="121" t="n">
+      <c r="AW10" s="122" t="n">
         <v>0.0446174650687081</v>
       </c>
-      <c r="AX10" s="121" t="n">
+      <c r="AX10" s="122" t="n">
         <v>0.0199705502020759</v>
       </c>
-      <c r="AY10" s="121" t="n">
+      <c r="AY10" s="122" t="n">
         <v>0.0263477233018017</v>
       </c>
-      <c r="AZ10" s="121" t="n">
+      <c r="AZ10" s="122" t="n">
         <v>0.0169627990134966</v>
       </c>
-      <c r="BA10" s="121" t="n">
+      <c r="BA10" s="122" t="n">
         <v>0.0169407770049703</v>
       </c>
-      <c r="BB10" s="121" t="n">
+      <c r="BB10" s="122" t="n">
         <v>0.0257376585669234</v>
       </c>
-      <c r="BC10" s="121" t="n">
+      <c r="BC10" s="122" t="n">
         <v>0.014690377422731</v>
       </c>
-      <c r="BD10" s="121" t="n">
+      <c r="BD10" s="122" t="n">
         <v>0.0139814910464274</v>
       </c>
-      <c r="BE10" s="121" t="n">
+      <c r="BE10" s="122" t="n">
         <v>0.0169038681755705</v>
       </c>
-      <c r="BF10" s="121" t="n">
+      <c r="BF10" s="122" t="n">
         <v>0.0140925353466491</v>
       </c>
-      <c r="BG10" s="120" t="n">
+      <c r="BG10" s="121" t="n">
         <v>0.0145457872793642</v>
       </c>
-      <c r="BH10" s="122" t="n">
+      <c r="BH10" s="123" t="n">
         <v>0.0083749618565592</v>
       </c>
-      <c r="BI10" s="122" t="n">
+      <c r="BI10" s="123" t="n">
         <v>0.0230168805481254</v>
       </c>
-      <c r="BJ10" s="122" t="n">
+      <c r="BJ10" s="123" t="n">
         <v>0.0165646859683249</v>
       </c>
-      <c r="BK10" s="122" t="n">
+      <c r="BK10" s="123" t="n">
         <v>0.0408141570180588</v>
       </c>
-      <c r="BL10" s="122" t="n">
+      <c r="BL10" s="123" t="n">
         <v>0.0248239148036963</v>
       </c>
-      <c r="BM10" s="122" t="n">
+      <c r="BM10" s="123" t="n">
         <v>0.045007353349066</v>
       </c>
-      <c r="BN10" s="122" t="n">
+      <c r="BN10" s="123" t="n">
         <v>0.00952731237117783</v>
       </c>
-      <c r="BO10" s="122" t="n">
+      <c r="BO10" s="123" t="n">
         <v>0.0281092700672904</v>
       </c>
-      <c r="BP10" s="122" t="n">
+      <c r="BP10" s="123" t="n">
         <v>0.0344172965751356</v>
       </c>
-      <c r="BQ10" s="122" t="n">
+      <c r="BQ10" s="123" t="n">
         <v>0.0283818447275103</v>
       </c>
-      <c r="BR10" s="122" t="n">
+      <c r="BR10" s="123" t="n">
         <v>0.0170558256940455</v>
       </c>
-      <c r="BS10" s="122" t="n">
+      <c r="BS10" s="123" t="n">
         <v>0.0280841227070609</v>
       </c>
-      <c r="BT10" s="122" t="n">
+      <c r="BT10" s="123" t="n">
         <v>0.0295874973098469</v>
       </c>
-      <c r="BU10" s="122" t="n">
+      <c r="BU10" s="123" t="n">
         <v>0.0293737079181134</v>
       </c>
-      <c r="BV10" s="122" t="n">
+      <c r="BV10" s="123" t="n">
         <v>0.0346550848597038</v>
       </c>
-      <c r="BW10" s="122" t="n">
+      <c r="BW10" s="123" t="n">
         <v>0.0536241355753926</v>
       </c>
-      <c r="BX10" s="123" t="n">
+      <c r="BX10" s="124" t="n">
         <v>0.0493119199673535</v>
       </c>
-      <c r="BY10" s="124" t="n">
+      <c r="BY10" s="125" t="n">
         <v>0.0396232251679154</v>
       </c>
     </row>
-    <row r="11" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="119" t="s">
+    <row r="11" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="120" t="n">
+      <c r="B11" s="121" t="n">
         <v>0.0606178969875688</v>
       </c>
-      <c r="C11" s="120" t="n">
+      <c r="C11" s="121" t="n">
         <v>0.0650706828718658</v>
       </c>
-      <c r="D11" s="120" t="n">
+      <c r="D11" s="121" t="n">
         <v>0.0656125146092075</v>
       </c>
-      <c r="E11" s="120" t="n">
+      <c r="E11" s="121" t="n">
         <v>0.0597955709435214</v>
       </c>
-      <c r="F11" s="120" t="n">
+      <c r="F11" s="121" t="n">
         <v>0.0546060287312871</v>
       </c>
-      <c r="G11" s="121" t="n">
+      <c r="G11" s="122" t="n">
         <v>0.0558336710023767</v>
       </c>
-      <c r="H11" s="121" t="n">
+      <c r="H11" s="122" t="n">
         <v>0.0582125241350434</v>
       </c>
-      <c r="I11" s="121" t="n">
+      <c r="I11" s="122" t="n">
         <v>0.0548954595083543</v>
       </c>
-      <c r="J11" s="121" t="n">
+      <c r="J11" s="122" t="n">
         <v>0.0360806920914634</v>
       </c>
-      <c r="K11" s="121" t="n">
+      <c r="K11" s="122" t="n">
         <v>0.0481871583563139</v>
       </c>
-      <c r="L11" s="121" t="n">
+      <c r="L11" s="122" t="n">
         <v>0.0464094567951124</v>
       </c>
-      <c r="M11" s="121" t="n">
+      <c r="M11" s="122" t="n">
         <v>0.0443132834564359</v>
       </c>
-      <c r="N11" s="121" t="n">
+      <c r="N11" s="122" t="n">
         <v>0.0436826702561705</v>
       </c>
-      <c r="O11" s="121" t="n">
+      <c r="O11" s="122" t="n">
         <v>0.0445975344283388</v>
       </c>
-      <c r="P11" s="121" t="n">
+      <c r="P11" s="122" t="n">
         <v>0.0452695287985679</v>
       </c>
-      <c r="Q11" s="121" t="n">
+      <c r="Q11" s="122" t="n">
         <v>0.0337365986658443</v>
       </c>
-      <c r="R11" s="121" t="n">
+      <c r="R11" s="122" t="n">
         <v>0.0405115025202897</v>
       </c>
-      <c r="S11" s="121" t="n">
+      <c r="S11" s="122" t="n">
         <v>0.0314203676493861</v>
       </c>
-      <c r="T11" s="121" t="n">
+      <c r="T11" s="122" t="n">
         <v>0.0447442365840318</v>
       </c>
-      <c r="U11" s="121" t="n">
+      <c r="U11" s="122" t="n">
         <v>0.0407082357609404</v>
       </c>
-      <c r="V11" s="121" t="n">
+      <c r="V11" s="122" t="n">
         <v>0.0409763179015282</v>
       </c>
-      <c r="W11" s="121" t="n">
+      <c r="W11" s="122" t="n">
         <v>0.0408858517393405</v>
       </c>
-      <c r="X11" s="121" t="n">
+      <c r="X11" s="122" t="n">
         <v>0.0433498868346552</v>
       </c>
-      <c r="Y11" s="121" t="n">
+      <c r="Y11" s="122" t="n">
         <v>0.0409388918802027</v>
       </c>
-      <c r="Z11" s="121" t="n">
+      <c r="Z11" s="122" t="n">
         <v>0.0439139831522486</v>
       </c>
-      <c r="AA11" s="121" t="n">
+      <c r="AA11" s="122" t="n">
         <v>0.0446818451569704</v>
       </c>
-      <c r="AB11" s="121" t="n">
+      <c r="AB11" s="122" t="n">
         <v>0.0455691959133646</v>
       </c>
-      <c r="AC11" s="121" t="n">
+      <c r="AC11" s="122" t="n">
         <v>0.0409332507808344</v>
       </c>
-      <c r="AD11" s="121" t="n">
+      <c r="AD11" s="122" t="n">
         <v>0.0391644221672273</v>
       </c>
-      <c r="AE11" s="121" t="n">
+      <c r="AE11" s="122" t="n">
         <v>0.0316329137131763</v>
       </c>
-      <c r="AF11" s="121" t="n">
+      <c r="AF11" s="122" t="n">
         <v>0.0456611709626325</v>
       </c>
-      <c r="AG11" s="121" t="n">
+      <c r="AG11" s="122" t="n">
         <v>0.0460193317141679</v>
       </c>
-      <c r="AH11" s="121" t="n">
+      <c r="AH11" s="122" t="n">
         <v>0.0423597118204074</v>
       </c>
-      <c r="AI11" s="121" t="n">
+      <c r="AI11" s="122" t="n">
         <v>0.0484291943209636</v>
       </c>
-      <c r="AJ11" s="121" t="n">
+      <c r="AJ11" s="122" t="n">
         <v>0.0417618022350472</v>
       </c>
-      <c r="AK11" s="121" t="n">
+      <c r="AK11" s="122" t="n">
         <v>0.049659297198301</v>
       </c>
-      <c r="AL11" s="121" t="n">
+      <c r="AL11" s="122" t="n">
         <v>0.0431121957090279</v>
       </c>
-      <c r="AM11" s="121" t="n">
+      <c r="AM11" s="122" t="n">
         <v>0.0489243756429371</v>
       </c>
-      <c r="AN11" s="121" t="n">
+      <c r="AN11" s="122" t="n">
         <v>0.0498125714707222</v>
       </c>
-      <c r="AO11" s="121" t="n">
+      <c r="AO11" s="122" t="n">
         <v>0.0454620107178115</v>
       </c>
-      <c r="AP11" s="121" t="n">
+      <c r="AP11" s="122" t="n">
         <v>0.0445294520498995</v>
       </c>
-      <c r="AQ11" s="121" t="n">
+      <c r="AQ11" s="122" t="n">
         <v>0.0469356118606684</v>
       </c>
-      <c r="AR11" s="121" t="n">
+      <c r="AR11" s="122" t="n">
         <v>0.0476264133286502</v>
       </c>
-      <c r="AS11" s="121" t="n">
+      <c r="AS11" s="122" t="n">
         <v>0.0528926980419681</v>
       </c>
-      <c r="AT11" s="121" t="n">
+      <c r="AT11" s="122" t="n">
         <v>0.0531567921858559</v>
       </c>
-      <c r="AU11" s="121" t="n">
+      <c r="AU11" s="122" t="n">
         <v>0.0550535627526163</v>
       </c>
-      <c r="AV11" s="121" t="n">
+      <c r="AV11" s="122" t="n">
         <v>0.0580628977065093</v>
       </c>
-      <c r="AW11" s="121" t="n">
+      <c r="AW11" s="122" t="n">
         <v>0.0648025058516946</v>
       </c>
-      <c r="AX11" s="121" t="n">
+      <c r="AX11" s="122" t="n">
         <v>0.0563689436399141</v>
       </c>
-      <c r="AY11" s="121" t="n">
+      <c r="AY11" s="122" t="n">
         <v>0.0523341740933814</v>
       </c>
-      <c r="AZ11" s="121" t="n">
+      <c r="AZ11" s="122" t="n">
         <v>0.0479799196668166</v>
       </c>
-      <c r="BA11" s="121" t="n">
+      <c r="BA11" s="122" t="n">
         <v>0.0470897099721165</v>
       </c>
-      <c r="BB11" s="121" t="n">
+      <c r="BB11" s="122" t="n">
         <v>0.0469514847032237</v>
       </c>
-      <c r="BC11" s="121" t="n">
+      <c r="BC11" s="122" t="n">
         <v>0.047053034984763</v>
       </c>
-      <c r="BD11" s="121" t="n">
+      <c r="BD11" s="122" t="n">
         <v>0.0585377186379417</v>
       </c>
-      <c r="BE11" s="121" t="n">
+      <c r="BE11" s="122" t="n">
         <v>0.0537226988210662</v>
       </c>
-      <c r="BF11" s="121" t="n">
+      <c r="BF11" s="122" t="n">
         <v>0.0518464760224288</v>
       </c>
-      <c r="BG11" s="120" t="n">
+      <c r="BG11" s="121" t="n">
         <v>0.0571135473377912</v>
       </c>
-      <c r="BH11" s="122" t="n">
+      <c r="BH11" s="123" t="n">
         <v>0.059185080543838</v>
       </c>
-      <c r="BI11" s="122" t="n">
+      <c r="BI11" s="123" t="n">
         <v>0.0629136002015497</v>
       </c>
-      <c r="BJ11" s="122" t="n">
+      <c r="BJ11" s="123" t="n">
         <v>0.0556931321724189</v>
       </c>
-      <c r="BK11" s="122" t="n">
+      <c r="BK11" s="123" t="n">
         <v>0.0568705158081544</v>
       </c>
-      <c r="BL11" s="122" t="n">
+      <c r="BL11" s="123" t="n">
         <v>0.0510940042906657</v>
       </c>
-      <c r="BM11" s="122" t="n">
+      <c r="BM11" s="123" t="n">
         <v>0.0529570975486639</v>
       </c>
-      <c r="BN11" s="122" t="n">
+      <c r="BN11" s="123" t="n">
         <v>0.057409377319068</v>
       </c>
-      <c r="BO11" s="122" t="n">
+      <c r="BO11" s="123" t="n">
         <v>0.0526916578325452</v>
       </c>
-      <c r="BP11" s="122" t="n">
+      <c r="BP11" s="123" t="n">
         <v>0.0620921361624829</v>
       </c>
-      <c r="BQ11" s="122" t="n">
+      <c r="BQ11" s="123" t="n">
         <v>0.0587016910714513</v>
       </c>
-      <c r="BR11" s="122" t="n">
+      <c r="BR11" s="123" t="n">
         <v>0.0564666959628224</v>
       </c>
-      <c r="BS11" s="122" t="n">
+      <c r="BS11" s="123" t="n">
         <v>0.0521081368426304</v>
       </c>
-      <c r="BT11" s="122" t="n">
+      <c r="BT11" s="123" t="n">
         <v>0.0489410150793559</v>
       </c>
-      <c r="BU11" s="122" t="n">
+      <c r="BU11" s="123" t="n">
         <v>0.0593236897969433</v>
       </c>
-      <c r="BV11" s="122" t="n">
+      <c r="BV11" s="123" t="n">
         <v>0.0531437289312609</v>
       </c>
-      <c r="BW11" s="122" t="n">
+      <c r="BW11" s="123" t="n">
         <v>0.0571737272654296</v>
       </c>
-      <c r="BX11" s="123" t="n">
+      <c r="BX11" s="124" t="n">
         <v>0.0428524491951565</v>
       </c>
-      <c r="BY11" s="124" t="n">
+      <c r="BY11" s="125" t="n">
         <v>0.05348322497702</v>
       </c>
     </row>
-    <row r="12" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="119" t="s">
+    <row r="12" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="120" t="n">
+      <c r="B12" s="121" t="n">
         <v>0.0507224912246812</v>
       </c>
-      <c r="C12" s="120" t="n">
+      <c r="C12" s="121" t="n">
         <v>0.0471151790285759</v>
       </c>
-      <c r="D12" s="120" t="n">
+      <c r="D12" s="121" t="n">
         <v>0.0599992968366566</v>
       </c>
-      <c r="E12" s="120" t="n">
+      <c r="E12" s="121" t="n">
         <v>0.0467328178005892</v>
       </c>
-      <c r="F12" s="120" t="n">
+      <c r="F12" s="121" t="n">
         <v>0.047973920790894</v>
       </c>
-      <c r="G12" s="121" t="n">
+      <c r="G12" s="122" t="n">
         <v>0.0470015249047107</v>
       </c>
-      <c r="H12" s="121" t="n">
+      <c r="H12" s="122" t="n">
         <v>0.042849952961472</v>
       </c>
-      <c r="I12" s="121" t="n">
+      <c r="I12" s="122" t="n">
         <v>0.0512257752840434</v>
       </c>
-      <c r="J12" s="121" t="n">
+      <c r="J12" s="122" t="n">
         <v>0.041811729432796</v>
       </c>
-      <c r="K12" s="121" t="n">
+      <c r="K12" s="122" t="n">
         <v>0.0404378347186639</v>
       </c>
-      <c r="L12" s="121" t="n">
+      <c r="L12" s="122" t="n">
         <v>0.040392081364342</v>
       </c>
-      <c r="M12" s="121" t="n">
+      <c r="M12" s="122" t="n">
         <v>0.0550071491096104</v>
       </c>
-      <c r="N12" s="121" t="n">
+      <c r="N12" s="122" t="n">
         <v>0.0332016767676809</v>
       </c>
-      <c r="O12" s="121" t="n">
+      <c r="O12" s="122" t="n">
         <v>0.0418875263034329</v>
       </c>
-      <c r="P12" s="121" t="n">
+      <c r="P12" s="122" t="n">
         <v>0.0374639366293027</v>
       </c>
-      <c r="Q12" s="121" t="n">
+      <c r="Q12" s="122" t="n">
         <v>0.0369150961158713</v>
       </c>
-      <c r="R12" s="121" t="n">
+      <c r="R12" s="122" t="n">
         <v>0.0371780802644832</v>
       </c>
-      <c r="S12" s="121" t="n">
+      <c r="S12" s="122" t="n">
         <v>0.0370622094125097</v>
       </c>
-      <c r="T12" s="121" t="n">
+      <c r="T12" s="122" t="n">
         <v>0.0384827721258096</v>
       </c>
-      <c r="U12" s="121" t="n">
+      <c r="U12" s="122" t="n">
         <v>0.0306034801170862</v>
       </c>
-      <c r="V12" s="121" t="n">
+      <c r="V12" s="122" t="n">
         <v>0.0361934964071113</v>
       </c>
-      <c r="W12" s="121" t="n">
+      <c r="W12" s="122" t="n">
         <v>0.0464647434205642</v>
       </c>
-      <c r="X12" s="121" t="n">
+      <c r="X12" s="122" t="n">
         <v>0.0450466260719838</v>
       </c>
-      <c r="Y12" s="121" t="n">
+      <c r="Y12" s="122" t="n">
         <v>0.0441262731212212</v>
       </c>
-      <c r="Z12" s="121" t="n">
+      <c r="Z12" s="122" t="n">
         <v>0.0282981210539109</v>
       </c>
-      <c r="AA12" s="121" t="n">
+      <c r="AA12" s="122" t="n">
         <v>0.0338873328096929</v>
       </c>
-      <c r="AB12" s="121" t="n">
+      <c r="AB12" s="122" t="n">
         <v>0.0346168154907139</v>
       </c>
-      <c r="AC12" s="121" t="n">
+      <c r="AC12" s="122" t="n">
         <v>0.031429577035351</v>
       </c>
-      <c r="AD12" s="121" t="n">
+      <c r="AD12" s="122" t="n">
         <v>0.0324182106206242</v>
       </c>
-      <c r="AE12" s="121" t="n">
+      <c r="AE12" s="122" t="n">
         <v>0.0322385983245745</v>
       </c>
-      <c r="AF12" s="121" t="n">
+      <c r="AF12" s="122" t="n">
         <v>0.040736735108162</v>
       </c>
-      <c r="AG12" s="121" t="n">
+      <c r="AG12" s="122" t="n">
         <v>0.0258390028662358</v>
       </c>
-      <c r="AH12" s="121" t="n">
+      <c r="AH12" s="122" t="n">
         <v>0.0334244307450594</v>
       </c>
-      <c r="AI12" s="121" t="n">
+      <c r="AI12" s="122" t="n">
         <v>0.0272648208367678</v>
       </c>
-      <c r="AJ12" s="121" t="n">
+      <c r="AJ12" s="122" t="n">
         <v>0.0288885539086149</v>
       </c>
-      <c r="AK12" s="121" t="n">
+      <c r="AK12" s="122" t="n">
         <v>0.0455381626307603</v>
       </c>
-      <c r="AL12" s="121" t="n">
+      <c r="AL12" s="122" t="n">
         <v>0.024937432101323</v>
       </c>
-      <c r="AM12" s="121" t="n">
+      <c r="AM12" s="122" t="n">
         <v>0.034229294270406</v>
       </c>
-      <c r="AN12" s="121" t="n">
+      <c r="AN12" s="122" t="n">
         <v>0.0254915496683009</v>
       </c>
-      <c r="AO12" s="121" t="n">
+      <c r="AO12" s="122" t="n">
         <v>0.0431820611097316</v>
       </c>
-      <c r="AP12" s="121" t="n">
+      <c r="AP12" s="122" t="n">
         <v>0.0397592153840858</v>
       </c>
-      <c r="AQ12" s="121" t="n">
+      <c r="AQ12" s="122" t="n">
         <v>0.0342463229479944</v>
       </c>
-      <c r="AR12" s="121" t="n">
+      <c r="AR12" s="122" t="n">
         <v>0.0484566241354019</v>
       </c>
-      <c r="AS12" s="121" t="n">
+      <c r="AS12" s="122" t="n">
         <v>0.0348247273976074</v>
       </c>
-      <c r="AT12" s="121" t="n">
+      <c r="AT12" s="122" t="n">
         <v>0.0454728567518605</v>
       </c>
-      <c r="AU12" s="121" t="n">
+      <c r="AU12" s="122" t="n">
         <v>0.0432093005320124</v>
       </c>
-      <c r="AV12" s="121" t="n">
+      <c r="AV12" s="122" t="n">
         <v>0.0350547486778326</v>
       </c>
-      <c r="AW12" s="121" t="n">
+      <c r="AW12" s="122" t="n">
         <v>0.0475991132930052</v>
       </c>
-      <c r="AX12" s="121" t="n">
+      <c r="AX12" s="122" t="n">
         <v>0.0371375728045543</v>
       </c>
-      <c r="AY12" s="121" t="n">
+      <c r="AY12" s="122" t="n">
         <v>0.0503800276754424</v>
       </c>
-      <c r="AZ12" s="121" t="n">
+      <c r="AZ12" s="122" t="n">
         <v>0.0428535507142924</v>
       </c>
-      <c r="BA12" s="121" t="n">
+      <c r="BA12" s="122" t="n">
         <v>0.0375257992480779</v>
       </c>
-      <c r="BB12" s="121" t="n">
+      <c r="BB12" s="122" t="n">
         <v>0.0517233439756446</v>
       </c>
-      <c r="BC12" s="121" t="n">
+      <c r="BC12" s="122" t="n">
         <v>0.0457424476973779</v>
       </c>
-      <c r="BD12" s="121" t="n">
+      <c r="BD12" s="122" t="n">
         <v>0.0496067688423732</v>
       </c>
-      <c r="BE12" s="121" t="n">
+      <c r="BE12" s="122" t="n">
         <v>0.0428936282511775</v>
       </c>
-      <c r="BF12" s="121" t="n">
+      <c r="BF12" s="122" t="n">
         <v>0.0531895822728948</v>
       </c>
-      <c r="BG12" s="120" t="n">
+      <c r="BG12" s="121" t="n">
         <v>0.0394179011490987</v>
       </c>
-      <c r="BH12" s="122" t="n">
+      <c r="BH12" s="123" t="n">
         <v>0.0409916765017848</v>
       </c>
-      <c r="BI12" s="122" t="n">
+      <c r="BI12" s="123" t="n">
         <v>0.048539223075456</v>
       </c>
-      <c r="BJ12" s="122" t="n">
+      <c r="BJ12" s="123" t="n">
         <v>0.0372557784487924</v>
       </c>
-      <c r="BK12" s="122" t="n">
+      <c r="BK12" s="123" t="n">
         <v>0.0377994917876515</v>
       </c>
-      <c r="BL12" s="122" t="n">
+      <c r="BL12" s="123" t="n">
         <v>0.0504130040821614</v>
       </c>
-      <c r="BM12" s="122" t="n">
+      <c r="BM12" s="123" t="n">
         <v>0.0447037708432078</v>
       </c>
-      <c r="BN12" s="122" t="n">
+      <c r="BN12" s="123" t="n">
         <v>0.0364653458038604</v>
       </c>
-      <c r="BO12" s="122" t="n">
+      <c r="BO12" s="123" t="n">
         <v>0.0623353804535875</v>
       </c>
-      <c r="BP12" s="122" t="n">
+      <c r="BP12" s="123" t="n">
         <v>0.0500445744704708</v>
       </c>
-      <c r="BQ12" s="122" t="n">
+      <c r="BQ12" s="123" t="n">
         <v>0.0544760482632326</v>
       </c>
-      <c r="BR12" s="122" t="n">
+      <c r="BR12" s="123" t="n">
         <v>0.0502246456867273</v>
       </c>
-      <c r="BS12" s="122" t="n">
+      <c r="BS12" s="123" t="n">
         <v>0.0475021947255892</v>
       </c>
-      <c r="BT12" s="122" t="n">
+      <c r="BT12" s="123" t="n">
         <v>0.0439480214555717</v>
       </c>
-      <c r="BU12" s="122" t="n">
+      <c r="BU12" s="123" t="n">
         <v>0.0532318182088272</v>
       </c>
-      <c r="BV12" s="122" t="n">
+      <c r="BV12" s="123" t="n">
         <v>0.0419594473851006</v>
       </c>
-      <c r="BW12" s="122" t="n">
+      <c r="BW12" s="123" t="n">
         <v>0.0486807839069958</v>
       </c>
-      <c r="BX12" s="123" t="n">
+      <c r="BX12" s="124" t="n">
         <v>0.0511706194195362</v>
       </c>
-      <c r="BY12" s="124" t="n">
+      <c r="BY12" s="125" t="n">
         <v>0.0525112547055228</v>
       </c>
     </row>
-    <row r="13" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="115" t="n">
+      <c r="B13" s="116" t="n">
         <v>0.0478944185854769</v>
       </c>
-      <c r="C13" s="115" t="n">
+      <c r="C13" s="116" t="n">
         <v>0.0465745313176367</v>
       </c>
-      <c r="D13" s="115" t="n">
+      <c r="D13" s="116" t="n">
         <v>0.0442472809265182</v>
       </c>
-      <c r="E13" s="115" t="n">
+      <c r="E13" s="116" t="n">
         <v>0.0437263272077622</v>
       </c>
-      <c r="F13" s="115" t="n">
+      <c r="F13" s="116" t="n">
         <v>0.0440855212471913</v>
       </c>
-      <c r="G13" s="115" t="n">
+      <c r="G13" s="116" t="n">
         <v>0.043714278806556</v>
       </c>
-      <c r="H13" s="115" t="n">
+      <c r="H13" s="116" t="n">
         <v>0.0423018529420315</v>
       </c>
-      <c r="I13" s="115" t="n">
+      <c r="I13" s="116" t="n">
         <v>0.0378685857100432</v>
       </c>
-      <c r="J13" s="115" t="n">
+      <c r="J13" s="116" t="n">
         <v>0.0354067126061238</v>
       </c>
-      <c r="K13" s="115" t="n">
+      <c r="K13" s="116" t="n">
         <v>0.0359465781026942</v>
       </c>
-      <c r="L13" s="115" t="n">
+      <c r="L13" s="116" t="n">
         <v>0.0341841500886205</v>
       </c>
-      <c r="M13" s="115" t="n">
+      <c r="M13" s="116" t="n">
         <v>0.0327780610789142</v>
       </c>
-      <c r="N13" s="115" t="n">
+      <c r="N13" s="116" t="n">
         <v>0.033659807527172</v>
       </c>
-      <c r="O13" s="115" t="n">
+      <c r="O13" s="116" t="n">
         <v>0.033143153507625</v>
       </c>
-      <c r="P13" s="115" t="n">
+      <c r="P13" s="116" t="n">
         <v>0.0333308039292813</v>
       </c>
-      <c r="Q13" s="115" t="n">
+      <c r="Q13" s="116" t="n">
         <v>0.0340335952860436</v>
       </c>
-      <c r="R13" s="115" t="n">
+      <c r="R13" s="116" t="n">
         <v>0.0333844109132968</v>
       </c>
-      <c r="S13" s="115" t="n">
+      <c r="S13" s="116" t="n">
         <v>0.0315877712094889</v>
       </c>
-      <c r="T13" s="115" t="n">
+      <c r="T13" s="116" t="n">
         <v>0.032915463989385</v>
       </c>
-      <c r="U13" s="115" t="n">
+      <c r="U13" s="116" t="n">
         <v>0.0320667027387498</v>
       </c>
-      <c r="V13" s="115" t="n">
+      <c r="V13" s="116" t="n">
         <v>0.0322289356399022</v>
       </c>
-      <c r="W13" s="115" t="n">
+      <c r="W13" s="116" t="n">
         <v>0.0331424993910847</v>
       </c>
-      <c r="X13" s="115" t="n">
+      <c r="X13" s="116" t="n">
         <v>0.0320013153199085</v>
       </c>
-      <c r="Y13" s="115" t="n">
+      <c r="Y13" s="116" t="n">
         <v>0.0313133351835744</v>
       </c>
-      <c r="Z13" s="115" t="n">
+      <c r="Z13" s="116" t="n">
         <v>0.0316916851186398</v>
       </c>
-      <c r="AA13" s="115" t="n">
+      <c r="AA13" s="116" t="n">
         <v>0.0315545915595724</v>
       </c>
-      <c r="AB13" s="115" t="n">
+      <c r="AB13" s="116" t="n">
         <v>0.0330659528423291</v>
       </c>
-      <c r="AC13" s="115" t="n">
+      <c r="AC13" s="116" t="n">
         <v>0.0312491235784727</v>
       </c>
-      <c r="AD13" s="115" t="n">
+      <c r="AD13" s="116" t="n">
         <v>0.0321831618161193</v>
       </c>
-      <c r="AE13" s="115" t="n">
+      <c r="AE13" s="116" t="n">
         <v>0.0313616696053939</v>
       </c>
-      <c r="AF13" s="115" t="n">
+      <c r="AF13" s="116" t="n">
         <v>0.0306930662884915</v>
       </c>
-      <c r="AG13" s="115" t="n">
+      <c r="AG13" s="116" t="n">
         <v>0.0306529060980717</v>
       </c>
-      <c r="AH13" s="115" t="n">
+      <c r="AH13" s="116" t="n">
         <v>0.0330215509693217</v>
       </c>
-      <c r="AI13" s="115" t="n">
+      <c r="AI13" s="116" t="n">
         <v>0.0326257304111464</v>
       </c>
-      <c r="AJ13" s="115" t="n">
+      <c r="AJ13" s="116" t="n">
         <v>0.0335023661085196</v>
       </c>
-      <c r="AK13" s="115" t="n">
+      <c r="AK13" s="116" t="n">
         <v>0.0316377489360942</v>
       </c>
-      <c r="AL13" s="115" t="n">
+      <c r="AL13" s="116" t="n">
         <v>0.0314403665726897</v>
       </c>
-      <c r="AM13" s="115" t="n">
+      <c r="AM13" s="116" t="n">
         <v>0.033623370283261</v>
       </c>
-      <c r="AN13" s="115" t="n">
+      <c r="AN13" s="116" t="n">
         <v>0.0362606054253769</v>
       </c>
-      <c r="AO13" s="115" t="n">
+      <c r="AO13" s="116" t="n">
         <v>0.0347849123503971</v>
       </c>
-      <c r="AP13" s="115" t="n">
+      <c r="AP13" s="116" t="n">
         <v>0.0353582291220351</v>
       </c>
-      <c r="AQ13" s="115" t="n">
+      <c r="AQ13" s="116" t="n">
         <v>0.0351799534256906</v>
       </c>
-      <c r="AR13" s="115" t="n">
+      <c r="AR13" s="116" t="n">
         <v>0.0356428680889495</v>
       </c>
-      <c r="AS13" s="115" t="n">
+      <c r="AS13" s="116" t="n">
         <v>0.0366644835372692</v>
       </c>
-      <c r="AT13" s="115" t="n">
+      <c r="AT13" s="116" t="n">
         <v>0.0374105589738655</v>
       </c>
-      <c r="AU13" s="115" t="n">
+      <c r="AU13" s="116" t="n">
         <v>0.0389272666830545</v>
       </c>
-      <c r="AV13" s="115" t="n">
+      <c r="AV13" s="116" t="n">
         <v>0.0398837807808734</v>
       </c>
-      <c r="AW13" s="115" t="n">
+      <c r="AW13" s="116" t="n">
         <v>0.041473252940783</v>
       </c>
-      <c r="AX13" s="115" t="n">
+      <c r="AX13" s="116" t="n">
         <v>0.0407231676909049</v>
       </c>
-      <c r="AY13" s="115" t="n">
+      <c r="AY13" s="116" t="n">
         <v>0.0393230133937549</v>
       </c>
-      <c r="AZ13" s="125" t="n">
+      <c r="AZ13" s="126" t="n">
         <v>0.0415032548415249</v>
       </c>
-      <c r="BA13" s="125" t="n">
+      <c r="BA13" s="126" t="n">
         <v>0.0402823193602113</v>
       </c>
-      <c r="BB13" s="125" t="n">
+      <c r="BB13" s="126" t="n">
         <v>0.0414906689583962</v>
       </c>
-      <c r="BC13" s="125" t="n">
+      <c r="BC13" s="126" t="n">
         <v>0.0419108230486721</v>
       </c>
-      <c r="BD13" s="125" t="n">
+      <c r="BD13" s="126" t="n">
         <v>0.0430726151530623</v>
       </c>
-      <c r="BE13" s="125" t="n">
+      <c r="BE13" s="126" t="n">
         <v>0.0428400998364933</v>
       </c>
-      <c r="BF13" s="125" t="n">
+      <c r="BF13" s="126" t="n">
         <v>0.0434193414459068</v>
       </c>
-      <c r="BG13" s="115" t="n">
+      <c r="BG13" s="116" t="n">
         <v>0.0432793045927696</v>
       </c>
-      <c r="BH13" s="126" t="n">
+      <c r="BH13" s="127" t="n">
         <v>0.0439485072809379</v>
       </c>
-      <c r="BI13" s="126" t="n">
+      <c r="BI13" s="127" t="n">
         <v>0.0436502930403754</v>
       </c>
-      <c r="BJ13" s="126" t="n">
+      <c r="BJ13" s="127" t="n">
         <v>0.044261938455253</v>
       </c>
-      <c r="BK13" s="126" t="n">
+      <c r="BK13" s="127" t="n">
         <v>0.0451151538858778</v>
       </c>
-      <c r="BL13" s="126" t="n">
+      <c r="BL13" s="127" t="n">
         <v>0.0433286514751055</v>
       </c>
-      <c r="BM13" s="126" t="n">
+      <c r="BM13" s="127" t="n">
         <v>0.045093546703037</v>
       </c>
-      <c r="BN13" s="126" t="n">
+      <c r="BN13" s="127" t="n">
         <v>0.0433955914177779</v>
       </c>
-      <c r="BO13" s="126" t="n">
+      <c r="BO13" s="127" t="n">
         <v>0.0443766283565012</v>
       </c>
-      <c r="BP13" s="126" t="n">
+      <c r="BP13" s="127" t="n">
         <v>0.0453511561037414</v>
       </c>
-      <c r="BQ13" s="126" t="n">
+      <c r="BQ13" s="127" t="n">
         <v>0.0441037741829245</v>
       </c>
-      <c r="BR13" s="126" t="n">
+      <c r="BR13" s="127" t="n">
         <v>0.0430288529429415</v>
       </c>
-      <c r="BS13" s="126" t="n">
+      <c r="BS13" s="127" t="n">
         <v>0.0438033701462958</v>
       </c>
-      <c r="BT13" s="126" t="n">
+      <c r="BT13" s="127" t="n">
         <v>0.044950919756627</v>
       </c>
-      <c r="BU13" s="126" t="n">
+      <c r="BU13" s="127" t="n">
         <v>0.0434523955988953</v>
       </c>
-      <c r="BV13" s="126" t="n">
+      <c r="BV13" s="127" t="n">
         <v>0.0442188159006661</v>
       </c>
-      <c r="BW13" s="126" t="n">
+      <c r="BW13" s="127" t="n">
         <v>0.0433002744947049</v>
       </c>
-      <c r="BX13" s="127" t="n">
+      <c r="BX13" s="128" t="n">
         <v>0.0441289662534673</v>
       </c>
-      <c r="BY13" s="128" t="n">
+      <c r="BY13" s="129" t="n">
         <v>0.0454200163877761</v>
       </c>
     </row>
-    <row r="14" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="119" t="s">
+    <row r="14" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="120" t="n">
+      <c r="B14" s="121" t="n">
         <v>0.0101614093403427</v>
       </c>
-      <c r="C14" s="120" t="n">
+      <c r="C14" s="121" t="n">
         <v>0.0100300214772455</v>
       </c>
-      <c r="D14" s="120" t="n">
+      <c r="D14" s="121" t="n">
         <v>0.00963409296246972</v>
       </c>
-      <c r="E14" s="120" t="n">
+      <c r="E14" s="121" t="n">
         <v>0.0088885714825041</v>
       </c>
-      <c r="F14" s="120" t="n">
+      <c r="F14" s="121" t="n">
         <v>0.00961259219654031</v>
       </c>
-      <c r="G14" s="121" t="n">
+      <c r="G14" s="122" t="n">
         <v>0.00916784832110711</v>
       </c>
-      <c r="H14" s="121" t="n">
+      <c r="H14" s="122" t="n">
         <v>0.0089178666895877</v>
       </c>
-      <c r="I14" s="121" t="n">
+      <c r="I14" s="122" t="n">
         <v>0.00931555606315587</v>
       </c>
-      <c r="J14" s="121" t="n">
+      <c r="J14" s="122" t="n">
         <v>0.00905504446577709</v>
       </c>
-      <c r="K14" s="121" t="n">
+      <c r="K14" s="122" t="n">
         <v>0.00914572103895494</v>
       </c>
-      <c r="L14" s="121" t="n">
+      <c r="L14" s="122" t="n">
         <v>0.00923765026663177</v>
       </c>
-      <c r="M14" s="121" t="n">
+      <c r="M14" s="122" t="n">
         <v>0.00877901756421588</v>
       </c>
-      <c r="N14" s="121" t="n">
+      <c r="N14" s="122" t="n">
         <v>0.00900540670267479</v>
       </c>
-      <c r="O14" s="121" t="n">
+      <c r="O14" s="122" t="n">
         <v>0.00925203614270898</v>
       </c>
-      <c r="P14" s="121" t="n">
+      <c r="P14" s="122" t="n">
         <v>0.00868886000167259</v>
       </c>
-      <c r="Q14" s="121" t="n">
+      <c r="Q14" s="122" t="n">
         <v>0.00880786259167041</v>
       </c>
-      <c r="R14" s="121" t="n">
+      <c r="R14" s="122" t="n">
         <v>0.00900214191982696</v>
       </c>
-      <c r="S14" s="121" t="n">
+      <c r="S14" s="122" t="n">
         <v>0.00868238011504392</v>
       </c>
-      <c r="T14" s="121" t="n">
+      <c r="T14" s="122" t="n">
         <v>0.013425319655878</v>
       </c>
-      <c r="U14" s="121" t="n">
+      <c r="U14" s="122" t="n">
         <v>0.008974908509421</v>
       </c>
-      <c r="V14" s="121" t="n">
+      <c r="V14" s="122" t="n">
         <v>0.00879008571907253</v>
       </c>
-      <c r="W14" s="121" t="n">
+      <c r="W14" s="122" t="n">
         <v>0.0113611043400756</v>
       </c>
-      <c r="X14" s="121" t="n">
+      <c r="X14" s="122" t="n">
         <v>0.00911039251381717</v>
       </c>
-      <c r="Y14" s="121" t="n">
+      <c r="Y14" s="122" t="n">
         <v>0.00889817421003901</v>
       </c>
-      <c r="Z14" s="121" t="n">
+      <c r="Z14" s="122" t="n">
         <v>0.00877577611468737</v>
       </c>
-      <c r="AA14" s="121" t="n">
+      <c r="AA14" s="122" t="n">
         <v>0.00894759155092165</v>
       </c>
-      <c r="AB14" s="121" t="n">
+      <c r="AB14" s="122" t="n">
         <v>0.00930307403825524</v>
       </c>
-      <c r="AC14" s="121" t="n">
+      <c r="AC14" s="122" t="n">
         <v>0.00893019170122978</v>
       </c>
-      <c r="AD14" s="121" t="n">
+      <c r="AD14" s="122" t="n">
         <v>0.00920373115198538</v>
       </c>
-      <c r="AE14" s="121" t="n">
+      <c r="AE14" s="122" t="n">
         <v>0.00933534677743549</v>
       </c>
-      <c r="AF14" s="121" t="n">
+      <c r="AF14" s="122" t="n">
         <v>0.00901628793030831</v>
       </c>
-      <c r="AG14" s="121" t="n">
+      <c r="AG14" s="122" t="n">
         <v>0.00905617511839628</v>
       </c>
-      <c r="AH14" s="121" t="n">
+      <c r="AH14" s="122" t="n">
         <v>0.00963267603075646</v>
       </c>
-      <c r="AI14" s="121" t="n">
+      <c r="AI14" s="122" t="n">
         <v>0.0090694488544538</v>
       </c>
-      <c r="AJ14" s="121" t="n">
+      <c r="AJ14" s="122" t="n">
         <v>0.00910229798314282</v>
       </c>
-      <c r="AK14" s="121" t="n">
+      <c r="AK14" s="122" t="n">
         <v>0.00915257515563861</v>
       </c>
-      <c r="AL14" s="121" t="n">
+      <c r="AL14" s="122" t="n">
         <v>0.00964846712450878</v>
       </c>
-      <c r="AM14" s="121" t="n">
+      <c r="AM14" s="122" t="n">
         <v>0.00921039304599826</v>
       </c>
-      <c r="AN14" s="121" t="n">
+      <c r="AN14" s="122" t="n">
         <v>0.00894043716940817</v>
       </c>
-      <c r="AO14" s="121" t="n">
+      <c r="AO14" s="122" t="n">
         <v>0.00872265280411083</v>
       </c>
-      <c r="AP14" s="121" t="n">
+      <c r="AP14" s="122" t="n">
         <v>0.00869899140244728</v>
       </c>
-      <c r="AQ14" s="121" t="n">
+      <c r="AQ14" s="122" t="n">
         <v>0.010700582327555</v>
       </c>
-      <c r="AR14" s="121" t="n">
+      <c r="AR14" s="122" t="n">
         <v>0.00877084023617969</v>
       </c>
-      <c r="AS14" s="121" t="n">
+      <c r="AS14" s="122" t="n">
         <v>0.00883392318666352</v>
       </c>
-      <c r="AT14" s="121" t="n">
+      <c r="AT14" s="122" t="n">
         <v>0.0091270760645674</v>
       </c>
-      <c r="AU14" s="121" t="n">
+      <c r="AU14" s="122" t="n">
         <v>0.0091590725009393</v>
       </c>
-      <c r="AV14" s="121" t="n">
+      <c r="AV14" s="122" t="n">
         <v>0.00909723291613571</v>
       </c>
-      <c r="AW14" s="121" t="n">
+      <c r="AW14" s="122" t="n">
         <v>0.00919778891380804</v>
       </c>
-      <c r="AX14" s="121" t="n">
+      <c r="AX14" s="122" t="n">
         <v>0.00898925774940301</v>
       </c>
-      <c r="AY14" s="121" t="n">
+      <c r="AY14" s="122" t="n">
         <v>0.00876787479424335</v>
       </c>
-      <c r="AZ14" s="121" t="n">
+      <c r="AZ14" s="122" t="n">
         <v>0.00896987124877486</v>
       </c>
-      <c r="BA14" s="121" t="n">
+      <c r="BA14" s="122" t="n">
         <v>0.00894370990993241</v>
       </c>
-      <c r="BB14" s="121" t="n">
+      <c r="BB14" s="122" t="n">
         <v>0.00905317580900191</v>
       </c>
-      <c r="BC14" s="121" t="n">
+      <c r="BC14" s="122" t="n">
         <v>0.00932573387626066</v>
       </c>
-      <c r="BD14" s="121" t="n">
+      <c r="BD14" s="122" t="n">
         <v>0.00945605073860636</v>
       </c>
-      <c r="BE14" s="121" t="n">
+      <c r="BE14" s="122" t="n">
         <v>0.00984171324808189</v>
       </c>
-      <c r="BF14" s="121" t="n">
+      <c r="BF14" s="122" t="n">
         <v>0.00928398830296047</v>
       </c>
-      <c r="BG14" s="120" t="n">
+      <c r="BG14" s="121" t="n">
         <v>0.00944576375181593</v>
       </c>
-      <c r="BH14" s="122" t="n">
+      <c r="BH14" s="123" t="n">
         <v>0.00895059988812852</v>
       </c>
-      <c r="BI14" s="122" t="n">
+      <c r="BI14" s="123" t="n">
         <v>0.00923329008385363</v>
       </c>
-      <c r="BJ14" s="122" t="n">
+      <c r="BJ14" s="123" t="n">
         <v>0.00978540566966196</v>
       </c>
-      <c r="BK14" s="122" t="n">
+      <c r="BK14" s="123" t="n">
         <v>0.00951536122240334</v>
       </c>
-      <c r="BL14" s="122" t="n">
+      <c r="BL14" s="123" t="n">
         <v>0.00959476314670548</v>
       </c>
-      <c r="BM14" s="122" t="n">
+      <c r="BM14" s="123" t="n">
         <v>0.0103685691339359</v>
       </c>
-      <c r="BN14" s="122" t="n">
+      <c r="BN14" s="123" t="n">
         <v>0.00966663749237052</v>
       </c>
-      <c r="BO14" s="122" t="n">
+      <c r="BO14" s="123" t="n">
         <v>0.00964305577439153</v>
       </c>
-      <c r="BP14" s="122" t="n">
+      <c r="BP14" s="123" t="n">
         <v>0.00947564082659749</v>
       </c>
-      <c r="BQ14" s="122" t="n">
+      <c r="BQ14" s="123" t="n">
         <v>0.00967458485314052</v>
       </c>
-      <c r="BR14" s="122" t="n">
+      <c r="BR14" s="123" t="n">
         <v>0.00984916794209649</v>
       </c>
-      <c r="BS14" s="122" t="n">
+      <c r="BS14" s="123" t="n">
         <v>0.00962455428222012</v>
       </c>
-      <c r="BT14" s="122" t="n">
+      <c r="BT14" s="123" t="n">
         <v>0.00954348460910861</v>
       </c>
-      <c r="BU14" s="122" t="n">
+      <c r="BU14" s="123" t="n">
         <v>0.00963159701634016</v>
       </c>
-      <c r="BV14" s="122" t="n">
+      <c r="BV14" s="123" t="n">
         <v>0.0098657332690329</v>
       </c>
-      <c r="BW14" s="122" t="n">
+      <c r="BW14" s="123" t="n">
         <v>0.00962968717451571</v>
       </c>
-      <c r="BX14" s="123" t="n">
+      <c r="BX14" s="124" t="n">
         <v>0.00976647212234072</v>
       </c>
-      <c r="BY14" s="124" t="n">
+      <c r="BY14" s="125" t="n">
         <v>0.00960249010038478</v>
       </c>
     </row>
-    <row r="15" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="119" t="s">
+    <row r="15" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="120" t="n">
+      <c r="B15" s="121" t="n">
         <v>0.0226900322311949</v>
       </c>
-      <c r="C15" s="120" t="n">
+      <c r="C15" s="121" t="n">
         <v>0.0221763061114825</v>
       </c>
-      <c r="D15" s="120" t="n">
+      <c r="D15" s="121" t="n">
         <v>0.0206093885001649</v>
       </c>
-      <c r="E15" s="120" t="n">
+      <c r="E15" s="121" t="n">
         <v>0.0136386772675318</v>
       </c>
-      <c r="F15" s="120" t="n">
+      <c r="F15" s="121" t="n">
         <v>0.0175662745576425</v>
       </c>
-      <c r="G15" s="121" t="n">
+      <c r="G15" s="122" t="n">
         <v>0.0171910546736302</v>
       </c>
-      <c r="H15" s="121" t="n">
+      <c r="H15" s="122" t="n">
         <v>0.0164842759399021</v>
       </c>
-      <c r="I15" s="121" t="n">
+      <c r="I15" s="122" t="n">
         <v>0.013828255605818</v>
       </c>
-      <c r="J15" s="121" t="n">
+      <c r="J15" s="122" t="n">
         <v>0.0122184323547793</v>
       </c>
-      <c r="K15" s="121" t="n">
+      <c r="K15" s="122" t="n">
         <v>0.01143319788526</v>
       </c>
-      <c r="L15" s="121" t="n">
+      <c r="L15" s="122" t="n">
         <v>0.0108703243683413</v>
       </c>
-      <c r="M15" s="121" t="n">
+      <c r="M15" s="122" t="n">
         <v>0.0108879588326448</v>
       </c>
-      <c r="N15" s="121" t="n">
+      <c r="N15" s="122" t="n">
         <v>0.01116214375449</v>
       </c>
-      <c r="O15" s="121" t="n">
+      <c r="O15" s="122" t="n">
         <v>0.0120187915682413</v>
       </c>
-      <c r="P15" s="121" t="n">
+      <c r="P15" s="122" t="n">
         <v>0.0111231276848327</v>
       </c>
-      <c r="Q15" s="121" t="n">
+      <c r="Q15" s="122" t="n">
         <v>0.0110715838489401</v>
       </c>
-      <c r="R15" s="121" t="n">
+      <c r="R15" s="122" t="n">
         <v>0.0125187076899658</v>
       </c>
-      <c r="S15" s="121" t="n">
+      <c r="S15" s="122" t="n">
         <v>0.0114688049743431</v>
       </c>
-      <c r="T15" s="121" t="n">
+      <c r="T15" s="122" t="n">
         <v>0.0121124900142402</v>
       </c>
-      <c r="U15" s="121" t="n">
+      <c r="U15" s="122" t="n">
         <v>0.0118561631357924</v>
       </c>
-      <c r="V15" s="121" t="n">
+      <c r="V15" s="122" t="n">
         <v>0.0123139708868437</v>
       </c>
-      <c r="W15" s="121" t="n">
+      <c r="W15" s="122" t="n">
         <v>0.0158080948589534</v>
       </c>
-      <c r="X15" s="121" t="n">
+      <c r="X15" s="122" t="n">
         <v>0.0105936406705294</v>
       </c>
-      <c r="Y15" s="121" t="n">
+      <c r="Y15" s="122" t="n">
         <v>0.0114551297393504</v>
       </c>
-      <c r="Z15" s="121" t="n">
+      <c r="Z15" s="122" t="n">
         <v>0.0111958356168774</v>
       </c>
-      <c r="AA15" s="121" t="n">
+      <c r="AA15" s="122" t="n">
         <v>0.0114265768248307</v>
       </c>
-      <c r="AB15" s="121" t="n">
+      <c r="AB15" s="122" t="n">
         <v>0.0122762481978843</v>
       </c>
-      <c r="AC15" s="121" t="n">
+      <c r="AC15" s="122" t="n">
         <v>0.0121412273303762</v>
       </c>
-      <c r="AD15" s="121" t="n">
+      <c r="AD15" s="122" t="n">
         <v>0.0128109740553381</v>
       </c>
-      <c r="AE15" s="121" t="n">
+      <c r="AE15" s="122" t="n">
         <v>0.0123488337251555</v>
       </c>
-      <c r="AF15" s="121" t="n">
+      <c r="AF15" s="122" t="n">
         <v>0.0122171340321552</v>
       </c>
-      <c r="AG15" s="121" t="n">
+      <c r="AG15" s="122" t="n">
         <v>0.010893556758329</v>
       </c>
-      <c r="AH15" s="121" t="n">
+      <c r="AH15" s="122" t="n">
         <v>0.0125047609594602</v>
       </c>
-      <c r="AI15" s="121" t="n">
+      <c r="AI15" s="122" t="n">
         <v>0.0102807690452756</v>
       </c>
-      <c r="AJ15" s="121" t="n">
+      <c r="AJ15" s="122" t="n">
         <v>0.012968402172939</v>
       </c>
-      <c r="AK15" s="121" t="n">
+      <c r="AK15" s="122" t="n">
         <v>0.0113698265634864</v>
       </c>
-      <c r="AL15" s="121" t="n">
+      <c r="AL15" s="122" t="n">
         <v>0.0109918673415535</v>
       </c>
-      <c r="AM15" s="121" t="n">
+      <c r="AM15" s="122" t="n">
         <v>0.0111480642364295</v>
       </c>
-      <c r="AN15" s="121" t="n">
+      <c r="AN15" s="122" t="n">
         <v>0.0128532477952884</v>
       </c>
-      <c r="AO15" s="121" t="n">
+      <c r="AO15" s="122" t="n">
         <v>0.0145357347502514</v>
       </c>
-      <c r="AP15" s="121" t="n">
+      <c r="AP15" s="122" t="n">
         <v>0.0136714250220664</v>
       </c>
-      <c r="AQ15" s="121" t="n">
+      <c r="AQ15" s="122" t="n">
         <v>0.0173694806341368</v>
       </c>
-      <c r="AR15" s="121" t="n">
+      <c r="AR15" s="122" t="n">
         <v>0.0137930996993652</v>
       </c>
-      <c r="AS15" s="121" t="n">
+      <c r="AS15" s="122" t="n">
         <v>0.0131628586111995</v>
       </c>
-      <c r="AT15" s="121" t="n">
+      <c r="AT15" s="122" t="n">
         <v>0.0122842970246985</v>
       </c>
-      <c r="AU15" s="121" t="n">
+      <c r="AU15" s="122" t="n">
         <v>0.0128070258163911</v>
       </c>
-      <c r="AV15" s="121" t="n">
+      <c r="AV15" s="122" t="n">
         <v>0.0165705515357691</v>
       </c>
-      <c r="AW15" s="121" t="n">
+      <c r="AW15" s="122" t="n">
         <v>0.0200096119195911</v>
       </c>
-      <c r="AX15" s="121" t="n">
+      <c r="AX15" s="122" t="n">
         <v>0.0184238905138679</v>
       </c>
-      <c r="AY15" s="121" t="n">
+      <c r="AY15" s="122" t="n">
         <v>0.0183982859219792</v>
       </c>
-      <c r="AZ15" s="121" t="n">
+      <c r="AZ15" s="122" t="n">
         <v>0.0175145424133845</v>
       </c>
-      <c r="BA15" s="121" t="n">
+      <c r="BA15" s="122" t="n">
         <v>0.0179851351408824</v>
       </c>
-      <c r="BB15" s="121" t="n">
+      <c r="BB15" s="122" t="n">
         <v>0.0186178456785511</v>
       </c>
-      <c r="BC15" s="121" t="n">
+      <c r="BC15" s="122" t="n">
         <v>0.0188537178962936</v>
       </c>
-      <c r="BD15" s="121" t="n">
+      <c r="BD15" s="122" t="n">
         <v>0.0205013997043771</v>
       </c>
-      <c r="BE15" s="121" t="n">
+      <c r="BE15" s="122" t="n">
         <v>0.0252130740078842</v>
       </c>
-      <c r="BF15" s="121" t="n">
+      <c r="BF15" s="122" t="n">
         <v>0.0284002718746066</v>
       </c>
-      <c r="BG15" s="120" t="n">
+      <c r="BG15" s="121" t="n">
         <v>0.0202826237759468</v>
       </c>
-      <c r="BH15" s="122" t="n">
+      <c r="BH15" s="123" t="n">
         <v>0.0262797934338735</v>
       </c>
-      <c r="BI15" s="122" t="n">
+      <c r="BI15" s="123" t="n">
         <v>0.0237642937833516</v>
       </c>
-      <c r="BJ15" s="122" t="n">
+      <c r="BJ15" s="123" t="n">
         <v>0.0247565082506459</v>
       </c>
-      <c r="BK15" s="122" t="n">
+      <c r="BK15" s="123" t="n">
         <v>0.020935988666005</v>
       </c>
-      <c r="BL15" s="122" t="n">
+      <c r="BL15" s="123" t="n">
         <v>0.0163214931113196</v>
       </c>
-      <c r="BM15" s="122" t="n">
+      <c r="BM15" s="123" t="n">
         <v>0.0193818186679199</v>
       </c>
-      <c r="BN15" s="122" t="n">
+      <c r="BN15" s="123" t="n">
         <v>0.0175998403188464</v>
       </c>
-      <c r="BO15" s="122" t="n">
+      <c r="BO15" s="123" t="n">
         <v>0.0214043691593718</v>
       </c>
-      <c r="BP15" s="122" t="n">
+      <c r="BP15" s="123" t="n">
         <v>0.0213127500048908</v>
       </c>
-      <c r="BQ15" s="122" t="n">
+      <c r="BQ15" s="123" t="n">
         <v>0.0198762355541446</v>
       </c>
-      <c r="BR15" s="122" t="n">
+      <c r="BR15" s="123" t="n">
         <v>0.0209381604625426</v>
       </c>
-      <c r="BS15" s="122" t="n">
+      <c r="BS15" s="123" t="n">
         <v>0.0158250616349335</v>
       </c>
-      <c r="BT15" s="122" t="n">
+      <c r="BT15" s="123" t="n">
         <v>0.0200263553576456</v>
       </c>
-      <c r="BU15" s="122" t="n">
+      <c r="BU15" s="123" t="n">
         <v>0.0162518511422823</v>
       </c>
-      <c r="BV15" s="122" t="n">
+      <c r="BV15" s="123" t="n">
         <v>0.0182598972955334</v>
       </c>
-      <c r="BW15" s="122" t="n">
+      <c r="BW15" s="123" t="n">
         <v>0.0203175762658501</v>
       </c>
-      <c r="BX15" s="123" t="n">
+      <c r="BX15" s="124" t="n">
         <v>0.0175140645036291</v>
       </c>
-      <c r="BY15" s="124" t="n">
+      <c r="BY15" s="125" t="n">
         <v>0.0181640700284315</v>
       </c>
     </row>
-    <row r="16" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="119" t="s">
+    <row r="16" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="129" t="n">
+      <c r="B16" s="130" t="n">
         <v>0.0393824671173955</v>
       </c>
-      <c r="C16" s="129" t="n">
+      <c r="C16" s="130" t="n">
         <v>0.0385237579868731</v>
       </c>
-      <c r="D16" s="129" t="n">
+      <c r="D16" s="130" t="n">
         <v>0.0302444747868922</v>
       </c>
-      <c r="E16" s="129" t="n">
+      <c r="E16" s="130" t="n">
         <v>0.0352935841077808</v>
       </c>
-      <c r="F16" s="129" t="n">
+      <c r="F16" s="130" t="n">
         <v>0.0338135490675248</v>
       </c>
-      <c r="G16" s="130" t="n">
+      <c r="G16" s="131" t="n">
         <v>0.0342173547063659</v>
       </c>
-      <c r="H16" s="130" t="n">
+      <c r="H16" s="131" t="n">
         <v>0.03446522414261</v>
       </c>
-      <c r="I16" s="130" t="n">
+      <c r="I16" s="131" t="n">
         <v>0.0294392748904744</v>
       </c>
-      <c r="J16" s="130" t="n">
+      <c r="J16" s="131" t="n">
         <v>0.0242009192793884</v>
       </c>
-      <c r="K16" s="130" t="n">
+      <c r="K16" s="131" t="n">
         <v>0.0232124579225143</v>
       </c>
-      <c r="L16" s="130" t="n">
+      <c r="L16" s="131" t="n">
         <v>0.026063511059199</v>
       </c>
-      <c r="M16" s="130" t="n">
+      <c r="M16" s="131" t="n">
         <v>0.0192418195706316</v>
       </c>
-      <c r="N16" s="130" t="n">
+      <c r="N16" s="131" t="n">
         <v>0.0218015034072809</v>
       </c>
-      <c r="O16" s="130" t="n">
+      <c r="O16" s="131" t="n">
         <v>0.0228265578057387</v>
       </c>
-      <c r="P16" s="130" t="n">
+      <c r="P16" s="131" t="n">
         <v>0.0205044089202285</v>
       </c>
-      <c r="Q16" s="130" t="n">
+      <c r="Q16" s="131" t="n">
         <v>0.0231571349484191</v>
       </c>
-      <c r="R16" s="130" t="n">
+      <c r="R16" s="131" t="n">
         <v>0.0254301253297026</v>
       </c>
-      <c r="S16" s="130" t="n">
+      <c r="S16" s="131" t="n">
         <v>0.0190691437404505</v>
       </c>
-      <c r="T16" s="130" t="n">
+      <c r="T16" s="131" t="n">
         <v>0.0230975691403391</v>
       </c>
-      <c r="U16" s="130" t="n">
+      <c r="U16" s="131" t="n">
         <v>0.0221052364627462</v>
       </c>
-      <c r="V16" s="130" t="n">
+      <c r="V16" s="131" t="n">
         <v>0.0223330909816157</v>
       </c>
-      <c r="W16" s="130" t="n">
+      <c r="W16" s="131" t="n">
         <v>0.0212330869046117</v>
       </c>
-      <c r="X16" s="130" t="n">
+      <c r="X16" s="131" t="n">
         <v>0.0200233077728003</v>
       </c>
-      <c r="Y16" s="130" t="n">
+      <c r="Y16" s="131" t="n">
         <v>0.0239010549719476</v>
       </c>
-      <c r="Z16" s="130" t="n">
+      <c r="Z16" s="131" t="n">
         <v>0.0203396900816838</v>
       </c>
-      <c r="AA16" s="130" t="n">
+      <c r="AA16" s="131" t="n">
         <v>0.0206862370833287</v>
       </c>
-      <c r="AB16" s="130" t="n">
+      <c r="AB16" s="131" t="n">
         <v>0.0210332023223115</v>
       </c>
-      <c r="AC16" s="130" t="n">
+      <c r="AC16" s="131" t="n">
         <v>0.0188948407185142</v>
       </c>
-      <c r="AD16" s="130" t="n">
+      <c r="AD16" s="131" t="n">
         <v>0.020937846202675</v>
       </c>
-      <c r="AE16" s="130" t="n">
+      <c r="AE16" s="131" t="n">
         <v>0.0210998458428351</v>
       </c>
-      <c r="AF16" s="130" t="n">
+      <c r="AF16" s="131" t="n">
         <v>0.0182572169218286</v>
       </c>
-      <c r="AG16" s="130" t="n">
+      <c r="AG16" s="131" t="n">
         <v>0.0218447951159363</v>
       </c>
-      <c r="AH16" s="130" t="n">
+      <c r="AH16" s="131" t="n">
         <v>0.0219218880454896</v>
       </c>
-      <c r="AI16" s="130" t="n">
+      <c r="AI16" s="131" t="n">
         <v>0.0233268063415237</v>
       </c>
-      <c r="AJ16" s="130" t="n">
+      <c r="AJ16" s="131" t="n">
         <v>0.025112423860701</v>
       </c>
-      <c r="AK16" s="130" t="n">
+      <c r="AK16" s="131" t="n">
         <v>0.0219957544521249</v>
       </c>
-      <c r="AL16" s="130" t="n">
+      <c r="AL16" s="131" t="n">
         <v>0.0238771418471687</v>
       </c>
-      <c r="AM16" s="130" t="n">
+      <c r="AM16" s="131" t="n">
         <v>0.0222560177966233</v>
       </c>
-      <c r="AN16" s="130" t="n">
+      <c r="AN16" s="131" t="n">
         <v>0.0304048442102802</v>
       </c>
-      <c r="AO16" s="130" t="n">
+      <c r="AO16" s="131" t="n">
         <v>0.0234501395156037</v>
       </c>
-      <c r="AP16" s="130" t="n">
+      <c r="AP16" s="131" t="n">
         <v>0.0273449541199188</v>
       </c>
-      <c r="AQ16" s="130" t="n">
+      <c r="AQ16" s="131" t="n">
         <v>0.0313517805843389</v>
       </c>
-      <c r="AR16" s="130" t="n">
+      <c r="AR16" s="131" t="n">
         <v>0.0239266795531343</v>
       </c>
-      <c r="AS16" s="130" t="n">
+      <c r="AS16" s="131" t="n">
         <v>0.0281739975676316</v>
       </c>
-      <c r="AT16" s="130" t="n">
+      <c r="AT16" s="131" t="n">
         <v>0.0311610077423845</v>
       </c>
-      <c r="AU16" s="130" t="n">
+      <c r="AU16" s="131" t="n">
         <v>0.0308477022617903</v>
       </c>
-      <c r="AV16" s="130" t="n">
+      <c r="AV16" s="131" t="n">
         <v>0.0316483850457941</v>
       </c>
-      <c r="AW16" s="130" t="n">
+      <c r="AW16" s="131" t="n">
         <v>0.0352018733109614</v>
       </c>
-      <c r="AX16" s="130" t="n">
+      <c r="AX16" s="131" t="n">
         <v>0.0338062226498551</v>
       </c>
-      <c r="AY16" s="130" t="n">
+      <c r="AY16" s="131" t="n">
         <v>0.0283612087681158</v>
       </c>
-      <c r="AZ16" s="130" t="n">
+      <c r="AZ16" s="131" t="n">
         <v>0.0347042922971622</v>
       </c>
-      <c r="BA16" s="130" t="n">
+      <c r="BA16" s="131" t="n">
         <v>0.0336080253600485</v>
       </c>
-      <c r="BB16" s="130" t="n">
+      <c r="BB16" s="131" t="n">
         <v>0.0288311473737704</v>
       </c>
-      <c r="BC16" s="130" t="n">
+      <c r="BC16" s="131" t="n">
         <v>0.0339121786831189</v>
       </c>
-      <c r="BD16" s="130" t="n">
+      <c r="BD16" s="131" t="n">
         <v>0.035154369362916</v>
       </c>
-      <c r="BE16" s="130" t="n">
+      <c r="BE16" s="131" t="n">
         <v>0.0337287672780458</v>
       </c>
-      <c r="BF16" s="130" t="n">
+      <c r="BF16" s="131" t="n">
         <v>0.0323852694269048</v>
       </c>
-      <c r="BG16" s="129" t="n">
+      <c r="BG16" s="130" t="n">
         <v>0.038152081439356</v>
       </c>
-      <c r="BH16" s="131" t="n">
+      <c r="BH16" s="132" t="n">
         <v>0.0310007566671126</v>
       </c>
-      <c r="BI16" s="131" t="n">
+      <c r="BI16" s="132" t="n">
         <v>0.0352778341906694</v>
       </c>
-      <c r="BJ16" s="122" t="n">
+      <c r="BJ16" s="123" t="n">
         <v>0.0333548520372058</v>
       </c>
-      <c r="BK16" s="122" t="n">
+      <c r="BK16" s="123" t="n">
         <v>0.0354977097069578</v>
       </c>
-      <c r="BL16" s="122" t="n">
+      <c r="BL16" s="123" t="n">
         <v>0.0406266685690652</v>
       </c>
-      <c r="BM16" s="122" t="n">
+      <c r="BM16" s="123" t="n">
         <v>0.0301259338379975</v>
       </c>
-      <c r="BN16" s="122" t="n">
+      <c r="BN16" s="123" t="n">
         <v>0.0293395319537318</v>
       </c>
-      <c r="BO16" s="122" t="n">
+      <c r="BO16" s="123" t="n">
         <v>0.0293113092966426</v>
       </c>
-      <c r="BP16" s="122" t="n">
+      <c r="BP16" s="123" t="n">
         <v>0.0307687378255238</v>
       </c>
-      <c r="BQ16" s="122" t="n">
+      <c r="BQ16" s="123" t="n">
         <v>0.0262824275853042</v>
       </c>
-      <c r="BR16" s="122" t="n">
+      <c r="BR16" s="123" t="n">
         <v>0.0314175139750098</v>
       </c>
-      <c r="BS16" s="122" t="n">
+      <c r="BS16" s="123" t="n">
         <v>0.0320960527318201</v>
       </c>
-      <c r="BT16" s="122" t="n">
+      <c r="BT16" s="123" t="n">
         <v>0.0360706326556013</v>
       </c>
-      <c r="BU16" s="122" t="n">
+      <c r="BU16" s="123" t="n">
         <v>0.0314937217513565</v>
       </c>
-      <c r="BV16" s="122" t="n">
+      <c r="BV16" s="123" t="n">
         <v>0.0298211541427451</v>
       </c>
-      <c r="BW16" s="122" t="n">
+      <c r="BW16" s="123" t="n">
         <v>0.0295983999158013</v>
       </c>
-      <c r="BX16" s="123" t="n">
+      <c r="BX16" s="124" t="n">
         <v>0.0316199566888007</v>
       </c>
-      <c r="BY16" s="124" t="n">
+      <c r="BY16" s="125" t="n">
         <v>0.0319915952313056</v>
       </c>
     </row>
-    <row r="17" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="119" t="s">
+    <row r="17" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="129" t="n">
+      <c r="B17" s="130" t="n">
         <v>0.0505629994803284</v>
       </c>
-      <c r="C17" s="129" t="n">
+      <c r="C17" s="130" t="n">
         <v>0.0507735562284778</v>
       </c>
-      <c r="D17" s="129" t="n">
+      <c r="D17" s="130" t="n">
         <v>0.0475344520509508</v>
       </c>
-      <c r="E17" s="129" t="n">
+      <c r="E17" s="130" t="n">
         <v>0.0468038301402158</v>
       </c>
-      <c r="F17" s="129" t="n">
+      <c r="F17" s="130" t="n">
         <v>0.0501400534860111</v>
       </c>
-      <c r="G17" s="130" t="n">
+      <c r="G17" s="131" t="n">
         <v>0.049194825812599</v>
       </c>
-      <c r="H17" s="130" t="n">
+      <c r="H17" s="131" t="n">
         <v>0.0461250091461923</v>
       </c>
-      <c r="I17" s="130" t="n">
+      <c r="I17" s="131" t="n">
         <v>0.0406650345038263</v>
       </c>
-      <c r="J17" s="130" t="n">
+      <c r="J17" s="131" t="n">
         <v>0.0380219923692012</v>
       </c>
-      <c r="K17" s="130" t="n">
+      <c r="K17" s="131" t="n">
         <v>0.0366987022170273</v>
       </c>
-      <c r="L17" s="130" t="n">
+      <c r="L17" s="131" t="n">
         <v>0.0346347230760813</v>
       </c>
-      <c r="M17" s="130" t="n">
+      <c r="M17" s="131" t="n">
         <v>0.0339332556397922</v>
       </c>
-      <c r="N17" s="130" t="n">
+      <c r="N17" s="131" t="n">
         <v>0.0344360487547068</v>
       </c>
-      <c r="O17" s="130" t="n">
+      <c r="O17" s="131" t="n">
         <v>0.0341399619650503</v>
       </c>
-      <c r="P17" s="130" t="n">
+      <c r="P17" s="131" t="n">
         <v>0.0334780618239589</v>
       </c>
-      <c r="Q17" s="130" t="n">
+      <c r="Q17" s="131" t="n">
         <v>0.034597553674507</v>
       </c>
-      <c r="R17" s="130" t="n">
+      <c r="R17" s="131" t="n">
         <v>0.0343325517058383</v>
       </c>
-      <c r="S17" s="130" t="n">
+      <c r="S17" s="131" t="n">
         <v>0.0318672078290017</v>
       </c>
-      <c r="T17" s="130" t="n">
+      <c r="T17" s="131" t="n">
         <v>0.0332386800437392</v>
       </c>
-      <c r="U17" s="130" t="n">
+      <c r="U17" s="131" t="n">
         <v>0.0344260728906789</v>
       </c>
-      <c r="V17" s="130" t="n">
+      <c r="V17" s="131" t="n">
         <v>0.0339437454125677</v>
       </c>
-      <c r="W17" s="130" t="n">
+      <c r="W17" s="131" t="n">
         <v>0.0337569242232007</v>
       </c>
-      <c r="X17" s="130" t="n">
+      <c r="X17" s="131" t="n">
         <v>0.0351058300250706</v>
       </c>
-      <c r="Y17" s="130" t="n">
+      <c r="Y17" s="131" t="n">
         <v>0.0327441914731409</v>
       </c>
-      <c r="Z17" s="130" t="n">
+      <c r="Z17" s="131" t="n">
         <v>0.0329864105594065</v>
       </c>
-      <c r="AA17" s="130" t="n">
+      <c r="AA17" s="131" t="n">
         <v>0.0322933496798065</v>
       </c>
-      <c r="AB17" s="130" t="n">
+      <c r="AB17" s="131" t="n">
         <v>0.0333021778202374</v>
       </c>
-      <c r="AC17" s="130" t="n">
+      <c r="AC17" s="131" t="n">
         <v>0.0321303718901925</v>
       </c>
-      <c r="AD17" s="130" t="n">
+      <c r="AD17" s="131" t="n">
         <v>0.0329508929540616</v>
       </c>
-      <c r="AE17" s="130" t="n">
+      <c r="AE17" s="131" t="n">
         <v>0.0323423068779465</v>
       </c>
-      <c r="AF17" s="130" t="n">
+      <c r="AF17" s="131" t="n">
         <v>0.0305360859991586</v>
       </c>
-      <c r="AG17" s="130" t="n">
+      <c r="AG17" s="131" t="n">
         <v>0.0319051621581785</v>
       </c>
-      <c r="AH17" s="130" t="n">
+      <c r="AH17" s="131" t="n">
         <v>0.0341907984612276</v>
       </c>
-      <c r="AI17" s="130" t="n">
+      <c r="AI17" s="131" t="n">
         <v>0.033763537248881</v>
       </c>
-      <c r="AJ17" s="130" t="n">
+      <c r="AJ17" s="131" t="n">
         <v>0.0343181026965813</v>
       </c>
-      <c r="AK17" s="130" t="n">
+      <c r="AK17" s="131" t="n">
         <v>0.0325019167293664</v>
       </c>
-      <c r="AL17" s="130" t="n">
+      <c r="AL17" s="131" t="n">
         <v>0.0327548138404508</v>
       </c>
-      <c r="AM17" s="130" t="n">
+      <c r="AM17" s="131" t="n">
         <v>0.0360404283617235</v>
       </c>
-      <c r="AN17" s="130" t="n">
+      <c r="AN17" s="131" t="n">
         <v>0.0378752550562307</v>
       </c>
-      <c r="AO17" s="130" t="n">
+      <c r="AO17" s="131" t="n">
         <v>0.0369292409376806</v>
       </c>
-      <c r="AP17" s="130" t="n">
+      <c r="AP17" s="131" t="n">
         <v>0.035984761553132</v>
       </c>
-      <c r="AQ17" s="130" t="n">
+      <c r="AQ17" s="131" t="n">
         <v>0.0358382235855293</v>
       </c>
-      <c r="AR17" s="130" t="n">
+      <c r="AR17" s="131" t="n">
         <v>0.0363656860469494</v>
       </c>
-      <c r="AS17" s="130" t="n">
+      <c r="AS17" s="131" t="n">
         <v>0.0395253331777189</v>
       </c>
-      <c r="AT17" s="130" t="n">
+      <c r="AT17" s="131" t="n">
         <v>0.0403584098625879</v>
       </c>
-      <c r="AU17" s="130" t="n">
+      <c r="AU17" s="131" t="n">
         <v>0.0428750406737386</v>
       </c>
-      <c r="AV17" s="130" t="n">
+      <c r="AV17" s="131" t="n">
         <v>0.0445787940421031</v>
       </c>
-      <c r="AW17" s="130" t="n">
+      <c r="AW17" s="131" t="n">
         <v>0.0461403198942946</v>
       </c>
-      <c r="AX17" s="130" t="n">
+      <c r="AX17" s="131" t="n">
         <v>0.0434489993259619</v>
       </c>
-      <c r="AY17" s="130" t="n">
+      <c r="AY17" s="131" t="n">
         <v>0.0444405972360882</v>
       </c>
-      <c r="AZ17" s="130" t="n">
+      <c r="AZ17" s="131" t="n">
         <v>0.0441772625289381</v>
       </c>
-      <c r="BA17" s="130" t="n">
+      <c r="BA17" s="131" t="n">
         <v>0.0438926494734729</v>
       </c>
-      <c r="BB17" s="130" t="n">
+      <c r="BB17" s="131" t="n">
         <v>0.0461933404268779</v>
       </c>
-      <c r="BC17" s="130" t="n">
+      <c r="BC17" s="131" t="n">
         <v>0.046498901389683</v>
       </c>
-      <c r="BD17" s="130" t="n">
+      <c r="BD17" s="131" t="n">
         <v>0.0457830444343238</v>
       </c>
-      <c r="BE17" s="130" t="n">
+      <c r="BE17" s="131" t="n">
         <v>0.045671599404243</v>
       </c>
-      <c r="BF17" s="130" t="n">
+      <c r="BF17" s="131" t="n">
         <v>0.0423788805752563</v>
       </c>
-      <c r="BG17" s="129" t="n">
+      <c r="BG17" s="130" t="n">
         <v>0.0467251574692902</v>
       </c>
-      <c r="BH17" s="131" t="n">
+      <c r="BH17" s="132" t="n">
         <v>0.0514542474786401</v>
       </c>
-      <c r="BI17" s="131" t="n">
+      <c r="BI17" s="132" t="n">
         <v>0.0478747483432454</v>
       </c>
-      <c r="BJ17" s="122" t="n">
+      <c r="BJ17" s="123" t="n">
         <v>0.0491820854092454</v>
       </c>
-      <c r="BK17" s="122" t="n">
+      <c r="BK17" s="123" t="n">
         <v>0.0514147744841589</v>
       </c>
-      <c r="BL17" s="122" t="n">
+      <c r="BL17" s="123" t="n">
         <v>0.0502957018060985</v>
       </c>
-      <c r="BM17" s="122" t="n">
+      <c r="BM17" s="123" t="n">
         <v>0.0499743500614917</v>
       </c>
-      <c r="BN17" s="122" t="n">
+      <c r="BN17" s="123" t="n">
         <v>0.0486123226464394</v>
       </c>
-      <c r="BO17" s="122" t="n">
+      <c r="BO17" s="123" t="n">
         <v>0.0477925539526288</v>
       </c>
-      <c r="BP17" s="122" t="n">
+      <c r="BP17" s="123" t="n">
         <v>0.0521562427911916</v>
       </c>
-      <c r="BQ17" s="122" t="n">
+      <c r="BQ17" s="123" t="n">
         <v>0.0448549555407939</v>
       </c>
-      <c r="BR17" s="122" t="n">
+      <c r="BR17" s="123" t="n">
         <v>0.0483905255443958</v>
       </c>
-      <c r="BS17" s="122" t="n">
+      <c r="BS17" s="123" t="n">
         <v>0.0502921456953818</v>
       </c>
-      <c r="BT17" s="122" t="n">
+      <c r="BT17" s="123" t="n">
         <v>0.0483783549616054</v>
       </c>
-      <c r="BU17" s="122" t="n">
+      <c r="BU17" s="123" t="n">
         <v>0.0476930729380514</v>
       </c>
-      <c r="BV17" s="122" t="n">
+      <c r="BV17" s="123" t="n">
         <v>0.0516307493877717</v>
       </c>
-      <c r="BW17" s="122" t="n">
+      <c r="BW17" s="123" t="n">
         <v>0.04581086487988</v>
       </c>
-      <c r="BX17" s="123" t="n">
+      <c r="BX17" s="124" t="n">
         <v>0.0466078714818981</v>
       </c>
-      <c r="BY17" s="124" t="n">
+      <c r="BY17" s="125" t="n">
         <v>0.0505735208995275</v>
       </c>
     </row>
-    <row r="18" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="119" t="s">
+    <row r="18" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="129" t="n">
+      <c r="B18" s="130" t="n">
         <v>0.0547948649298821</v>
       </c>
-      <c r="C18" s="129" t="n">
+      <c r="C18" s="130" t="n">
         <v>0.0508451392644476</v>
       </c>
-      <c r="D18" s="129" t="n">
+      <c r="D18" s="130" t="n">
         <v>0.0501471776242359</v>
       </c>
-      <c r="E18" s="129" t="n">
+      <c r="E18" s="130" t="n">
         <v>0.0496355585945543</v>
       </c>
-      <c r="F18" s="129" t="n">
+      <c r="F18" s="130" t="n">
         <v>0.0343190671288883</v>
       </c>
-      <c r="G18" s="130" t="n">
+      <c r="G18" s="131" t="n">
         <v>0.0483616099189231</v>
       </c>
-      <c r="H18" s="130" t="n">
+      <c r="H18" s="131" t="n">
         <v>0.0464710588023713</v>
       </c>
-      <c r="I18" s="130" t="n">
+      <c r="I18" s="131" t="n">
         <v>0.0466818556638984</v>
       </c>
-      <c r="J18" s="130" t="n">
+      <c r="J18" s="131" t="n">
         <v>0.0401875382341605</v>
       </c>
-      <c r="K18" s="130" t="n">
+      <c r="K18" s="131" t="n">
         <v>0.0432976547536016</v>
       </c>
-      <c r="L18" s="130" t="n">
+      <c r="L18" s="131" t="n">
         <v>0.0391391941142483</v>
       </c>
-      <c r="M18" s="130" t="n">
+      <c r="M18" s="131" t="n">
         <v>0.034928317467692</v>
       </c>
-      <c r="N18" s="130" t="n">
+      <c r="N18" s="131" t="n">
         <v>0.0400442648093148</v>
       </c>
-      <c r="O18" s="130" t="n">
+      <c r="O18" s="131" t="n">
         <v>0.0413735606359445</v>
       </c>
-      <c r="P18" s="130" t="n">
+      <c r="P18" s="131" t="n">
         <v>0.0411271142060117</v>
       </c>
-      <c r="Q18" s="130" t="n">
+      <c r="Q18" s="131" t="n">
         <v>0.0395842222639135</v>
       </c>
-      <c r="R18" s="130" t="n">
+      <c r="R18" s="131" t="n">
         <v>0.0342741265449172</v>
       </c>
-      <c r="S18" s="130" t="n">
+      <c r="S18" s="131" t="n">
         <v>0.0361794217834084</v>
       </c>
-      <c r="T18" s="130" t="n">
+      <c r="T18" s="131" t="n">
         <v>0.0411954175801543</v>
       </c>
-      <c r="U18" s="130" t="n">
+      <c r="U18" s="131" t="n">
         <v>0.0403668680823982</v>
       </c>
-      <c r="V18" s="130" t="n">
+      <c r="V18" s="131" t="n">
         <v>0.0387524574136461</v>
       </c>
-      <c r="W18" s="130" t="n">
+      <c r="W18" s="131" t="n">
         <v>0.0359412494653555</v>
       </c>
-      <c r="X18" s="130" t="n">
+      <c r="X18" s="131" t="n">
         <v>0.0310797295954616</v>
       </c>
-      <c r="Y18" s="130" t="n">
+      <c r="Y18" s="131" t="n">
         <v>0.0377972904266783</v>
       </c>
-      <c r="Z18" s="130" t="n">
+      <c r="Z18" s="131" t="n">
         <v>0.0347350220749717</v>
       </c>
-      <c r="AA18" s="130" t="n">
+      <c r="AA18" s="131" t="n">
         <v>0.0372574610150604</v>
       </c>
-      <c r="AB18" s="130" t="n">
+      <c r="AB18" s="131" t="n">
         <v>0.0357723289591397</v>
       </c>
-      <c r="AC18" s="130" t="n">
+      <c r="AC18" s="131" t="n">
         <v>0.0315821594518996</v>
       </c>
-      <c r="AD18" s="130" t="n">
+      <c r="AD18" s="131" t="n">
         <v>0.0331796503257987</v>
       </c>
-      <c r="AE18" s="130" t="n">
+      <c r="AE18" s="131" t="n">
         <v>0.0354444594969558</v>
       </c>
-      <c r="AF18" s="130" t="n">
+      <c r="AF18" s="131" t="n">
         <v>0.0325919162164511</v>
       </c>
-      <c r="AG18" s="130" t="n">
+      <c r="AG18" s="131" t="n">
         <v>0.0335810316825394</v>
       </c>
-      <c r="AH18" s="130" t="n">
+      <c r="AH18" s="131" t="n">
         <v>0.0320064316325723</v>
       </c>
-      <c r="AI18" s="130" t="n">
+      <c r="AI18" s="131" t="n">
         <v>0.0355077465202679</v>
       </c>
-      <c r="AJ18" s="130" t="n">
+      <c r="AJ18" s="131" t="n">
         <v>0.0292710039909771</v>
       </c>
-      <c r="AK18" s="130" t="n">
+      <c r="AK18" s="131" t="n">
         <v>0.0249008984503143</v>
       </c>
-      <c r="AL18" s="130" t="n">
+      <c r="AL18" s="131" t="n">
         <v>0.0419443033419002</v>
       </c>
-      <c r="AM18" s="130" t="n">
+      <c r="AM18" s="131" t="n">
         <v>0.0351693054695651</v>
       </c>
-      <c r="AN18" s="130" t="n">
+      <c r="AN18" s="131" t="n">
         <v>0.0423088626895875</v>
       </c>
-      <c r="AO18" s="130" t="n">
+      <c r="AO18" s="131" t="n">
         <v>0.0340638210911702</v>
       </c>
-      <c r="AP18" s="130" t="n">
+      <c r="AP18" s="131" t="n">
         <v>0.0384789345424069</v>
       </c>
-      <c r="AQ18" s="130" t="n">
+      <c r="AQ18" s="131" t="n">
         <v>0.039242838330402</v>
       </c>
-      <c r="AR18" s="130" t="n">
+      <c r="AR18" s="131" t="n">
         <v>0.0424210079384822</v>
       </c>
-      <c r="AS18" s="130" t="n">
+      <c r="AS18" s="131" t="n">
         <v>0.0424679607384854</v>
       </c>
-      <c r="AT18" s="130" t="n">
+      <c r="AT18" s="131" t="n">
         <v>0.0436837407302664</v>
       </c>
-      <c r="AU18" s="130" t="n">
+      <c r="AU18" s="131" t="n">
         <v>0.0383424110721431</v>
       </c>
-      <c r="AV18" s="130" t="n">
+      <c r="AV18" s="131" t="n">
         <v>0.0451089171244734</v>
       </c>
-      <c r="AW18" s="130" t="n">
+      <c r="AW18" s="131" t="n">
         <v>0.0399535799314595</v>
       </c>
-      <c r="AX18" s="130" t="n">
+      <c r="AX18" s="131" t="n">
         <v>0.0478519552600622</v>
       </c>
-      <c r="AY18" s="130" t="n">
+      <c r="AY18" s="131" t="n">
         <v>0.0440635961336466</v>
       </c>
-      <c r="AZ18" s="130" t="n">
+      <c r="AZ18" s="131" t="n">
         <v>0.049614969155119</v>
       </c>
-      <c r="BA18" s="130" t="n">
+      <c r="BA18" s="131" t="n">
         <v>0.0474216219058021</v>
       </c>
-      <c r="BB18" s="130" t="n">
+      <c r="BB18" s="131" t="n">
         <v>0.0490080137394824</v>
       </c>
-      <c r="BC18" s="130" t="n">
+      <c r="BC18" s="131" t="n">
         <v>0.0468798244508864</v>
       </c>
-      <c r="BD18" s="130" t="n">
+      <c r="BD18" s="131" t="n">
         <v>0.0484229771317165</v>
       </c>
-      <c r="BE18" s="130" t="n">
+      <c r="BE18" s="131" t="n">
         <v>0.044183201366803</v>
       </c>
-      <c r="BF18" s="130" t="n">
+      <c r="BF18" s="131" t="n">
         <v>0.0480756433404024</v>
       </c>
-      <c r="BG18" s="129" t="n">
+      <c r="BG18" s="130" t="n">
         <v>0.0485934545043024</v>
       </c>
-      <c r="BH18" s="131" t="n">
+      <c r="BH18" s="132" t="n">
         <v>0.0364603579504658</v>
       </c>
-      <c r="BI18" s="131" t="n">
+      <c r="BI18" s="132" t="n">
         <v>0.0324462607280142</v>
       </c>
-      <c r="BJ18" s="122" t="n">
+      <c r="BJ18" s="123" t="n">
         <v>0.0518576211975192</v>
       </c>
-      <c r="BK18" s="122" t="n">
+      <c r="BK18" s="123" t="n">
         <v>0.0424699919610045</v>
       </c>
-      <c r="BL18" s="122" t="n">
+      <c r="BL18" s="123" t="n">
         <v>0.051341496739351</v>
       </c>
-      <c r="BM18" s="122" t="n">
+      <c r="BM18" s="123" t="n">
         <v>0.0483972352692278</v>
       </c>
-      <c r="BN18" s="122" t="n">
+      <c r="BN18" s="123" t="n">
         <v>0.0525760235936711</v>
       </c>
-      <c r="BO18" s="122" t="n">
+      <c r="BO18" s="123" t="n">
         <v>0.0525235334283048</v>
       </c>
-      <c r="BP18" s="122" t="n">
+      <c r="BP18" s="123" t="n">
         <v>0.0507074572851218</v>
       </c>
-      <c r="BQ18" s="122" t="n">
+      <c r="BQ18" s="123" t="n">
         <v>0.0541708357268169</v>
       </c>
-      <c r="BR18" s="122" t="n">
+      <c r="BR18" s="123" t="n">
         <v>0.0356218442726341</v>
       </c>
-      <c r="BS18" s="122" t="n">
+      <c r="BS18" s="123" t="n">
         <v>0.0490793287594674</v>
       </c>
-      <c r="BT18" s="122" t="n">
+      <c r="BT18" s="123" t="n">
         <v>0.0535073732615466</v>
       </c>
-      <c r="BU18" s="122" t="n">
+      <c r="BU18" s="123" t="n">
         <v>0.0479066871132758</v>
       </c>
-      <c r="BV18" s="122" t="n">
+      <c r="BV18" s="123" t="n">
         <v>0.037327080158145</v>
       </c>
-      <c r="BW18" s="122" t="n">
+      <c r="BW18" s="123" t="n">
         <v>0.0511086925426924</v>
       </c>
-      <c r="BX18" s="123" t="n">
+      <c r="BX18" s="124" t="n">
         <v>0.0456178672736924</v>
       </c>
-      <c r="BY18" s="124" t="n">
+      <c r="BY18" s="125" t="n">
         <v>0.0499581232277786</v>
       </c>
     </row>
-    <row r="19" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="119" t="s">
+    <row r="19" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="129" t="n">
+      <c r="B19" s="130" t="n">
         <v>0.0610650378806912</v>
       </c>
-      <c r="C19" s="129" t="n">
+      <c r="C19" s="130" t="n">
         <v>0.0584524981281657</v>
       </c>
-      <c r="D19" s="129" t="n">
+      <c r="D19" s="130" t="n">
         <v>0.057743238057482</v>
       </c>
-      <c r="E19" s="129" t="n">
+      <c r="E19" s="130" t="n">
         <v>0.0568431662429868</v>
       </c>
-      <c r="F19" s="129" t="n">
+      <c r="F19" s="130" t="n">
         <v>0.0574625785071403</v>
       </c>
-      <c r="G19" s="130" t="n">
+      <c r="G19" s="131" t="n">
         <v>0.0545094231677192</v>
       </c>
-      <c r="H19" s="130" t="n">
+      <c r="H19" s="131" t="n">
         <v>0.0542107087764456</v>
       </c>
-      <c r="I19" s="130" t="n">
+      <c r="I19" s="131" t="n">
         <v>0.0464645443350768</v>
       </c>
-      <c r="J19" s="130" t="n">
+      <c r="J19" s="131" t="n">
         <v>0.0457660954439224</v>
       </c>
-      <c r="K19" s="130" t="n">
+      <c r="K19" s="131" t="n">
         <v>0.0493420170031218</v>
       </c>
-      <c r="L19" s="130" t="n">
+      <c r="L19" s="131" t="n">
         <v>0.0456820625523481</v>
       </c>
-      <c r="M19" s="130" t="n">
+      <c r="M19" s="131" t="n">
         <v>0.0435879299910559</v>
       </c>
-      <c r="N19" s="130" t="n">
+      <c r="N19" s="131" t="n">
         <v>0.0460111272020561</v>
       </c>
-      <c r="O19" s="130" t="n">
+      <c r="O19" s="131" t="n">
         <v>0.0420702871556565</v>
       </c>
-      <c r="P19" s="130" t="n">
+      <c r="P19" s="131" t="n">
         <v>0.0448769425046264</v>
       </c>
-      <c r="Q19" s="130" t="n">
+      <c r="Q19" s="131" t="n">
         <v>0.0448824295955372</v>
       </c>
-      <c r="R19" s="130" t="n">
+      <c r="R19" s="131" t="n">
         <v>0.0425979813609684</v>
       </c>
-      <c r="S19" s="130" t="n">
+      <c r="S19" s="131" t="n">
         <v>0.0426435970785867</v>
       </c>
-      <c r="T19" s="130" t="n">
+      <c r="T19" s="131" t="n">
         <v>0.0405653762656237</v>
       </c>
-      <c r="U19" s="130" t="n">
+      <c r="U19" s="131" t="n">
         <v>0.0393414190463612</v>
       </c>
-      <c r="V19" s="130" t="n">
+      <c r="V19" s="131" t="n">
         <v>0.0407575365915481</v>
       </c>
-      <c r="W19" s="130" t="n">
+      <c r="W19" s="131" t="n">
         <v>0.0431278121045595</v>
       </c>
-      <c r="X19" s="130" t="n">
+      <c r="X19" s="131" t="n">
         <v>0.0409138831219735</v>
       </c>
-      <c r="Y19" s="130" t="n">
+      <c r="Y19" s="131" t="n">
         <v>0.0391094164135183</v>
       </c>
-      <c r="Z19" s="130" t="n">
+      <c r="Z19" s="131" t="n">
         <v>0.0425689559290601</v>
       </c>
-      <c r="AA19" s="130" t="n">
+      <c r="AA19" s="131" t="n">
         <v>0.0428313793800398</v>
       </c>
-      <c r="AB19" s="130" t="n">
+      <c r="AB19" s="131" t="n">
         <v>0.0446832610245461</v>
       </c>
-      <c r="AC19" s="130" t="n">
+      <c r="AC19" s="131" t="n">
         <v>0.0422282628682572</v>
       </c>
-      <c r="AD19" s="130" t="n">
+      <c r="AD19" s="131" t="n">
         <v>0.0426415145862303</v>
       </c>
-      <c r="AE19" s="130" t="n">
+      <c r="AE19" s="131" t="n">
         <v>0.0406189963999518</v>
       </c>
-      <c r="AF19" s="130" t="n">
+      <c r="AF19" s="131" t="n">
         <v>0.0412922029244264</v>
       </c>
-      <c r="AG19" s="130" t="n">
+      <c r="AG19" s="131" t="n">
         <v>0.0393663831850398</v>
       </c>
-      <c r="AH19" s="130" t="n">
+      <c r="AH19" s="131" t="n">
         <v>0.0441801353956996</v>
       </c>
-      <c r="AI19" s="130" t="n">
+      <c r="AI19" s="131" t="n">
         <v>0.0424604142988056</v>
       </c>
-      <c r="AJ19" s="130" t="n">
+      <c r="AJ19" s="131" t="n">
         <v>0.0431812291381447</v>
       </c>
-      <c r="AK19" s="130" t="n">
+      <c r="AK19" s="131" t="n">
         <v>0.0442797967808364</v>
       </c>
-      <c r="AL19" s="130" t="n">
+      <c r="AL19" s="131" t="n">
         <v>0.0424663659583155</v>
       </c>
-      <c r="AM19" s="130" t="n">
+      <c r="AM19" s="131" t="n">
         <v>0.0448496353622489</v>
       </c>
-      <c r="AN19" s="130" t="n">
+      <c r="AN19" s="131" t="n">
         <v>0.0466130272559623</v>
       </c>
-      <c r="AO19" s="130" t="n">
+      <c r="AO19" s="131" t="n">
         <v>0.0460399997945627</v>
       </c>
-      <c r="AP19" s="130" t="n">
+      <c r="AP19" s="131" t="n">
         <v>0.0462426302253728</v>
       </c>
-      <c r="AQ19" s="130" t="n">
+      <c r="AQ19" s="131" t="n">
         <v>0.0458842279142401</v>
       </c>
-      <c r="AR19" s="130" t="n">
+      <c r="AR19" s="131" t="n">
         <v>0.0483129709564263</v>
       </c>
-      <c r="AS19" s="130" t="n">
+      <c r="AS19" s="131" t="n">
         <v>0.047013667415196</v>
       </c>
-      <c r="AT19" s="130" t="n">
+      <c r="AT19" s="131" t="n">
         <v>0.0481142982228072</v>
       </c>
-      <c r="AU19" s="130" t="n">
+      <c r="AU19" s="131" t="n">
         <v>0.0500477773012542</v>
       </c>
-      <c r="AV19" s="130" t="n">
+      <c r="AV19" s="131" t="n">
         <v>0.0498083788414103</v>
       </c>
-      <c r="AW19" s="130" t="n">
+      <c r="AW19" s="131" t="n">
         <v>0.0512173520801304</v>
       </c>
-      <c r="AX19" s="130" t="n">
+      <c r="AX19" s="131" t="n">
         <v>0.0508326825258858</v>
       </c>
-      <c r="AY19" s="130" t="n">
+      <c r="AY19" s="131" t="n">
         <v>0.0514152776575037</v>
       </c>
-      <c r="AZ19" s="130" t="n">
+      <c r="AZ19" s="131" t="n">
         <v>0.0521961885802299</v>
       </c>
-      <c r="BA19" s="130" t="n">
+      <c r="BA19" s="131" t="n">
         <v>0.0528499885463457</v>
       </c>
-      <c r="BB19" s="130" t="n">
+      <c r="BB19" s="131" t="n">
         <v>0.0529986239648984</v>
       </c>
-      <c r="BC19" s="130" t="n">
+      <c r="BC19" s="131" t="n">
         <v>0.0525314785957938</v>
       </c>
-      <c r="BD19" s="130" t="n">
+      <c r="BD19" s="131" t="n">
         <v>0.0548228305437701</v>
       </c>
-      <c r="BE19" s="130" t="n">
+      <c r="BE19" s="131" t="n">
         <v>0.0533551117295187</v>
       </c>
-      <c r="BF19" s="130" t="n">
+      <c r="BF19" s="131" t="n">
         <v>0.056491353126099</v>
       </c>
-      <c r="BG19" s="129" t="n">
+      <c r="BG19" s="130" t="n">
         <v>0.0545103722564248</v>
       </c>
-      <c r="BH19" s="131" t="n">
+      <c r="BH19" s="132" t="n">
         <v>0.0551777585865637</v>
       </c>
-      <c r="BI19" s="131" t="n">
+      <c r="BI19" s="132" t="n">
         <v>0.0560993124668041</v>
       </c>
-      <c r="BJ19" s="122" t="n">
+      <c r="BJ19" s="123" t="n">
         <v>0.0539484222526481</v>
       </c>
-      <c r="BK19" s="122" t="n">
+      <c r="BK19" s="123" t="n">
         <v>0.0547858511619111</v>
       </c>
-      <c r="BL19" s="122" t="n">
+      <c r="BL19" s="123" t="n">
         <v>0.0496634345483148</v>
       </c>
-      <c r="BM19" s="122" t="n">
+      <c r="BM19" s="123" t="n">
         <v>0.057703109922406</v>
       </c>
-      <c r="BN19" s="122" t="n">
+      <c r="BN19" s="123" t="n">
         <v>0.0547245058059516</v>
       </c>
-      <c r="BO19" s="122" t="n">
+      <c r="BO19" s="123" t="n">
         <v>0.0572290468173482</v>
       </c>
-      <c r="BP19" s="122" t="n">
+      <c r="BP19" s="123" t="n">
         <v>0.0573824361508026</v>
       </c>
-      <c r="BQ19" s="122" t="n">
+      <c r="BQ19" s="123" t="n">
         <v>0.0578957018260516</v>
       </c>
-      <c r="BR19" s="122" t="n">
+      <c r="BR19" s="123" t="n">
         <v>0.054146024629313</v>
       </c>
-      <c r="BS19" s="122" t="n">
+      <c r="BS19" s="123" t="n">
         <v>0.0546969714032496</v>
       </c>
-      <c r="BT19" s="122" t="n">
+      <c r="BT19" s="123" t="n">
         <v>0.0560234234563151</v>
       </c>
-      <c r="BU19" s="122" t="n">
+      <c r="BU19" s="123" t="n">
         <v>0.0558223797889027</v>
       </c>
-      <c r="BV19" s="122" t="n">
+      <c r="BV19" s="123" t="n">
         <v>0.0556090935947218</v>
       </c>
-      <c r="BW19" s="122" t="n">
+      <c r="BW19" s="123" t="n">
         <v>0.053875436357975</v>
       </c>
-      <c r="BX19" s="123" t="n">
+      <c r="BX19" s="124" t="n">
         <v>0.0565587202291508</v>
       </c>
-      <c r="BY19" s="124" t="n">
+      <c r="BY19" s="125" t="n">
         <v>0.0574703299376629</v>
       </c>
     </row>
-    <row r="20" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="132" t="s">
+    <row r="20" s="103" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="133" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="133" t="n">
+      <c r="B20" s="134" t="n">
         <v>0.0697773143112962</v>
       </c>
-      <c r="C20" s="133" t="n">
+      <c r="C20" s="134" t="n">
         <v>0.0677243159350208</v>
       </c>
-      <c r="D20" s="133" t="n">
+      <c r="D20" s="134" t="n">
         <v>0.0664071399013448</v>
       </c>
-      <c r="E20" s="133" t="n">
+      <c r="E20" s="134" t="n">
         <v>0.066933871136213</v>
       </c>
-      <c r="F20" s="133" t="n">
+      <c r="F20" s="134" t="n">
         <v>0.0638642642484444</v>
       </c>
-      <c r="G20" s="134" t="n">
+      <c r="G20" s="135" t="n">
         <v>0.0672491819095636</v>
       </c>
-      <c r="H20" s="134" t="n">
+      <c r="H20" s="135" t="n">
         <v>0.0622578334195745</v>
       </c>
-      <c r="I20" s="134" t="n">
+      <c r="I20" s="135" t="n">
         <v>0.0626413345929634</v>
       </c>
-      <c r="J20" s="134" t="n">
+      <c r="J20" s="135" t="n">
         <v>0.0569966530176066</v>
       </c>
-      <c r="K20" s="134" t="n">
+      <c r="K20" s="135" t="n">
         <v>0.0549524018459611</v>
       </c>
-      <c r="L20" s="134" t="n">
+      <c r="L20" s="135" t="n">
         <v>0.0517748366270869</v>
       </c>
-      <c r="M20" s="134" t="n">
+      <c r="M20" s="135" t="n">
         <v>0.0558380124349161</v>
       </c>
-      <c r="N20" s="134" t="n">
+      <c r="N20" s="135" t="n">
         <v>0.0511255240981654</v>
       </c>
-      <c r="O20" s="134" t="n">
+      <c r="O20" s="135" t="n">
         <v>0.0557844272253703</v>
       </c>
-      <c r="P20" s="134" t="n">
+      <c r="P20" s="135" t="n">
         <v>0.0546935439787142</v>
       </c>
-      <c r="Q20" s="134" t="n">
+      <c r="Q20" s="135" t="n">
         <v>0.0561842325508118</v>
       </c>
-      <c r="R20" s="134" t="n">
+      <c r="R20" s="135" t="n">
         <v>0.0547607082515897</v>
       </c>
-      <c r="S20" s="134" t="n">
+      <c r="S20" s="135" t="n">
         <v>0.0511823675627279</v>
       </c>
-      <c r="T20" s="134" t="n">
+      <c r="T20" s="135" t="n">
         <v>0.0555968639756272</v>
       </c>
-      <c r="U20" s="134" t="n">
+      <c r="U20" s="135" t="n">
         <v>0.0549636828110589</v>
       </c>
-      <c r="V20" s="134" t="n">
+      <c r="V20" s="135" t="n">
         <v>0.0531824756387832</v>
       </c>
-      <c r="W20" s="134" t="n">
+      <c r="W20" s="135" t="n">
         <v>0.0514612299687673</v>
       </c>
-      <c r="X20" s="134" t="n">
+      <c r="X20" s="135" t="n">
         <v>0.0545086387849261</v>
       </c>
-      <c r="Y20" s="134" t="n">
+      <c r="Y20" s="135" t="n">
         <v>0.0510760735884514</v>
       </c>
-      <c r="Z20" s="134" t="n">
+      <c r="Z20" s="135" t="n">
         <v>0.0493655087167514</v>
       </c>
-      <c r="AA20" s="134" t="n">
+      <c r="AA20" s="135" t="n">
         <v>0.0472474551784698</v>
       </c>
-      <c r="AB20" s="134" t="n">
+      <c r="AB20" s="135" t="n">
         <v>0.0524553667211598</v>
       </c>
-      <c r="AC20" s="134" t="n">
+      <c r="AC20" s="135" t="n">
         <v>0.0494770449300324</v>
       </c>
-      <c r="AD20" s="134" t="n">
+      <c r="AD20" s="135" t="n">
         <v>0.0514865065965193</v>
       </c>
-      <c r="AE20" s="134" t="n">
+      <c r="AE20" s="135" t="n">
         <v>0.0505761733580886</v>
       </c>
-      <c r="AF20" s="134" t="n">
+      <c r="AF20" s="135" t="n">
         <v>0.0504352013341369</v>
       </c>
-      <c r="AG20" s="134" t="n">
+      <c r="AG20" s="135" t="n">
         <v>0.0498441364115754</v>
       </c>
-      <c r="AH20" s="134" t="n">
+      <c r="AH20" s="135" t="n">
         <v>0.0513546004232994</v>
       </c>
-      <c r="AI20" s="134" t="n">
+      <c r="AI20" s="135" t="n">
         <v>0.0534712094139359</v>
       </c>
-      <c r="AJ20" s="134" t="n">
+      <c r="AJ20" s="135" t="n">
         <v>0.0553708427500036</v>
       </c>
-      <c r="AK20" s="134" t="n">
+      <c r="AK20" s="135" t="n">
         <v>0.0451310129525746</v>
       </c>
-      <c r="AL20" s="134" t="n">
+      <c r="AL20" s="135" t="n">
         <v>0.0413096498704529</v>
       </c>
-      <c r="AM20" s="134" t="n">
+      <c r="AM20" s="135" t="n">
         <v>0.0517766664798769</v>
       </c>
-      <c r="AN20" s="134" t="n">
+      <c r="AN20" s="135" t="n">
         <v>0.054325299514295</v>
       </c>
-      <c r="AO20" s="134" t="n">
+      <c r="AO20" s="135" t="n">
         <v>0.0534167013461358</v>
       </c>
-      <c r="AP20" s="134" t="n">
+      <c r="AP20" s="135" t="n">
         <v>0.0548244978683724</v>
       </c>
-      <c r="AQ20" s="134" t="n">
+      <c r="AQ20" s="135" t="n">
         <v>0.0446726112873665</v>
       </c>
-      <c r="AR20" s="134" t="n">
+      <c r="AR20" s="135" t="n">
         <v>0.0534483310768196</v>
       </c>
-      <c r="AS20" s="134" t="n">
+      <c r="AS20" s="135" t="n">
         <v>0.0560752931919051</v>
       </c>
-      <c r="AT20" s="134" t="n">
+      <c r="AT20" s="135" t="n">
         <v>0.0548278760886616</v>
       </c>
-      <c r="AU20" s="134" t="n">
+      <c r="AU20" s="135" t="n">
         <v>0.0594546733732836</v>
       </c>
-      <c r="AV20" s="134" t="n">
+      <c r="AV20" s="135" t="n">
         <v>0.0595028559406303</v>
       </c>
-      <c r="AW20" s="134" t="n">
+      <c r="AW20" s="135" t="n">
         <v>0.0608931367930669</v>
       </c>
-      <c r="AX20" s="134" t="n">
+      <c r="AX20" s="135" t="n">
         <v>0.0613512110833654</v>
       </c>
-      <c r="AY20" s="134" t="n">
+      <c r="AY20" s="135" t="n">
         <v>0.0529139925959094</v>
       </c>
-      <c r="AZ20" s="134" t="n">
+      <c r="AZ20" s="135" t="n">
         <v>0.0623941928416833</v>
       </c>
-      <c r="BA20" s="134" t="n">
+      <c r="BA20" s="135" t="n">
         <v>0.0516738622310663</v>
       </c>
-      <c r="BB20" s="134" t="n">
+      <c r="BB20" s="135" t="n">
         <v>0.0621237019515291</v>
       </c>
-      <c r="BC20" s="134" t="n">
+      <c r="BC20" s="135" t="n">
         <v>0.0609314983490892</v>
       </c>
-      <c r="BD20" s="134" t="n">
+      <c r="BD20" s="135" t="n">
         <v>0.0626104251086402</v>
       </c>
-      <c r="BE20" s="134" t="n">
+      <c r="BE20" s="135" t="n">
         <v>0.0631338973578006</v>
       </c>
-      <c r="BF20" s="134" t="n">
+      <c r="BF20" s="135" t="n">
         <v>0.063526914560412</v>
       </c>
-      <c r="BG20" s="133" t="n">
+      <c r="BG20" s="134" t="n">
         <v>0.0603512997521992</v>
       </c>
-      <c r="BH20" s="135" t="n">
+      <c r="BH20" s="136" t="n">
         <v>0.0622268412736933</v>
       </c>
-      <c r="BI20" s="135" t="n">
+      <c r="BI20" s="136" t="n">
         <v>0.0616680051356843</v>
       </c>
-      <c r="BJ20" s="122" t="n">
+      <c r="BJ20" s="123" t="n">
         <v>0.0612376114881655</v>
       </c>
-      <c r="BK20" s="122" t="n">
+      <c r="BK20" s="123" t="n">
         <v>0.0659201615558739</v>
       </c>
-      <c r="BL20" s="122" t="n">
+      <c r="BL20" s="123" t="n">
         <v>0.0649618277242754</v>
       </c>
-      <c r="BM20" s="122" t="n">
+      <c r="BM20" s="123" t="n">
         <v>0.0634590538496245</v>
       </c>
-      <c r="BN20" s="122" t="n">
+      <c r="BN20" s="123" t="n">
         <v>0.0619745018028106</v>
       </c>
-      <c r="BO20" s="122" t="n">
+      <c r="BO20" s="123" t="n">
         <v>0.0611429547907256</v>
       </c>
-      <c r="BP20" s="122" t="n">
+      <c r="BP20" s="123" t="n">
         <v>0.0611462919551358</v>
       </c>
-      <c r="BQ20" s="122" t="n">
+      <c r="BQ20" s="123" t="n">
         <v>0.065053130072798</v>
       </c>
-      <c r="BR20" s="122" t="n">
+      <c r="BR20" s="123" t="n">
         <v>0.060269544804364</v>
       </c>
-      <c r="BS20" s="122" t="n">
+      <c r="BS20" s="123" t="n">
         <v>0.0626545753112138</v>
       </c>
-      <c r="BT20" s="122" t="n">
+      <c r="BT20" s="123" t="n">
         <v>0.0635676667509203</v>
       </c>
-      <c r="BU20" s="122" t="n">
+      <c r="BU20" s="123" t="n">
         <v>0.0611406364033097</v>
       </c>
-      <c r="BV20" s="122" t="n">
+      <c r="BV20" s="123" t="n">
         <v>0.0610596164435778</v>
       </c>
-      <c r="BW20" s="122" t="n">
+      <c r="BW20" s="123" t="n">
         <v>0.0632140193813563</v>
       </c>
-      <c r="BX20" s="123" t="n">
+      <c r="BX20" s="124" t="n">
         <v>0.0626972395635916</v>
       </c>
-      <c r="BY20" s="124" t="n">
+      <c r="BY20" s="125" t="n">
         <v>0.0629405167185035</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="136" t="s">
+      <c r="A21" s="137" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="137" t="n">
+      <c r="B21" s="138" t="n">
         <v>0.0473242274039947</v>
       </c>
-      <c r="C21" s="137" t="n">
+      <c r="C21" s="138" t="n">
         <v>0.0461929332190054</v>
       </c>
-      <c r="D21" s="137" t="n">
+      <c r="D21" s="138" t="n">
         <v>0.0440920752154815</v>
       </c>
-      <c r="E21" s="137" t="n">
+      <c r="E21" s="138" t="n">
         <v>0.0432202382393441</v>
       </c>
-      <c r="F21" s="137" t="n">
+      <c r="F21" s="138" t="n">
         <v>0.0436274118782642</v>
       </c>
-      <c r="G21" s="137" t="n">
+      <c r="G21" s="138" t="n">
         <v>0.0431587451861483</v>
       </c>
-      <c r="H21" s="137" t="n">
+      <c r="H21" s="138" t="n">
         <v>0.041659105209594</v>
       </c>
-      <c r="I21" s="137" t="n">
+      <c r="I21" s="138" t="n">
         <v>0.0379285516528471</v>
       </c>
-      <c r="J21" s="137" t="n">
+      <c r="J21" s="138" t="n">
         <v>0.0348902706856256</v>
       </c>
-      <c r="K21" s="137" t="n">
+      <c r="K21" s="138" t="n">
         <v>0.0357011291365187</v>
       </c>
-      <c r="L21" s="137" t="n">
+      <c r="L21" s="138" t="n">
         <v>0.0336731595901436</v>
       </c>
-      <c r="M21" s="137" t="n">
+      <c r="M21" s="138" t="n">
         <v>0.032607155947473</v>
       </c>
-      <c r="N21" s="137" t="n">
+      <c r="N21" s="138" t="n">
         <v>0.0331297226207967</v>
       </c>
-      <c r="O21" s="137" t="n">
+      <c r="O21" s="138" t="n">
         <v>0.0327036546944832</v>
       </c>
-      <c r="P21" s="137" t="n">
+      <c r="P21" s="138" t="n">
         <v>0.0330305624096397</v>
       </c>
-      <c r="Q21" s="137" t="n">
+      <c r="Q21" s="138" t="n">
         <v>0.0332035635886776</v>
       </c>
-      <c r="R21" s="137" t="n">
+      <c r="R21" s="138" t="n">
         <v>0.0325411733488781</v>
       </c>
-      <c r="S21" s="137" t="n">
+      <c r="S21" s="138" t="n">
         <v>0.0306073545897533</v>
       </c>
-      <c r="T21" s="137" t="n">
+      <c r="T21" s="138" t="n">
         <v>0.0321615993608287</v>
       </c>
-      <c r="U21" s="137" t="n">
+      <c r="U21" s="138" t="n">
         <v>0.031490928560051</v>
       </c>
-      <c r="V21" s="137" t="n">
+      <c r="V21" s="138" t="n">
         <v>0.0315875947043472</v>
       </c>
-      <c r="W21" s="137" t="n">
+      <c r="W21" s="138" t="n">
         <v>0.0324414371058717</v>
       </c>
-      <c r="X21" s="137" t="n">
+      <c r="X21" s="138" t="n">
         <v>0.0315370053061611</v>
       </c>
-      <c r="Y21" s="137" t="n">
+      <c r="Y21" s="138" t="n">
         <v>0.0308461680292614</v>
       </c>
-      <c r="Z21" s="137" t="n">
+      <c r="Z21" s="138" t="n">
         <v>0.0312041653342922</v>
       </c>
-      <c r="AA21" s="137" t="n">
+      <c r="AA21" s="138" t="n">
         <v>0.0309677628376067</v>
       </c>
-      <c r="AB21" s="137" t="n">
+      <c r="AB21" s="138" t="n">
         <v>0.0325615379260409</v>
       </c>
-      <c r="AC21" s="137" t="n">
+      <c r="AC21" s="138" t="n">
         <v>0.0305437373939358</v>
       </c>
-      <c r="AD21" s="137" t="n">
+      <c r="AD21" s="138" t="n">
         <v>0.0313383586224238</v>
       </c>
-      <c r="AE21" s="137" t="n">
+      <c r="AE21" s="138" t="n">
         <v>0.0303767635923207</v>
       </c>
-      <c r="AF21" s="137" t="n">
+      <c r="AF21" s="138" t="n">
         <v>0.0302267556370369</v>
       </c>
-      <c r="AG21" s="137" t="n">
+      <c r="AG21" s="138" t="n">
         <v>0.0301584695751926</v>
       </c>
-      <c r="AH21" s="137" t="n">
+      <c r="AH21" s="138" t="n">
         <v>0.0322854446657622</v>
       </c>
-      <c r="AI21" s="137" t="n">
+      <c r="AI21" s="138" t="n">
         <v>0.0320436300501972</v>
       </c>
-      <c r="AJ21" s="137" t="n">
+      <c r="AJ21" s="138" t="n">
         <v>0.032416440918079</v>
       </c>
-      <c r="AK21" s="137" t="n">
+      <c r="AK21" s="138" t="n">
         <v>0.0314552507680824</v>
       </c>
-      <c r="AL21" s="137" t="n">
+      <c r="AL21" s="138" t="n">
         <v>0.0311015428105571</v>
       </c>
-      <c r="AM21" s="137" t="n">
+      <c r="AM21" s="138" t="n">
         <v>0.0329477684480755</v>
       </c>
-      <c r="AN21" s="137" t="n">
+      <c r="AN21" s="138" t="n">
         <v>0.0355575425091701</v>
       </c>
-      <c r="AO21" s="137" t="n">
+      <c r="AO21" s="138" t="n">
         <v>0.0341589312594492</v>
       </c>
-      <c r="AP21" s="137" t="n">
+      <c r="AP21" s="138" t="n">
         <v>0.0344847168672771</v>
       </c>
-      <c r="AQ21" s="137" t="n">
+      <c r="AQ21" s="138" t="n">
         <v>0.0344557409576449</v>
       </c>
-      <c r="AR21" s="137" t="n">
+      <c r="AR21" s="138" t="n">
         <v>0.0351887071789874</v>
       </c>
-      <c r="AS21" s="137" t="n">
+      <c r="AS21" s="138" t="n">
         <v>0.0359983149112375</v>
       </c>
-      <c r="AT21" s="137" t="n">
+      <c r="AT21" s="138" t="n">
         <v>0.0368103583150335</v>
       </c>
-      <c r="AU21" s="137" t="n">
+      <c r="AU21" s="138" t="n">
         <v>0.0380950340167748</v>
       </c>
-      <c r="AV21" s="137" t="n">
+      <c r="AV21" s="138" t="n">
         <v>0.0391617026531068</v>
       </c>
-      <c r="AW21" s="137" t="n">
+      <c r="AW21" s="138" t="n">
         <v>0.0410103285542796</v>
       </c>
-      <c r="AX21" s="137" t="n">
+      <c r="AX21" s="138" t="n">
         <v>0.0399437161783858</v>
       </c>
-      <c r="AY21" s="137" t="n">
+      <c r="AY21" s="138" t="n">
         <v>0.0386148650664646</v>
       </c>
-      <c r="AZ21" s="138" t="n">
+      <c r="AZ21" s="139" t="n">
         <v>0.0404498901726038</v>
       </c>
-      <c r="BA21" s="138" t="n">
+      <c r="BA21" s="139" t="n">
         <v>0.0388663719456868</v>
       </c>
-      <c r="BB21" s="138" t="n">
+      <c r="BB21" s="139" t="n">
         <v>0.0404273103815348</v>
       </c>
-      <c r="BC21" s="138" t="n">
+      <c r="BC21" s="139" t="n">
         <v>0.0406163275058501</v>
       </c>
-      <c r="BD21" s="138" t="n">
+      <c r="BD21" s="139" t="n">
         <v>0.0420877310528428</v>
       </c>
-      <c r="BE21" s="138" t="n">
+      <c r="BE21" s="139" t="n">
         <v>0.0417405852469675</v>
       </c>
-      <c r="BF21" s="138" t="n">
+      <c r="BF21" s="139" t="n">
         <v>0.0420906239891241</v>
       </c>
-      <c r="BG21" s="137" t="n">
+      <c r="BG21" s="138" t="n">
         <v>0.0421012795959147</v>
       </c>
-      <c r="BH21" s="139" t="n">
+      <c r="BH21" s="140" t="n">
         <v>0.0433078192427392</v>
       </c>
-      <c r="BI21" s="139" t="n">
+      <c r="BI21" s="140" t="n">
         <v>0.0431236485708859</v>
       </c>
-      <c r="BJ21" s="139" t="n">
+      <c r="BJ21" s="140" t="n">
         <v>0.0429855738362184</v>
       </c>
-      <c r="BK21" s="139" t="n">
+      <c r="BK21" s="140" t="n">
         <v>0.0439842170940799</v>
       </c>
-      <c r="BL21" s="139" t="n">
+      <c r="BL21" s="140" t="n">
         <v>0.0421844159307167</v>
       </c>
-      <c r="BM21" s="139" t="n">
+      <c r="BM21" s="140" t="n">
         <v>0.0440947025109437</v>
       </c>
-      <c r="BN21" s="139" t="n">
+      <c r="BN21" s="140" t="n">
         <v>0.0422407780212036</v>
       </c>
-      <c r="BO21" s="139" t="n">
+      <c r="BO21" s="140" t="n">
         <v>0.0434211554225535</v>
       </c>
-      <c r="BP21" s="139" t="n">
+      <c r="BP21" s="140" t="n">
         <v>0.0444316965767415</v>
       </c>
-      <c r="BQ21" s="139" t="n">
+      <c r="BQ21" s="140" t="n">
         <v>0.0433958413419689</v>
       </c>
-      <c r="BR21" s="139" t="n">
+      <c r="BR21" s="140" t="n">
         <v>0.0423085214854351</v>
       </c>
-      <c r="BS21" s="139" t="n">
+      <c r="BS21" s="140" t="n">
         <v>0.0426698537448755</v>
       </c>
-      <c r="BT21" s="139" t="n">
+      <c r="BT21" s="140" t="n">
         <v>0.0435056684406616</v>
       </c>
-      <c r="BU21" s="139" t="n">
+      <c r="BU21" s="140" t="n">
         <v>0.0428030218405729</v>
       </c>
-      <c r="BV21" s="139" t="n">
+      <c r="BV21" s="140" t="n">
         <v>0.0431618567977709</v>
       </c>
-      <c r="BW21" s="139" t="n">
+      <c r="BW21" s="140" t="n">
         <v>0.0429266879969106</v>
       </c>
-      <c r="BX21" s="140" t="n">
+      <c r="BX21" s="141" t="n">
         <v>0.0430365224431418</v>
       </c>
-      <c r="BY21" s="138" t="n">
+      <c r="BY21" s="139" t="n">
         <v>0.0444423708108389</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="BR24" s="102"/>
+      <c r="BR24" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -24210,521 +24210,521 @@
   <dimension ref="A1:E47"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="93" width="5.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="93" width="26.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="93" width="14.2"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="141" t="s">
+      <c r="C1" s="142" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="142"/>
-      <c r="B2" s="143" t="s">
+      <c r="A2" s="143"/>
+      <c r="B2" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="144" t="n">
+      <c r="C2" s="145" t="n">
         <v>0.0751673224912434</v>
       </c>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="142"/>
-      <c r="B3" s="143" t="s">
+      <c r="A3" s="143"/>
+      <c r="B3" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="144" t="n">
+      <c r="C3" s="145" t="n">
         <v>0.819620434999222</v>
       </c>
-      <c r="D3" s="142"/>
-      <c r="E3" s="142"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="142"/>
-      <c r="B4" s="142" t="s">
+      <c r="A4" s="143"/>
+      <c r="B4" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="142" t="n">
+      <c r="C4" s="143" t="n">
         <v>0.0951665535643471</v>
       </c>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="142"/>
-      <c r="B5" s="142" t="s">
+      <c r="A5" s="143"/>
+      <c r="B5" s="143" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="142" t="n">
+      <c r="C5" s="143" t="n">
         <v>0.444139432258903</v>
       </c>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="142"/>
-      <c r="B6" s="142" t="s">
+      <c r="A6" s="143"/>
+      <c r="B6" s="143" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="142" t="n">
+      <c r="C6" s="143" t="n">
         <v>0.000521679575821926</v>
       </c>
-      <c r="D6" s="142"/>
-      <c r="E6" s="142"/>
+      <c r="D6" s="143"/>
+      <c r="E6" s="143"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="142"/>
-      <c r="B7" s="142" t="s">
+      <c r="A7" s="143"/>
+      <c r="B7" s="143" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="142" t="n">
+      <c r="C7" s="143" t="n">
         <v>0.145336159598175</v>
       </c>
-      <c r="D7" s="142"/>
-      <c r="E7" s="142"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="143"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="142"/>
-      <c r="B8" s="142" t="s">
+      <c r="A8" s="143"/>
+      <c r="B8" s="143" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="142" t="n">
+      <c r="C8" s="143" t="n">
         <v>0.00734992102454144</v>
       </c>
-      <c r="D8" s="142"/>
-      <c r="E8" s="142"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="142"/>
-      <c r="B9" s="142" t="s">
+      <c r="A9" s="143"/>
+      <c r="B9" s="143" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="142" t="n">
+      <c r="C9" s="143" t="n">
         <v>1.45210703566165E-006</v>
       </c>
-      <c r="D9" s="142"/>
-      <c r="E9" s="142"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="143"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="142"/>
-      <c r="B10" s="142" t="s">
+      <c r="A10" s="143"/>
+      <c r="B10" s="143" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="142" t="n">
+      <c r="C10" s="143" t="n">
         <v>0.157316000725758</v>
       </c>
-      <c r="D10" s="142"/>
-      <c r="E10" s="142"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="143"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="142"/>
-      <c r="B11" s="142" t="s">
+      <c r="A11" s="143"/>
+      <c r="B11" s="143" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="142" t="n">
+      <c r="C11" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="142"/>
-      <c r="E11" s="142"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="142"/>
-      <c r="B12" s="142" t="s">
+      <c r="A12" s="143"/>
+      <c r="B12" s="143" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="142" t="n">
+      <c r="C12" s="143" t="n">
         <v>0.00282110750931128</v>
       </c>
-      <c r="D12" s="142"/>
-      <c r="E12" s="142"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="143"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="142"/>
-      <c r="B13" s="142" t="s">
+      <c r="A13" s="143"/>
+      <c r="B13" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="142" t="n">
+      <c r="C13" s="143" t="n">
         <v>0.147347693636107</v>
       </c>
-      <c r="D13" s="142"/>
-      <c r="E13" s="142"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="142"/>
-      <c r="B14" s="143" t="s">
+      <c r="A14" s="143"/>
+      <c r="B14" s="144" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="144" t="n">
+      <c r="C14" s="145" t="n">
         <v>0.180379565000779</v>
       </c>
-      <c r="D14" s="142"/>
-      <c r="E14" s="142"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="142"/>
-      <c r="B15" s="142" t="s">
+      <c r="A15" s="143"/>
+      <c r="B15" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="142" t="n">
+      <c r="C15" s="143" t="n">
         <v>0.0246941771151519</v>
       </c>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="142"/>
-      <c r="B16" s="142" t="s">
+      <c r="A16" s="143"/>
+      <c r="B16" s="143" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="142" t="n">
+      <c r="C16" s="143" t="n">
         <v>0.752688739243253</v>
       </c>
-      <c r="D16" s="142"/>
-      <c r="E16" s="142"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="142"/>
-      <c r="B17" s="142" t="s">
+      <c r="A17" s="143"/>
+      <c r="B17" s="143" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="142" t="n">
+      <c r="C17" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="142"/>
-      <c r="E17" s="142"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="142"/>
-      <c r="B18" s="142" t="s">
+      <c r="A18" s="143"/>
+      <c r="B18" s="143" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="142" t="n">
+      <c r="C18" s="143" t="n">
         <v>0.0611490999517944</v>
       </c>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="142"/>
-      <c r="B19" s="142" t="s">
+      <c r="A19" s="143"/>
+      <c r="B19" s="143" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="142" t="n">
+      <c r="C19" s="143" t="n">
         <v>0.00848949761991656</v>
       </c>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
+      <c r="D19" s="143"/>
+      <c r="E19" s="143"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="142"/>
-      <c r="B20" s="142" t="s">
+      <c r="A20" s="143"/>
+      <c r="B20" s="143" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="142" t="n">
+      <c r="C20" s="143" t="n">
         <v>3.46514075460914E-005</v>
       </c>
-      <c r="D20" s="142"/>
-      <c r="E20" s="142"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="143"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="142"/>
-      <c r="B21" s="142" t="s">
+      <c r="A21" s="143"/>
+      <c r="B21" s="143" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="142" t="n">
+      <c r="C21" s="143" t="n">
         <v>0.0318234654550061</v>
       </c>
-      <c r="D21" s="142"/>
-      <c r="E21" s="142"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="143"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142" t="s">
+      <c r="A22" s="143"/>
+      <c r="B22" s="143" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="142" t="n">
+      <c r="C22" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="142"/>
-      <c r="E22" s="142"/>
+      <c r="D22" s="143"/>
+      <c r="E22" s="143"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="142"/>
-      <c r="B23" s="142" t="s">
+      <c r="A23" s="143"/>
+      <c r="B23" s="143" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="142" t="n">
+      <c r="C23" s="143" t="n">
         <v>0.119664559599747</v>
       </c>
-      <c r="D23" s="142"/>
-      <c r="E23" s="142"/>
+      <c r="D23" s="143"/>
+      <c r="E23" s="143"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="142"/>
-      <c r="B24" s="142" t="s">
+      <c r="A24" s="143"/>
+      <c r="B24" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="142" t="n">
+      <c r="C24" s="143" t="n">
         <v>0.00145580960758527</v>
       </c>
-      <c r="D24" s="142"/>
-      <c r="E24" s="142"/>
+      <c r="D24" s="143"/>
+      <c r="E24" s="143"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="142"/>
-      <c r="B25" s="143" t="s">
+      <c r="A25" s="143"/>
+      <c r="B25" s="144" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="144" t="n">
+      <c r="C25" s="145" t="n">
         <v>0.924832677508757</v>
       </c>
-      <c r="D25" s="142"/>
-      <c r="E25" s="142"/>
+      <c r="D25" s="143"/>
+      <c r="E25" s="143"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="142"/>
-      <c r="B26" s="143" t="s">
+      <c r="A26" s="143"/>
+      <c r="B26" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="144" t="n">
+      <c r="C26" s="145" t="n">
         <v>0.587969181889205</v>
       </c>
-      <c r="D26" s="142"/>
-      <c r="E26" s="142"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="143"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="142"/>
-      <c r="B27" s="142" t="s">
+      <c r="A27" s="143"/>
+      <c r="B27" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="142" t="n">
+      <c r="C27" s="143" t="n">
         <v>0.0958253434886631</v>
       </c>
-      <c r="D27" s="142"/>
-      <c r="E27" s="142"/>
+      <c r="D27" s="143"/>
+      <c r="E27" s="143"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="142"/>
-      <c r="B28" s="142" t="s">
+      <c r="A28" s="143"/>
+      <c r="B28" s="143" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="142" t="n">
+      <c r="C28" s="143" t="n">
         <v>0.485640231800696</v>
       </c>
-      <c r="D28" s="142"/>
-      <c r="E28" s="142"/>
+      <c r="D28" s="143"/>
+      <c r="E28" s="143"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="142"/>
-      <c r="B29" s="142" t="s">
+      <c r="A29" s="143"/>
+      <c r="B29" s="143" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="142" t="n">
+      <c r="C29" s="143" t="n">
         <v>0.000272466585363393</v>
       </c>
-      <c r="D29" s="142"/>
-      <c r="E29" s="142"/>
+      <c r="D29" s="143"/>
+      <c r="E29" s="143"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="142"/>
-      <c r="B30" s="142" t="s">
+      <c r="A30" s="143"/>
+      <c r="B30" s="143" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="142" t="n">
+      <c r="C30" s="143" t="n">
         <v>0.0309302512502964</v>
       </c>
-      <c r="D30" s="142"/>
-      <c r="E30" s="142"/>
+      <c r="D30" s="143"/>
+      <c r="E30" s="143"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="142"/>
-      <c r="B31" s="142" t="s">
+      <c r="A31" s="143"/>
+      <c r="B31" s="143" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="142" t="n">
+      <c r="C31" s="143" t="n">
         <v>0.00582226594193594</v>
       </c>
-      <c r="D31" s="142"/>
-      <c r="E31" s="142"/>
+      <c r="D31" s="143"/>
+      <c r="E31" s="143"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="142"/>
-      <c r="B32" s="142" t="s">
+      <c r="A32" s="143"/>
+      <c r="B32" s="143" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="142" t="n">
+      <c r="C32" s="143" t="n">
         <v>0.000881105254506303</v>
       </c>
-      <c r="D32" s="142"/>
-      <c r="E32" s="142"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="142"/>
-      <c r="B33" s="142" t="s">
+      <c r="A33" s="143"/>
+      <c r="B33" s="143" t="s">
         <v>84</v>
       </c>
-      <c r="C33" s="142" t="n">
+      <c r="C33" s="143" t="n">
         <v>0.26909980032473</v>
       </c>
-      <c r="D33" s="142"/>
-      <c r="E33" s="142"/>
+      <c r="D33" s="143"/>
+      <c r="E33" s="143"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="142"/>
-      <c r="B34" s="142" t="s">
+      <c r="A34" s="143"/>
+      <c r="B34" s="143" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="142" t="n">
+      <c r="C34" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="142"/>
-      <c r="E34" s="142"/>
+      <c r="D34" s="143"/>
+      <c r="E34" s="143"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="142"/>
-      <c r="B35" s="142" t="s">
+      <c r="A35" s="143"/>
+      <c r="B35" s="143" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="142" t="n">
+      <c r="C35" s="143" t="n">
         <v>0.035704945251689</v>
       </c>
-      <c r="D35" s="142"/>
-      <c r="E35" s="142"/>
+      <c r="D35" s="143"/>
+      <c r="E35" s="143"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="142"/>
-      <c r="B36" s="142" t="s">
+      <c r="A36" s="143"/>
+      <c r="B36" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="142" t="n">
+      <c r="C36" s="143" t="n">
         <v>0.0758235901021198</v>
       </c>
-      <c r="D36" s="142"/>
-      <c r="E36" s="142"/>
+      <c r="D36" s="143"/>
+      <c r="E36" s="143"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="142"/>
-      <c r="B37" s="143" t="s">
+      <c r="A37" s="143"/>
+      <c r="B37" s="144" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="144" t="n">
+      <c r="C37" s="145" t="n">
         <v>0.412030818110795</v>
       </c>
-      <c r="D37" s="142"/>
-      <c r="E37" s="142"/>
+      <c r="D37" s="143"/>
+      <c r="E37" s="143"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="142"/>
-      <c r="B38" s="142" t="s">
+      <c r="A38" s="143"/>
+      <c r="B38" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="142" t="n">
+      <c r="C38" s="143" t="n">
         <v>0.0380573762351591</v>
       </c>
-      <c r="D38" s="142"/>
-      <c r="E38" s="142"/>
+      <c r="D38" s="143"/>
+      <c r="E38" s="143"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="142"/>
-      <c r="B39" s="142" t="s">
+      <c r="A39" s="143"/>
+      <c r="B39" s="143" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="142" t="n">
+      <c r="C39" s="143" t="n">
         <v>0.411445768577163</v>
       </c>
-      <c r="D39" s="142"/>
-      <c r="E39" s="142"/>
+      <c r="D39" s="143"/>
+      <c r="E39" s="143"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="142"/>
-      <c r="B40" s="142" t="s">
+      <c r="A40" s="143"/>
+      <c r="B40" s="143" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="142" t="n">
+      <c r="C40" s="143" t="n">
         <v>5.69841418035346E-005</v>
       </c>
-      <c r="D40" s="142"/>
-      <c r="E40" s="142"/>
+      <c r="D40" s="143"/>
+      <c r="E40" s="143"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="142"/>
-      <c r="B41" s="142" t="s">
+      <c r="A41" s="143"/>
+      <c r="B41" s="143" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="142" t="n">
+      <c r="C41" s="143" t="n">
         <v>0.00235101313202752</v>
       </c>
-      <c r="D41" s="142"/>
-      <c r="E41" s="142"/>
+      <c r="D41" s="143"/>
+      <c r="E41" s="143"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="142"/>
-      <c r="B42" s="142" t="s">
+      <c r="A42" s="143"/>
+      <c r="B42" s="143" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="142" t="n">
+      <c r="C42" s="143" t="n">
         <v>0.0143169220894984</v>
       </c>
-      <c r="D42" s="142"/>
-      <c r="E42" s="142"/>
+      <c r="D42" s="143"/>
+      <c r="E42" s="143"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="142"/>
-      <c r="B43" s="142" t="s">
+      <c r="A43" s="143"/>
+      <c r="B43" s="143" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="142" t="n">
+      <c r="C43" s="143" t="n">
         <v>0.0592221411941844</v>
       </c>
-      <c r="D43" s="142"/>
-      <c r="E43" s="142"/>
+      <c r="D43" s="143"/>
+      <c r="E43" s="143"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="142"/>
-      <c r="B44" s="142" t="s">
+      <c r="A44" s="143"/>
+      <c r="B44" s="143" t="s">
         <v>84</v>
       </c>
-      <c r="C44" s="142" t="n">
+      <c r="C44" s="143" t="n">
         <v>0.0874699530203374</v>
       </c>
-      <c r="D44" s="142"/>
-      <c r="E44" s="142"/>
+      <c r="D44" s="143"/>
+      <c r="E44" s="143"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="142"/>
-      <c r="B45" s="142" t="s">
+      <c r="A45" s="143"/>
+      <c r="B45" s="143" t="s">
         <v>85</v>
       </c>
-      <c r="C45" s="142" t="n">
+      <c r="C45" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="142"/>
-      <c r="E45" s="142"/>
+      <c r="D45" s="143"/>
+      <c r="E45" s="143"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="142"/>
-      <c r="B46" s="142" t="s">
+      <c r="A46" s="143"/>
+      <c r="B46" s="143" t="s">
         <v>86</v>
       </c>
-      <c r="C46" s="142" t="n">
+      <c r="C46" s="143" t="n">
         <v>0.383264783601781</v>
       </c>
-      <c r="D46" s="142"/>
-      <c r="E46" s="142"/>
+      <c r="D46" s="143"/>
+      <c r="E46" s="143"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="142"/>
-      <c r="B47" s="142" t="s">
+      <c r="A47" s="143"/>
+      <c r="B47" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="142" t="n">
+      <c r="C47" s="143" t="n">
         <v>0.00381505800804553</v>
       </c>
-      <c r="D47" s="142"/>
-      <c r="E47" s="142"/>
+      <c r="D47" s="143"/>
+      <c r="E47" s="143"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -24746,180 +24746,180 @@
   <dimension ref="B1:C28"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="93" width="3.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="93" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="141" t="s">
+      <c r="C1" s="142" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="93" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="145" t="s">
+      <c r="C2" s="146" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="143" t="s">
+      <c r="B3" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="146" t="n">
+      <c r="C3" s="147" t="n">
         <v>0.102769550518034</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="142" t="n">
+      <c r="C4" s="143" t="n">
         <v>0.232471083612584</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="142" t="n">
+      <c r="C5" s="143" t="n">
         <v>0.0886797183056611</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="142" t="n">
+      <c r="C6" s="143" t="n">
         <v>0.0580276742923043</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="93" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="142" t="n">
+      <c r="C7" s="143" t="n">
         <v>0.157383753547195</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="142" t="n">
+      <c r="C8" s="143" t="n">
         <v>0.0414943679333337</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="93" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="142" t="n">
+      <c r="C9" s="143" t="n">
         <v>0.346627121625464</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="93" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="142" t="n">
+      <c r="C10" s="143" t="n">
         <v>0.075316280683458</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="143" t="s">
+      <c r="B11" s="144" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="146" t="n">
+      <c r="C11" s="147" t="n">
         <v>0.897230449481966</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="142" t="n">
+      <c r="C12" s="143" t="n">
         <v>0.106746149803862</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="142" t="n">
+      <c r="C13" s="143" t="n">
         <v>0.100483559265677</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="142" t="n">
+      <c r="C14" s="143" t="n">
         <v>0.0874407400871563</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="93" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="142" t="n">
+      <c r="C15" s="143" t="n">
         <v>0.185553092213221</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="142" t="n">
+      <c r="C16" s="143" t="n">
         <v>0.0255661408527924</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="93" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="142" t="n">
+      <c r="C17" s="143" t="n">
         <v>0.36465555572555</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="93" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="142" t="n">
+      <c r="C18" s="143" t="n">
         <v>0.129554762051742</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="142"/>
+      <c r="C19" s="143"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="142"/>
+      <c r="C20" s="143"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="142"/>
+      <c r="C21" s="143"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="142"/>
+      <c r="C22" s="143"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="142"/>
+      <c r="C23" s="143"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="142"/>
+      <c r="C24" s="143"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="142"/>
+      <c r="C25" s="143"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="142"/>
+      <c r="C26" s="143"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="142"/>
+      <c r="C27" s="143"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="142"/>
+      <c r="C28" s="143"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
